--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'차량인보이스'!$A$1:$I$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'차량팩킹'!$A$1:$I$40</definedName>
   </definedNames>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -5806,8 +5806,8 @@
         </is>
       </c>
       <c r="I6" s="115" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"소형승용","Small Passenger"),"중형승용","Medium Passenger"),"대형승용","HEAVY Passenger"),"중형승합","Medium Ven"),"대형승합","Large Ven"),"중형화물","Medium Cargo")</f>
-        <v>Medium Passenger</v>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"승용 소형","Small Passenger"),"승용 중형","Medium Passenger"),"승용 대형","HEAVY Passenger"),"중형 승합","Medium Ven"),"대형 승합","Large Ven"),"중형 화물","Medium Cargo")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
@@ -6131,7 +6131,7 @@
       <c r="H13" s="247"/>
       <c r="I13" s="113" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
-        <v>DIESEL</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" customHeight="1" ht="120.75" s="246" customFormat="1">
@@ -6202,7 +6202,7 @@
           </r>
         </is>
       </c>
-      <c r="I15" t="str">
+      <c r="I15" s="246" t="str">
         <f t="array" ref="I15" aca="1" ca="1">_xlfn.TEXTJOIN(",",,
  _xlfn.UNIQUE(_xlfn.IFNA(INDEX({"GASOLIN","DIESEL","LPG"},
  MATCH(G15,{"휘발유","경유","LPG"},0)),""),1))</f>
@@ -6218,14 +6218,14 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="111">
+      <c r="D16" s="111" t="str">
         <f>SUM(B15,D15)</f>
-        <v>16400</v>
+        <v>0</v>
       </c>
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -6676,9 +6676,9 @@
           </r>
         </is>
       </c>
-      <c r="C3" s="153">
+      <c r="C3" s="153" t="str">
         <f>구매리스트!G3</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D3" s="253"/>
       <c r="E3" s="253"/>
@@ -6708,9 +6708,9 @@
           </r>
         </is>
       </c>
-      <c r="O3" s="150">
+      <c r="O3" s="150" t="str">
         <f>구매리스트!B6</f>
-        <v>42853</v>
+        <v>0</v>
       </c>
       <c r="P3" s="253"/>
       <c r="Q3" s="254"/>
@@ -6728,7 +6728,7 @@
       <c r="D4" s="255"/>
       <c r="E4" s="151" t="str">
         <f>구매리스트!B4</f>
-        <v>19더9065</v>
+        <v>0</v>
       </c>
       <c r="F4" s="255"/>
       <c r="G4" s="255"/>
@@ -6745,7 +6745,7 @@
       <c r="L4" s="256"/>
       <c r="M4" s="151" t="str">
         <f>구매리스트!G6</f>
-        <v>중형승용</v>
+        <v>0</v>
       </c>
       <c r="N4" s="256"/>
       <c r="O4" s="136" t="inlineStr">
@@ -6777,7 +6777,7 @@
       <c r="D5" s="256"/>
       <c r="E5" s="151" t="str">
         <f>구매리스트!B5</f>
-        <v>BMW 520d xDrive</v>
+        <v>0</v>
       </c>
       <c r="F5" s="255"/>
       <c r="G5" s="255"/>
@@ -6794,13 +6794,13 @@
       <c r="L5" s="256"/>
       <c r="M5" s="134" t="str">
         <f>구매리스트!G4</f>
-        <v>JC51</v>
+        <v>0</v>
       </c>
       <c r="N5" s="255"/>
       <c r="O5" s="255"/>
       <c r="P5" s="257" t="str">
         <f>구매리스트!I5</f>
-        <v>2017-02</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="256"/>
     </row>
@@ -6817,7 +6817,7 @@
       <c r="D6" s="256"/>
       <c r="E6" s="151" t="str">
         <f>구매리스트!D5</f>
-        <v>WBAJC5105HG850942</v>
+        <v>0</v>
       </c>
       <c r="F6" s="255"/>
       <c r="G6" s="255"/>
@@ -6834,7 +6834,7 @@
       <c r="L6" s="256"/>
       <c r="M6" s="151" t="str">
         <f>구매리스트!I4</f>
-        <v>B47D20A</v>
+        <v>0</v>
       </c>
       <c r="N6" s="255"/>
       <c r="O6" s="255"/>
@@ -6921,7 +6921,7 @@
       <c r="O8" s="255"/>
       <c r="P8" s="255"/>
       <c r="Q8" s="256"/>
-      <c r="T8" t="inlineStr">
+      <c r="T8" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -6996,16 +6996,16 @@
           </r>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="L13" s="155">
+      <c r="B13" s="246" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="L13" s="155" t="str">
         <f>구매리스트!I3</f>
-        <v>45875</v>
+        <v>0</v>
       </c>
       <c r="O13" s="246"/>
       <c r="P13" s="264"/>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="17" spans="1:20" customHeight="1" ht="8.25" s="246" customFormat="1">
       <c r="A17" s="4"/>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -7116,7 +7116,7 @@
       <c r="E19" s="251"/>
       <c r="F19" s="268" t="str">
         <f>구매리스트!G5</f>
-        <v>001-2-00057-0002-1217</v>
+        <v>0</v>
       </c>
       <c r="G19" s="251"/>
       <c r="H19" s="251"/>
@@ -7247,9 +7247,9 @@
         </is>
       </c>
       <c r="C21" s="256"/>
-      <c r="D21" s="157">
+      <c r="D21" s="157" t="str">
         <f>구매리스트!G7</f>
-        <v>4935</v>
+        <v>0</v>
       </c>
       <c r="E21" s="255"/>
       <c r="F21" s="16" t="inlineStr">
@@ -7273,9 +7273,9 @@
           </r>
         </is>
       </c>
-      <c r="I21" s="120">
+      <c r="I21" s="120" t="str">
         <f>구매리스트!I7</f>
-        <v>1860</v>
+        <v>0</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -7284,18 +7284,18 @@
           </r>
         </is>
       </c>
-      <c r="L21" s="121">
+      <c r="L21" s="121" t="str">
         <f>구매리스트!I10</f>
-        <v>45775</v>
-      </c>
-      <c r="M21" s="121">
+        <v>0</v>
+      </c>
+      <c r="M21" s="121" t="str">
         <f>구매리스트!I11</f>
-        <v>46504</v>
+        <v>0</v>
       </c>
       <c r="N21" s="12"/>
-      <c r="O21" s="122">
+      <c r="O21" s="122" t="str">
         <f>구매리스트!I12</f>
-        <v>163268</v>
+        <v>0</v>
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
@@ -7318,7 +7318,7 @@
       <c r="C22" s="256"/>
       <c r="D22" s="141" t="str">
         <f>구매리스트!G8</f>
-        <v>1455</v>
+        <v>0</v>
       </c>
       <c r="E22" s="255"/>
       <c r="F22" s="16" t="inlineStr">
@@ -7342,9 +7342,9 @@
           </r>
         </is>
       </c>
-      <c r="I22" s="120">
+      <c r="I22" s="120" t="str">
         <f>구매리스트!I8</f>
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
       <c r="C23" s="256"/>
       <c r="D23" s="141" t="str">
         <f>구매리스트!G9</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E23" s="255"/>
       <c r="F23" s="16" t="inlineStr">
@@ -7437,7 +7437,7 @@
       <c r="C24" s="252"/>
       <c r="D24" s="270" t="str">
         <f>구매리스트!G10</f>
-        <v>1995</v>
+        <v>0</v>
       </c>
       <c r="E24" s="251"/>
       <c r="F24" s="251"/>
@@ -7513,7 +7513,7 @@
       <c r="C27" s="256"/>
       <c r="D27" s="141" t="str">
         <f>구매리스트!G11</f>
-        <v>190/4000</v>
+        <v>0</v>
       </c>
       <c r="E27" s="255"/>
       <c r="F27" s="255"/>
@@ -7552,7 +7552,7 @@
       <c r="C28" s="252"/>
       <c r="D28" s="274" t="str">
         <f>구매리스트!G12</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28" s="251"/>
       <c r="F28" s="251"/>
@@ -7633,12 +7633,12 @@
       <c r="C31" s="256"/>
       <c r="D31" s="146" t="str">
         <f>구매리스트!G13</f>
-        <v>경유</v>
+        <v>0</v>
       </c>
       <c r="E31" s="255"/>
-      <c r="F31" s="145">
+      <c r="F31" s="145" t="str">
         <f>구매리스트!H13</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G31" s="255"/>
       <c r="H31" s="161" t="inlineStr">
@@ -7967,7 +7967,7 @@
       <c r="I41" s="255"/>
       <c r="J41" s="256"/>
       <c r="L41" s="4"/>
-      <c r="O41" t="inlineStr">
+      <c r="O41" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -8296,9 +8296,9 @@
           </r>
         </is>
       </c>
-      <c r="C3" s="153">
+      <c r="C3" s="153" t="str">
         <f>구매리스트!G3</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D3" s="253"/>
       <c r="E3" s="253"/>
@@ -8329,9 +8329,9 @@
       <c r="L3" s="253"/>
       <c r="M3" s="253"/>
       <c r="N3" s="253"/>
-      <c r="O3" s="176">
+      <c r="O3" s="176" t="str">
         <f>구매리스트!B6</f>
-        <v>42853</v>
+        <v>0</v>
       </c>
       <c r="P3" s="253"/>
       <c r="Q3" s="254"/>
@@ -8349,7 +8349,7 @@
       <c r="D4" s="256"/>
       <c r="E4" s="151" t="str">
         <f>구매리스트!D4</f>
-        <v>19DEO9065</v>
+        <v>0</v>
       </c>
       <c r="F4" s="255"/>
       <c r="G4" s="255"/>
@@ -8366,7 +8366,7 @@
       <c r="L4" s="255"/>
       <c r="M4" s="177" t="str">
         <f>구매리스트!I6</f>
-        <v>Medium Passenger</v>
+        <v>0</v>
       </c>
       <c r="N4" s="256"/>
       <c r="O4" s="136" t="inlineStr">
@@ -8398,7 +8398,7 @@
       <c r="D5" s="256"/>
       <c r="E5" s="151" t="str">
         <f>구매리스트!B5</f>
-        <v>BMW 520d xDrive</v>
+        <v>0</v>
       </c>
       <c r="F5" s="255"/>
       <c r="G5" s="255"/>
@@ -8415,16 +8415,16 @@
       <c r="L5" s="256"/>
       <c r="M5" s="134" t="str">
         <f>구매리스트!G4</f>
-        <v>JC51</v>
+        <v>0</v>
       </c>
       <c r="N5" s="255"/>
       <c r="O5" s="255"/>
       <c r="P5" s="257" t="str">
         <f>구매리스트!I5</f>
-        <v>2017-02</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="256"/>
-      <c r="S5" t="inlineStr">
+      <c r="S5" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -8445,7 +8445,7 @@
       <c r="D6" s="256"/>
       <c r="E6" s="151" t="str">
         <f>구매리스트!D5</f>
-        <v>WBAJC5105HG850942</v>
+        <v>0</v>
       </c>
       <c r="F6" s="255"/>
       <c r="G6" s="255"/>
@@ -8462,7 +8462,7 @@
       <c r="L6" s="256"/>
       <c r="M6" s="151" t="str">
         <f>구매리스트!I4</f>
-        <v>B47D20A</v>
+        <v>0</v>
       </c>
       <c r="N6" s="255"/>
       <c r="O6" s="255"/>
@@ -8555,7 +8555,7 @@
       <c r="O8" s="255"/>
       <c r="P8" s="255"/>
       <c r="Q8" s="256"/>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -8636,23 +8636,23 @@
           </r>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="L13" s="169">
+      <c r="B13" s="246" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J13" s="246" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="L13" s="169" t="str">
         <f>구매리스트!I3</f>
-        <v>45875</v>
+        <v>0</v>
       </c>
       <c r="O13" s="246"/>
       <c r="P13" s="264"/>
@@ -8677,7 +8677,7 @@
         </is>
       </c>
       <c r="Q15" s="263"/>
-      <c r="W15" t="inlineStr">
+      <c r="W15" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -8706,7 +8706,7 @@
     </row>
     <row r="17" spans="1:23" customHeight="1" ht="8.25" s="246" customFormat="1">
       <c r="A17" s="4"/>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -8771,7 +8771,7 @@
       <c r="E19" s="251"/>
       <c r="F19" s="268" t="str">
         <f>구매리스트!G5</f>
-        <v>001-2-00057-0002-1217</v>
+        <v>0</v>
       </c>
       <c r="G19" s="251"/>
       <c r="H19" s="251"/>
@@ -8870,9 +8870,9 @@
         </is>
       </c>
       <c r="C21" s="256"/>
-      <c r="D21" s="157">
+      <c r="D21" s="157" t="str">
         <f>구매리스트!G7</f>
-        <v>4935</v>
+        <v>0</v>
       </c>
       <c r="E21" s="255"/>
       <c r="F21" s="16" t="inlineStr">
@@ -8896,9 +8896,9 @@
           </r>
         </is>
       </c>
-      <c r="I21" s="120">
+      <c r="I21" s="120" t="str">
         <f>구매리스트!I7</f>
-        <v>1860</v>
+        <v>0</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -8907,22 +8907,22 @@
           </r>
         </is>
       </c>
-      <c r="L21" s="121">
+      <c r="L21" s="121" t="str">
         <f>구매리스트!I10</f>
-        <v>45775</v>
-      </c>
-      <c r="M21" s="121">
+        <v>0</v>
+      </c>
+      <c r="M21" s="121" t="str">
         <f>구매리스트!I11</f>
-        <v>46504</v>
+        <v>0</v>
       </c>
       <c r="N21" s="12"/>
-      <c r="O21" s="122">
+      <c r="O21" s="122" t="str">
         <f>구매리스트!I12</f>
-        <v>163268</v>
+        <v>0</v>
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
-      <c r="R21" t="inlineStr">
+      <c r="R21" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -8948,7 +8948,7 @@
       <c r="C22" s="256"/>
       <c r="D22" s="141" t="str">
         <f>구매리스트!G8</f>
-        <v>1455</v>
+        <v>0</v>
       </c>
       <c r="E22" s="255"/>
       <c r="F22" s="16" t="inlineStr">
@@ -8972,9 +8972,9 @@
           </r>
         </is>
       </c>
-      <c r="I22" s="120">
+      <c r="I22" s="120" t="str">
         <f>구매리스트!I8</f>
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
-      <c r="S22" t="inlineStr">
+      <c r="S22" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -9015,7 +9015,7 @@
       <c r="C23" s="256"/>
       <c r="D23" s="141" t="str">
         <f>구매리스트!G9</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E23" s="255"/>
       <c r="F23" s="73" t="inlineStr">
@@ -9074,7 +9074,7 @@
       <c r="C24" s="252"/>
       <c r="D24" s="270" t="str">
         <f>구매리스트!G10</f>
-        <v>1995</v>
+        <v>0</v>
       </c>
       <c r="E24" s="251"/>
       <c r="F24" s="251"/>
@@ -9094,7 +9094,7 @@
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
-      <c r="S24" t="inlineStr">
+      <c r="S24" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -9139,7 +9139,7 @@
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
-      <c r="S26" t="inlineStr">
+      <c r="S26" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -9165,7 +9165,7 @@
       <c r="C27" s="256"/>
       <c r="D27" s="141" t="str">
         <f>구매리스트!G11</f>
-        <v>190/4000</v>
+        <v>0</v>
       </c>
       <c r="E27" s="255"/>
       <c r="F27" s="255"/>
@@ -9204,7 +9204,7 @@
       <c r="C28" s="252"/>
       <c r="D28" s="274" t="str">
         <f>구매리스트!G12</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28" s="251"/>
       <c r="F28" s="251"/>
@@ -9287,12 +9287,12 @@
       <c r="C31" s="256"/>
       <c r="D31" s="146" t="str">
         <f>구매리스트!I13</f>
-        <v>DIESEL</v>
+        <v>0</v>
       </c>
       <c r="E31" s="255"/>
-      <c r="F31" s="145">
+      <c r="F31" s="145" t="str">
         <f>구매리스트!H13</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G31" s="255"/>
       <c r="H31" s="161" t="inlineStr">
@@ -9624,7 +9624,7 @@
       <c r="I41" s="255"/>
       <c r="J41" s="256"/>
       <c r="L41" s="4"/>
-      <c r="O41" t="inlineStr">
+      <c r="O41" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -9945,9 +9945,9 @@
           </r>
         </is>
       </c>
-      <c r="B6" s="205">
+      <c r="B6" s="205" t="str">
         <f>구매리스트!D3</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C6" s="255"/>
       <c r="D6" s="255"/>
@@ -10020,7 +10020,7 @@
       <c r="D8" s="304"/>
       <c r="E8" s="199" t="str">
         <f>구매리스트!B4</f>
-        <v>19더9065</v>
+        <v>0</v>
       </c>
       <c r="F8" s="251"/>
       <c r="G8" s="304"/>
@@ -10071,9 +10071,9 @@
         </is>
       </c>
       <c r="J9" s="305"/>
-      <c r="K9" s="203">
+      <c r="K9" s="203" t="str">
         <f>구매리스트!D7</f>
-        <v>167725</v>
+        <v>0</v>
       </c>
       <c r="N9" s="82"/>
       <c r="O9" s="83"/>
@@ -10090,7 +10090,7 @@
       <c r="D10" s="307"/>
       <c r="E10" s="308" t="str">
         <f>구매리스트!B5</f>
-        <v>BMW 520d xDrive</v>
+        <v>0</v>
       </c>
       <c r="F10" s="309"/>
       <c r="G10" s="307"/>
@@ -10105,7 +10105,7 @@
       <c r="J10" s="307"/>
       <c r="K10" s="310" t="str">
         <f>구매리스트!D5</f>
-        <v>WBAJC5105HG850942</v>
+        <v>0</v>
       </c>
       <c r="L10" s="309"/>
       <c r="M10" s="309"/>
@@ -10152,7 +10152,7 @@
       <c r="D12" s="305"/>
       <c r="E12" s="185" t="str">
         <f>구매리스트!I4</f>
-        <v>B47D20A</v>
+        <v>0</v>
       </c>
       <c r="G12" s="305"/>
       <c r="H12" s="181" t="inlineStr">
@@ -10163,9 +10163,9 @@
         </is>
       </c>
       <c r="J12" s="305"/>
-      <c r="K12" s="184">
+      <c r="K12" s="184" t="str">
         <f>구매리스트!D6</f>
-        <v>2017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
@@ -10202,7 +10202,7 @@
       <c r="D14" s="314"/>
       <c r="E14" s="315" t="str">
         <f>구매리스트!G5</f>
-        <v>001-2-00057-0002-1217</v>
+        <v>0</v>
       </c>
       <c r="F14" s="316"/>
       <c r="G14" s="314"/>
@@ -10276,9 +10276,9 @@
         </is>
       </c>
       <c r="D17" s="305"/>
-      <c r="E17" s="188">
+      <c r="E17" s="188" t="str">
         <f>구매리스트!B6</f>
-        <v>42853</v>
+        <v>0</v>
       </c>
       <c r="G17" s="305"/>
       <c r="H17" s="181" t="inlineStr">
@@ -10476,9 +10476,9 @@
       <c r="B24" s="251"/>
       <c r="C24" s="251"/>
       <c r="D24" s="304"/>
-      <c r="E24" s="325">
+      <c r="E24" s="325" t="str">
         <f>구매리스트!B7</f>
-        <v>45898</v>
+        <v>0</v>
       </c>
       <c r="F24" s="251"/>
       <c r="G24" s="304"/>
@@ -10719,9 +10719,9 @@
           </r>
         </is>
       </c>
-      <c r="K33" s="219">
+      <c r="K33" s="219" t="str">
         <f>E24</f>
-        <v>45898</v>
+        <v>0</v>
       </c>
       <c r="O33" s="77"/>
     </row>
@@ -11283,7 +11283,7 @@
       <c r="F2" s="251"/>
       <c r="G2" s="128" t="str">
         <f>구매리스트!B12</f>
-        <v>RORO 2-6_3</v>
+        <v>0</v>
       </c>
       <c r="H2" s="345" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="G3" s="129" t="str">
         <f>구매리스트!B12</f>
-        <v>RORO 2-6_3</v>
+        <v>0</v>
       </c>
       <c r="H3" s="273"/>
       <c r="I3" s="254"/>
@@ -11391,12 +11391,7 @@
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
       <c r="A9" s="350" t="str">
         <f>구매리스트!B14</f>
-        <v>VIA AUTO
-811881897
-MAGJISTRALJA FERIZAJ PRISHTINEPN,PRELEZ I JERLIVE, 70000,
-FERIZAJ, KOSOVO
-EMAIL: INFO@VIA AUTO-KS.COM
-+38348507024</v>
+        <v>0</v>
       </c>
       <c r="D9" s="263"/>
       <c r="E9" s="235" t="inlineStr">
@@ -11410,7 +11405,7 @@
       <c r="G9" s="251"/>
       <c r="H9" s="251"/>
       <c r="I9" s="252"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11440,11 +11435,11 @@
       <c r="D11" s="254"/>
       <c r="E11" s="227" t="str">
         <f>구매리스트!B3</f>
-        <v>850942</v>
+        <v>0</v>
       </c>
       <c r="I11" s="53" t="str">
         <f>구매리스트!D11</f>
-        <v> </v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
@@ -11531,12 +11526,12 @@
     <row r="16" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A16" s="232" t="str">
         <f>구매리스트!B10</f>
-        <v>INCHOEN, KOREA</v>
+        <v>0</v>
       </c>
       <c r="B16" s="253"/>
       <c r="C16" s="352" t="str">
         <f>구매리스트!D10</f>
-        <v>DURRESS,  ALBANIA</v>
+        <v>0</v>
       </c>
       <c r="D16" s="254"/>
       <c r="E16" s="353" t="inlineStr">
@@ -11567,7 +11562,7 @@
       <c r="D17" s="252"/>
       <c r="E17" s="354" t="str">
         <f>구매리스트!D12</f>
-        <v>RORO</v>
+        <v>0</v>
       </c>
       <c r="F17" s="251"/>
       <c r="G17" s="251"/>
@@ -11577,12 +11572,12 @@
     <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A18" s="352" t="str">
         <f>구매리스트!B11</f>
-        <v> MV HAE SHIN V.2509</v>
+        <v>0</v>
       </c>
       <c r="B18" s="254"/>
       <c r="C18" s="355" t="str">
         <f>구매리스트!D11</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="D18" s="254"/>
       <c r="E18" s="273"/>
@@ -11715,35 +11710,35 @@
       </c>
       <c r="B22" s="123" t="str">
         <f>구매리스트!B5</f>
-        <v>BMW 520d xDrive</v>
-      </c>
-      <c r="C22" s="124">
+        <v>0</v>
+      </c>
+      <c r="C22" s="124" t="str">
         <f>구매리스트!D6</f>
-        <v>2017</v>
+        <v>0</v>
       </c>
       <c r="D22" s="125" t="str">
         <f>구매리스트!D5</f>
-        <v>WBAJC5105HG850942</v>
+        <v>0</v>
       </c>
       <c r="E22" s="362">
         <v>1</v>
       </c>
       <c r="F22" s="256"/>
-      <c r="G22" s="126">
+      <c r="G22" s="126" t="str">
         <f>구매리스트!B15</f>
-        <v>14730</v>
-      </c>
-      <c r="H22" s="126">
+        <v>0</v>
+      </c>
+      <c r="H22" s="126" t="str">
         <f>SUM(G22)</f>
-        <v>14730</v>
-      </c>
-      <c r="I22" s="127">
+        <v>0</v>
+      </c>
+      <c r="I22" s="127" t="str">
         <f>구매리스트!D15</f>
-        <v>1670</v>
-      </c>
-      <c r="J22" s="23">
+        <v>0</v>
+      </c>
+      <c r="J22" s="23" t="str">
         <f>SUM(H22:I22)</f>
-        <v>16400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
@@ -12068,9 +12063,9 @@
       <c r="E32" s="371"/>
       <c r="F32" s="234"/>
       <c r="G32" s="234"/>
-      <c r="H32" s="228">
+      <c r="H32" s="228" t="str">
         <f>SUM(H22:I22,H24:I24,H26:I26,H28:I28,H30:I30)</f>
-        <v>16400</v>
+        <v>0</v>
       </c>
       <c r="I32" s="372"/>
       <c r="J32" s="18"/>
@@ -12314,7 +12309,7 @@
       <c r="F2" s="251"/>
       <c r="G2" s="128" t="str">
         <f>차량인보이스!G2</f>
-        <v>RORO 2-6_3</v>
+        <v>0</v>
       </c>
       <c r="H2" s="345" t="inlineStr">
         <is>
@@ -12347,7 +12342,7 @@
       </c>
       <c r="G3" s="129" t="str">
         <f>차량인보이스!G3</f>
-        <v>RORO 2-6_3</v>
+        <v>0</v>
       </c>
       <c r="H3" s="273"/>
       <c r="I3" s="254"/>
@@ -12422,12 +12417,7 @@
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
       <c r="A9" s="373" t="str">
         <f>차량인보이스!A9</f>
-        <v>VIA AUTO
-811881897
-MAGJISTRALJA FERIZAJ PRISHTINEPN,PRELEZ I JERLIVE, 70000,
-FERIZAJ, KOSOVO
-EMAIL: INFO@VIA AUTO-KS.COM
-+38348507024</v>
+        <v>0</v>
       </c>
       <c r="D9" s="263"/>
       <c r="E9" s="235" t="inlineStr">
@@ -12441,7 +12431,7 @@
       <c r="G9" s="251"/>
       <c r="H9" s="251"/>
       <c r="I9" s="252"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="246" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12471,11 +12461,11 @@
       <c r="D11" s="254"/>
       <c r="E11" s="227" t="str">
         <f>구매리스트!B3</f>
-        <v>850942</v>
+        <v>0</v>
       </c>
       <c r="I11" s="53" t="str">
         <f>구매리스트!D11</f>
-        <v> </v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
@@ -12562,12 +12552,12 @@
     <row r="16" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A16" s="232" t="str">
         <f>구매리스트!B10</f>
-        <v>INCHOEN, KOREA</v>
+        <v>0</v>
       </c>
       <c r="B16" s="253"/>
       <c r="C16" s="352" t="str">
         <f>구매리스트!D10</f>
-        <v>DURRESS,  ALBANIA</v>
+        <v>0</v>
       </c>
       <c r="D16" s="254"/>
       <c r="E16" s="353" t="inlineStr">
@@ -12598,7 +12588,7 @@
       <c r="D17" s="252"/>
       <c r="E17" s="354" t="str">
         <f>차량인보이스!E17</f>
-        <v>RORO</v>
+        <v>0</v>
       </c>
       <c r="F17" s="251"/>
       <c r="G17" s="251"/>
@@ -12608,12 +12598,12 @@
     <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A18" s="352" t="str">
         <f>구매리스트!B11</f>
-        <v> MV HAE SHIN V.2509</v>
+        <v>0</v>
       </c>
       <c r="B18" s="254"/>
       <c r="C18" s="355" t="str">
         <f>구매리스트!D11</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="D18" s="254"/>
       <c r="E18" s="273"/>
@@ -12747,19 +12737,19 @@
       </c>
       <c r="B22" s="123" t="str">
         <f>차량인보이스!B22</f>
-        <v>BMW 520d xDrive</v>
-      </c>
-      <c r="C22" s="124">
+        <v>0</v>
+      </c>
+      <c r="C22" s="124" t="str">
         <f>구매리스트!D6</f>
-        <v>2017</v>
+        <v>0</v>
       </c>
       <c r="D22" s="125" t="str">
         <f>차량인보이스!D22</f>
-        <v>WBAJC5105HG850942</v>
-      </c>
-      <c r="E22" s="362">
+        <v>0</v>
+      </c>
+      <c r="E22" s="362" t="str">
         <f>차량인보이스!E22</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="256"/>
       <c r="G22" s="374" t="inlineStr">
@@ -12776,9 +12766,9 @@
           </r>
         </is>
       </c>
-      <c r="I22" s="130">
+      <c r="I22" s="130" t="str">
         <f>구매리스트!I8</f>
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="J22" s="363" t="inlineStr">
         <is>
@@ -13122,9 +13112,9 @@
       <c r="E32" s="371"/>
       <c r="F32" s="236"/>
       <c r="G32" s="236"/>
-      <c r="H32" s="237">
+      <c r="H32" s="237" t="str">
         <f>SUM(I22,I24,I26,I28,I30)</f>
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="I32" s="372"/>
       <c r="J32" s="18"/>
@@ -13360,7 +13350,7 @@
       </c>
       <c r="F3" s="375" t="str">
         <f>구매리스트!D11</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="G3" s="376"/>
     </row>
@@ -13378,7 +13368,7 @@
       </c>
       <c r="F4" s="377" t="str">
         <f>구매리스트!B3</f>
-        <v>850942</v>
+        <v>0</v>
       </c>
       <c r="G4" s="378"/>
     </row>
@@ -13394,7 +13384,7 @@
       </c>
       <c r="F5" s="379" t="str">
         <f>구매리스트!D14</f>
-        <v>VIA AUTO</v>
+        <v>0</v>
       </c>
       <c r="G5" s="378"/>
     </row>
@@ -13464,9 +13454,9 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="383">
+      <c r="F11" s="383" t="str">
         <f>F31</f>
-        <v>16400</v>
+        <v>0</v>
       </c>
       <c r="G11" s="378"/>
     </row>
@@ -13479,9 +13469,9 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="383">
+      <c r="F12" s="383" t="str">
         <f>F31</f>
-        <v>16400</v>
+        <v>0</v>
       </c>
       <c r="G12" s="378"/>
     </row>
@@ -13496,7 +13486,7 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="384">
+      <c r="F13" s="384" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
@@ -13675,24 +13665,24 @@
     <row r="21" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A21" s="133" t="str">
         <f>구매리스트!B3</f>
-        <v>850942</v>
+        <v>0</v>
       </c>
       <c r="B21" s="131" t="str">
         <f>구매리스트!B5</f>
-        <v>BMW 520d xDrive</v>
+        <v>0</v>
       </c>
       <c r="C21" s="132" t="str">
         <f>구매리스트!D5</f>
-        <v>WBAJC5105HG850942</v>
-      </c>
-      <c r="D21" s="132">
+        <v>0</v>
+      </c>
+      <c r="D21" s="132" t="str">
         <f>구매리스트!D6</f>
-        <v>2017</v>
+        <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="392">
+      <c r="F21" s="392" t="str">
         <f>차량인보이스!H22</f>
-        <v>14730</v>
+        <v>0</v>
       </c>
       <c r="G21" s="388"/>
     </row>
@@ -13762,9 +13752,9 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="394">
+      <c r="F28" s="394" t="str">
         <f>SUM(F21:G27)</f>
-        <v>14730</v>
+        <v>0</v>
       </c>
       <c r="G28" s="388"/>
     </row>
@@ -13780,9 +13770,9 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="394">
+      <c r="F29" s="394" t="str">
         <f>차량인보이스!I22</f>
-        <v>1670</v>
+        <v>0</v>
       </c>
       <c r="G29" s="388"/>
     </row>
@@ -13807,9 +13797,9 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="394">
+      <c r="F31" s="394" t="str">
         <f>SUM(F28:G29)</f>
-        <v>16400</v>
+        <v>0</v>
       </c>
       <c r="G31" s="388"/>
     </row>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="377">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -326,11 +326,6 @@
   <si>
     <r>
       <t xml:space="preserve">NAME</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">VIA AUTO</t>
     </r>
   </si>
   <si>
@@ -6161,12 +6156,9 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="118" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">VIA AUTO</t>
-          </r>
-        </is>
+      <c r="D14" s="118" t="str">
+        <f>B14</f>
+        <v>0</v>
       </c>
       <c r="E14" s="100"/>
       <c r="F14" s="100"/>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="379">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -555,6 +555,9 @@
     </r>
   </si>
   <si>
+    <t>대　한　민　국</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">1.제  원 </t>
     </r>
@@ -979,6 +982,9 @@
     <r>
       <t xml:space="preserve">※ Note: In the case of an electric vehicle or hydrogen fuel cell vehicle, the 'prime motor type' in column ⑦ refers to the 'drive motor type</t>
     </r>
+  </si>
+  <si>
+    <t>Republic of Korea</t>
   </si>
   <si>
     <r>
@@ -1963,7 +1969,7 @@
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="74">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -2373,15 +2379,6 @@
       <name val="Malgun Gothic"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="22"/>
-      <color rgb="FF000000"/>
-      <name val="HY견명조"/>
-    </font>
-    <font>
       <b val="0"/>
       <i val="0"/>
       <strike val="0"/>
@@ -2628,6 +2625,34 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Impact"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="HY견명조"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="HY견명조"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -3499,7 +3524,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="397">
+  <cellXfs count="399">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -3968,16 +3993,13 @@
     <xf xfId="0" fontId="4" numFmtId="170" fillId="11" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="4"/>
     </xf>
-    <xf xfId="0" fontId="44" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="11" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="45" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="44" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -3992,10 +4014,10 @@
     <xf xfId="0" fontId="41" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="45" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4004,7 +4026,7 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="165" fillId="11" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
@@ -4013,16 +4035,16 @@
     <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="16" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="45" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="44" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4091,7 +4113,7 @@
     <xf xfId="0" fontId="35" numFmtId="0" fillId="0" borderId="34" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="48" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="38" numFmtId="0" fillId="7" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4103,7 +4125,7 @@
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="26" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="49" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="48" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="25" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4112,7 +4134,7 @@
     <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="21" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false" indent="1"/>
     </xf>
-    <xf xfId="0" fontId="50" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="49" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4160,7 +4182,7 @@
     <xf xfId="0" fontId="37" numFmtId="171" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
     </xf>
-    <xf xfId="0" fontId="51" numFmtId="0" fillId="7" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="50" numFmtId="0" fillId="7" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="35" numFmtId="0" fillId="0" borderId="16" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4181,7 +4203,7 @@
     <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="52" numFmtId="168" fillId="11" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="51" numFmtId="168" fillId="11" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="14" numFmtId="167" fillId="0" borderId="42" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4208,10 +4230,10 @@
     <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="53" numFmtId="0" fillId="0" borderId="43" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="52" numFmtId="0" fillId="0" borderId="43" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="53" numFmtId="3" fillId="0" borderId="42" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="52" numFmtId="3" fillId="0" borderId="42" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
     </xf>
     <xf xfId="0" fontId="18" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -4226,13 +4248,13 @@
     <xf xfId="0" fontId="19" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="54" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="53" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="55" numFmtId="0" fillId="12" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="54" numFmtId="0" fillId="12" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="56" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="55" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="18" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -4250,298 +4272,298 @@
     <xf xfId="0" fontId="39" numFmtId="172" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="56" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="16" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="24" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="5" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="49" fillId="11" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="3"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="170" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="170" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="5"/>
+    </xf>
+    <xf xfId="0" fontId="38" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="11" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="29" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="49" fillId="11" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="49" fillId="11" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="45" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
     <xf xfId="0" fontId="57" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="58" numFmtId="173" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="59" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="60" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="15" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="60" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="61" numFmtId="170" fillId="7" borderId="17" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="45" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="36" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="37" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="21" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="31" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="31" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="20" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="50" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="36" numFmtId="14" fillId="11" borderId="51" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="36" numFmtId="0" fillId="0" borderId="51" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="52" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="38" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="53" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="16" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="24" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="54" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="40" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="5" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="49" fillId="11" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="3"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="170" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="170" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="5"/>
-    </xf>
-    <xf xfId="0" fontId="38" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="11" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="29" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="49" fillId="11" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="49" fillId="11" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="58" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="59" numFmtId="173" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="60" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="61" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="15" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="61" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="62" numFmtId="170" fillId="7" borderId="17" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="45" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="36" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="21" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="37" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="21" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="35" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="32" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="31" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="31" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="55" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="20" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="50" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="36" numFmtId="14" fillId="11" borderId="51" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="36" numFmtId="0" fillId="0" borderId="51" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="52" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="38" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="53" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="16" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="54" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="40" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="21" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="37" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="35" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="32" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="55" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="63" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="62" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="64" numFmtId="165" fillId="0" borderId="8" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="63" numFmtId="165" fillId="0" borderId="8" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="6" numFmtId="49" fillId="0" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false" indent="1"/>
     </xf>
-    <xf xfId="0" fontId="65" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="64" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4550,7 +4572,7 @@
     <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="53" numFmtId="49" fillId="11" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="52" numFmtId="49" fillId="11" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false" indent="1"/>
     </xf>
     <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4559,10 +4581,10 @@
     <xf xfId="0" fontId="14" numFmtId="0" fillId="11" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="66" numFmtId="49" fillId="0" borderId="44" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="65" numFmtId="49" fillId="0" borderId="44" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="67" numFmtId="0" fillId="11" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="66" numFmtId="0" fillId="11" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="14" numFmtId="165" fillId="0" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4619,7 +4641,7 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="42" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="53" numFmtId="168" fillId="11" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="52" numFmtId="168" fillId="11" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false" indent="1"/>
     </xf>
     <xf xfId="0" fontId="11" numFmtId="167" fillId="0" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4640,15 +4662,15 @@
     <xf xfId="0" fontId="20" numFmtId="168" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="67" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="68" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="69" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="70" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="20" numFmtId="167" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4658,7 +4680,7 @@
     <xf xfId="0" fontId="18" numFmtId="179" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="71" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="70" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="63" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4690,6 +4712,15 @@
     </xf>
     <xf xfId="0" fontId="20" numFmtId="167" fillId="6" borderId="64" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="71" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="72" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="73" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5566,22 +5597,22 @@
   <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="true" style="246"/>
-    <col min="2" max="2" width="22.25" customWidth="true" style="246"/>
-    <col min="3" max="3" width="10.5" customWidth="true" style="246"/>
-    <col min="4" max="4" width="21.125" customWidth="true" style="246"/>
-    <col min="5" max="5" width="3.125" customWidth="true" style="246"/>
-    <col min="6" max="6" width="11" customWidth="true" style="246"/>
-    <col min="7" max="7" width="20.125" customWidth="true" style="246"/>
-    <col min="8" max="8" width="9.25" customWidth="true" style="246"/>
-    <col min="9" max="9" width="21.75" customWidth="true" style="246"/>
-    <col min="10" max="10" width="20.5" customWidth="true" style="246"/>
-    <col min="11" max="11" width="10.375" customWidth="true" style="246"/>
-    <col min="12" max="12" width="11.75" customWidth="true" style="246"/>
+    <col min="1" max="1" width="10.375" customWidth="true" style="245"/>
+    <col min="2" max="2" width="22.25" customWidth="true" style="245"/>
+    <col min="3" max="3" width="10.5" customWidth="true" style="245"/>
+    <col min="4" max="4" width="21.125" customWidth="true" style="245"/>
+    <col min="5" max="5" width="3.125" customWidth="true" style="245"/>
+    <col min="6" max="6" width="11" customWidth="true" style="245"/>
+    <col min="7" max="7" width="20.125" customWidth="true" style="245"/>
+    <col min="8" max="8" width="9.25" customWidth="true" style="245"/>
+    <col min="9" max="9" width="21.75" customWidth="true" style="245"/>
+    <col min="10" max="10" width="20.5" customWidth="true" style="245"/>
+    <col min="11" max="11" width="10.375" customWidth="true" style="245"/>
+    <col min="12" max="12" width="11.75" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="246" customFormat="1"/>
-    <row r="2" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
+    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="245" customFormat="1"/>
+    <row r="2" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A2" s="105" t="inlineStr">
         <is>
           <r>
@@ -5597,7 +5628,7 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
+    <row r="3" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A3" s="103" t="inlineStr">
         <is>
           <r>
@@ -5639,7 +5670,7 @@
         <v>45875</v>
       </c>
     </row>
-    <row r="4" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="4" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A4" s="103" t="inlineStr">
         <is>
           <r>
@@ -5698,7 +5729,7 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="5" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A5" s="103" t="inlineStr">
         <is>
           <r>
@@ -5757,7 +5788,7 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="6" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A6" s="103" t="inlineStr">
         <is>
           <r>
@@ -5805,7 +5836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="7" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A7" s="103" t="inlineStr">
         <is>
           <r>
@@ -5848,7 +5879,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="8" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="8" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A8" s="103" t="inlineStr">
         <is>
           <r>
@@ -5891,7 +5922,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="9" spans="1:12" customHeight="1" ht="22.5" s="246" customFormat="1">
+    <row r="9" spans="1:12" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A9" s="105" t="inlineStr">
         <is>
           <r>
@@ -5932,7 +5963,7 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="10" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A10" s="103" t="inlineStr">
         <is>
           <r>
@@ -5987,7 +6018,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="11" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="11" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A11" s="103" t="inlineStr">
         <is>
           <r>
@@ -6042,7 +6073,7 @@
         <v>46504</v>
       </c>
     </row>
-    <row r="12" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="12" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A12" s="103" t="inlineStr">
         <is>
           <r>
@@ -6097,7 +6128,7 @@
         <v>163268</v>
       </c>
     </row>
-    <row r="13" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="13" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A13" s="105" t="inlineStr">
         <is>
           <r>
@@ -6123,13 +6154,13 @@
           </r>
         </is>
       </c>
-      <c r="H13" s="247"/>
+      <c r="H13" s="246"/>
       <c r="I13" s="113" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" customHeight="1" ht="120.75" s="246" customFormat="1">
+    <row r="14" spans="1:12" customHeight="1" ht="120.75" s="245" customFormat="1">
       <c r="A14" s="103" t="inlineStr">
         <is>
           <r>
@@ -6164,7 +6195,7 @@
       <c r="F14" s="100"/>
       <c r="G14" s="100"/>
     </row>
-    <row r="15" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="15" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A15" s="103" t="inlineStr">
         <is>
           <r>
@@ -6172,7 +6203,7 @@
           </r>
         </is>
       </c>
-      <c r="B15" s="248">
+      <c r="B15" s="247">
         <v>14730</v>
       </c>
       <c r="C15" s="103" t="inlineStr">
@@ -6182,25 +6213,25 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="248">
+      <c r="D15" s="247">
         <v>1670</v>
       </c>
       <c r="E15" s="100"/>
       <c r="F15" s="100"/>
-      <c r="G15" s="249" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I15" s="246" t="str">
+      <c r="G15" s="248" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I15" s="245" t="str">
         <f t="array" ref="I15" aca="1" ca="1">_xlfn.TEXTJOIN(",",,
  _xlfn.UNIQUE(_xlfn.IFNA(INDEX({"GASOLIN","DIESEL","LPG"},
  MATCH(G15,{"휘발유","경유","LPG"},0)),""),1))</f>
       </c>
     </row>
-    <row r="16" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
+    <row r="16" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A16" s="100"/>
       <c r="B16" s="100"/>
       <c r="C16" s="103" t="inlineStr">
@@ -6217,7 +6248,7 @@
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
-      <c r="I16" s="246" t="inlineStr">
+      <c r="I16" s="245" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -6585,22 +6616,22 @@
   <dimension ref="A1:T47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="3.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="3.5" customWidth="true" style="246"/>
-    <col min="3" max="3" width="11.125" customWidth="true" style="246"/>
-    <col min="4" max="4" width="4.125" customWidth="true" style="246"/>
-    <col min="5" max="5" width="4.125" customWidth="true" style="246"/>
-    <col min="6" max="6" width="4.75" customWidth="true" style="246"/>
-    <col min="7" max="7" width="3.25" customWidth="true" style="246"/>
-    <col min="8" max="8" width="11.625" customWidth="true" style="246"/>
-    <col min="9" max="9" width="8.25" customWidth="true" style="246"/>
-    <col min="10" max="10" width="4.875" customWidth="true" style="246"/>
-    <col min="11" max="11" width="2.125" customWidth="true" style="246"/>
-    <col min="12" max="12" width="10.875" customWidth="true" style="246"/>
-    <col min="13" max="13" width="10.125" customWidth="true" style="246"/>
-    <col min="14" max="14" width="9.5" customWidth="true" style="246"/>
-    <col min="16" max="16" width="8.125" customWidth="true" style="246"/>
-    <col min="17" max="17" width="8.25" customWidth="true" style="246"/>
+    <col min="1" max="1" width="3.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="3.5" customWidth="true" style="245"/>
+    <col min="3" max="3" width="11.125" customWidth="true" style="245"/>
+    <col min="4" max="4" width="4.125" customWidth="true" style="245"/>
+    <col min="5" max="5" width="4.125" customWidth="true" style="245"/>
+    <col min="6" max="6" width="4.75" customWidth="true" style="245"/>
+    <col min="7" max="7" width="3.25" customWidth="true" style="245"/>
+    <col min="8" max="8" width="11.625" customWidth="true" style="245"/>
+    <col min="9" max="9" width="8.25" customWidth="true" style="245"/>
+    <col min="10" max="10" width="4.875" customWidth="true" style="245"/>
+    <col min="11" max="11" width="2.125" customWidth="true" style="245"/>
+    <col min="12" max="12" width="10.875" customWidth="true" style="245"/>
+    <col min="13" max="13" width="10.125" customWidth="true" style="245"/>
+    <col min="14" max="14" width="9.5" customWidth="true" style="245"/>
+    <col min="16" max="16" width="8.125" customWidth="true" style="245"/>
+    <col min="17" max="17" width="8.25" customWidth="true" style="245"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -6634,32 +6665,32 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:20" customHeight="1" ht="60" s="246" customFormat="1">
-      <c r="A2" s="250" t="inlineStr">
+    <row r="2" spans="1:20" customHeight="1" ht="60" s="245" customFormat="1">
+      <c r="A2" s="249" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자  동  차  등  록  증</t>
           </r>
         </is>
       </c>
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="251"/>
-      <c r="O2" s="251"/>
-      <c r="P2" s="251"/>
-      <c r="Q2" s="252"/>
-    </row>
-    <row r="3" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="250"/>
+      <c r="E2" s="250"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="250"/>
+      <c r="J2" s="250"/>
+      <c r="K2" s="250"/>
+      <c r="L2" s="250"/>
+      <c r="M2" s="250"/>
+      <c r="N2" s="250"/>
+      <c r="O2" s="250"/>
+      <c r="P2" s="250"/>
+      <c r="Q2" s="251"/>
+    </row>
+    <row r="3" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6703,10 @@
         <f>구매리스트!G3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="252"/>
       <c r="H3" s="17" t="inlineStr">
         <is>
           <r>
@@ -6704,10 +6735,10 @@
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="254"/>
-    </row>
-    <row r="4" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="P3" s="252"/>
+      <c r="Q3" s="253"/>
+    </row>
+    <row r="4" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A4" s="135" t="inlineStr">
         <is>
           <r>
@@ -6715,17 +6746,17 @@
           </r>
         </is>
       </c>
-      <c r="B4" s="255"/>
-      <c r="C4" s="255"/>
-      <c r="D4" s="255"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="151" t="str">
         <f>구매리스트!B4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="256"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="255"/>
       <c r="J4" s="136" t="inlineStr">
         <is>
           <r>
@@ -6733,13 +6764,13 @@
           </r>
         </is>
       </c>
-      <c r="K4" s="255"/>
-      <c r="L4" s="256"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="255"/>
       <c r="M4" s="151" t="str">
         <f>구매리스트!G6</f>
         <v>0</v>
       </c>
-      <c r="N4" s="256"/>
+      <c r="N4" s="255"/>
       <c r="O4" s="136" t="inlineStr">
         <is>
           <r>
@@ -6754,9 +6785,9 @@
           </r>
         </is>
       </c>
-      <c r="Q4" s="256"/>
-    </row>
-    <row r="5" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="Q4" s="255"/>
+    </row>
+    <row r="5" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A5" s="136" t="inlineStr">
         <is>
           <r>
@@ -6764,17 +6795,17 @@
           </r>
         </is>
       </c>
-      <c r="B5" s="255"/>
-      <c r="C5" s="255"/>
-      <c r="D5" s="256"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="255"/>
       <c r="E5" s="151" t="str">
         <f>구매리스트!B5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="256"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="255"/>
       <c r="J5" s="136" t="inlineStr">
         <is>
           <r>
@@ -6782,21 +6813,21 @@
           </r>
         </is>
       </c>
-      <c r="K5" s="255"/>
-      <c r="L5" s="256"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="255"/>
       <c r="M5" s="134" t="str">
         <f>구매리스트!G4</f>
         <v>0</v>
       </c>
-      <c r="N5" s="255"/>
-      <c r="O5" s="255"/>
-      <c r="P5" s="257" t="str">
+      <c r="N5" s="254"/>
+      <c r="O5" s="254"/>
+      <c r="P5" s="256" t="str">
         <f>구매리스트!I5</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="256"/>
-    </row>
-    <row r="6" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="Q5" s="255"/>
+    </row>
+    <row r="6" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A6" s="136" t="inlineStr">
         <is>
           <r>
@@ -6804,17 +6835,17 @@
           </r>
         </is>
       </c>
-      <c r="B6" s="255"/>
-      <c r="C6" s="255"/>
-      <c r="D6" s="256"/>
+      <c r="B6" s="254"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="255"/>
       <c r="E6" s="151" t="str">
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="F6" s="255"/>
-      <c r="G6" s="255"/>
-      <c r="H6" s="255"/>
-      <c r="I6" s="256"/>
+      <c r="F6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="254"/>
+      <c r="I6" s="255"/>
       <c r="J6" s="136" t="inlineStr">
         <is>
           <r>
@@ -6822,18 +6853,18 @@
           </r>
         </is>
       </c>
-      <c r="K6" s="255"/>
-      <c r="L6" s="256"/>
+      <c r="K6" s="254"/>
+      <c r="L6" s="255"/>
       <c r="M6" s="151" t="str">
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
-      <c r="N6" s="255"/>
-      <c r="O6" s="255"/>
-      <c r="P6" s="255"/>
-      <c r="Q6" s="256"/>
-    </row>
-    <row r="7" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="N6" s="254"/>
+      <c r="O6" s="254"/>
+      <c r="P6" s="254"/>
+      <c r="Q6" s="255"/>
+    </row>
+    <row r="7" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A7" s="136" t="inlineStr">
         <is>
           <r>
@@ -6841,38 +6872,38 @@
           </r>
         </is>
       </c>
-      <c r="B7" s="255"/>
-      <c r="C7" s="255"/>
-      <c r="D7" s="256"/>
-      <c r="E7" s="258" t="inlineStr">
+      <c r="B7" s="254"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="257" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">경기도 시흥시 산기대학로 163, A동 328호(정왕동)</t>
           </r>
         </is>
       </c>
-      <c r="F7" s="255"/>
-      <c r="G7" s="255"/>
-      <c r="H7" s="255"/>
-      <c r="I7" s="255"/>
-      <c r="J7" s="255"/>
-      <c r="K7" s="255"/>
-      <c r="L7" s="255"/>
-      <c r="M7" s="255"/>
-      <c r="N7" s="255"/>
-      <c r="O7" s="255"/>
-      <c r="P7" s="255"/>
-      <c r="Q7" s="256"/>
-    </row>
-    <row r="8" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A8" s="259" t="inlineStr">
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="254"/>
+      <c r="O7" s="254"/>
+      <c r="P7" s="254"/>
+      <c r="Q7" s="255"/>
+    </row>
+    <row r="8" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A8" s="258" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">소유자</t>
           </r>
         </is>
       </c>
-      <c r="B8" s="256"/>
+      <c r="B8" s="255"/>
       <c r="C8" s="135" t="inlineStr">
         <is>
           <r>
@@ -6880,19 +6911,19 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="255"/>
-      <c r="E8" s="260" t="inlineStr">
+      <c r="D8" s="254"/>
+      <c r="E8" s="259" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">주식회사 싼카 (상품용)</t>
           </r>
         </is>
       </c>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="255"/>
-      <c r="I8" s="256"/>
-      <c r="J8" s="261" t="inlineStr">
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="254"/>
+      <c r="I8" s="255"/>
+      <c r="J8" s="260" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">      생   년   월   일
@@ -6900,28 +6931,28 @@
           </r>
         </is>
       </c>
-      <c r="K8" s="255"/>
-      <c r="L8" s="256"/>
-      <c r="M8" s="260" t="inlineStr">
+      <c r="K8" s="254"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="259" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">120111-0922270</t>
           </r>
         </is>
       </c>
-      <c r="N8" s="255"/>
-      <c r="O8" s="255"/>
-      <c r="P8" s="255"/>
-      <c r="Q8" s="256"/>
-      <c r="T8" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="1:20" customHeight="1" ht="6.75" s="246" customFormat="1">
+      <c r="N8" s="254"/>
+      <c r="O8" s="254"/>
+      <c r="P8" s="254"/>
+      <c r="Q8" s="255"/>
+      <c r="T8" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:20" customHeight="1" ht="6.75" s="245" customFormat="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6940,17 +6971,17 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:20" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A10" s="262" t="inlineStr">
+    <row r="10" spans="1:20" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A10" s="261" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">「자동차관리법」제8조에 따라 위와 같이 등록하였음을 증명합니다. </t>
           </r>
         </is>
       </c>
-      <c r="Q10" s="263"/>
-    </row>
-    <row r="11" spans="1:20" customHeight="1" ht="22.5" s="246" customFormat="1">
+      <c r="Q10" s="262"/>
+    </row>
+    <row r="11" spans="1:20" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A11" s="1"/>
       <c r="B11" s="154" t="inlineStr">
         <is>
@@ -6959,9 +6990,9 @@
           </r>
         </is>
       </c>
-      <c r="Q11" s="263"/>
-    </row>
-    <row r="12" spans="1:20" customHeight="1" ht="20.25" s="246" customFormat="1">
+      <c r="Q11" s="262"/>
+    </row>
+    <row r="12" spans="1:20" customHeight="1" ht="20.25" s="245" customFormat="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -6980,7 +7011,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:20" customHeight="1" ht="26.25" s="246" customFormat="1">
+    <row r="13" spans="1:20" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <r>
@@ -6988,7 +7019,7 @@
           </r>
         </is>
       </c>
-      <c r="B13" s="246" t="inlineStr">
+      <c r="B13" s="245" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -6999,11 +7030,11 @@
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
-      <c r="O13" s="246"/>
-      <c r="P13" s="264"/>
+      <c r="O13" s="245"/>
+      <c r="P13" s="263"/>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
+    <row r="14" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A14" s="4"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
@@ -7011,18 +7042,14 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:20" customHeight="1" ht="39" s="246" customFormat="1">
+    <row r="15" spans="1:20" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="156" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="Q15" s="263"/>
-    </row>
-    <row r="16" spans="1:20" customHeight="1" ht="9" s="246" customFormat="1">
+      <c r="J15" s="396" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="262"/>
+    </row>
+    <row r="16" spans="1:20" customHeight="1" ht="9" s="245" customFormat="1">
       <c r="A16" s="7"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -7041,54 +7068,54 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
     </row>
-    <row r="17" spans="1:20" customHeight="1" ht="8.25" s="246" customFormat="1">
+    <row r="17" spans="1:20" customHeight="1" ht="8.25" s="245" customFormat="1">
       <c r="A17" s="4"/>
-      <c r="B17" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I17" s="265"/>
-      <c r="J17" s="265"/>
-      <c r="K17" s="265"/>
-      <c r="L17" s="265"/>
-      <c r="M17" s="265"/>
-      <c r="N17" s="265"/>
+      <c r="B17" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="264"/>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:20" customHeight="1" ht="21.75" s="246" customFormat="1">
-      <c r="A18" s="266" t="inlineStr">
+    <row r="18" spans="1:20" customHeight="1" ht="21.75" s="245" customFormat="1">
+      <c r="A18" s="265" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1.제  원 </t>
           </r>
         </is>
       </c>
-      <c r="B18" s="255"/>
-      <c r="C18" s="255"/>
-      <c r="D18" s="255"/>
-      <c r="E18" s="255"/>
-      <c r="F18" s="255"/>
-      <c r="G18" s="255"/>
-      <c r="H18" s="255"/>
-      <c r="I18" s="255"/>
-      <c r="J18" s="256"/>
-      <c r="L18" s="267" t="inlineStr">
+      <c r="B18" s="254"/>
+      <c r="C18" s="254"/>
+      <c r="D18" s="254"/>
+      <c r="E18" s="254"/>
+      <c r="F18" s="254"/>
+      <c r="G18" s="254"/>
+      <c r="H18" s="254"/>
+      <c r="I18" s="254"/>
+      <c r="J18" s="255"/>
+      <c r="L18" s="266" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  4. 검사유효기간</t>
           </r>
         </is>
       </c>
-      <c r="M18" s="255"/>
-      <c r="N18" s="255"/>
-      <c r="O18" s="255"/>
-      <c r="P18" s="255"/>
-      <c r="Q18" s="256"/>
-    </row>
-    <row r="19" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="M18" s="254"/>
+      <c r="N18" s="254"/>
+      <c r="O18" s="254"/>
+      <c r="P18" s="254"/>
+      <c r="Q18" s="255"/>
+    </row>
+    <row r="19" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
         <is>
           <r>
@@ -7103,39 +7130,39 @@
           </r>
         </is>
       </c>
-      <c r="C19" s="251"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="251"/>
-      <c r="F19" s="268" t="str">
+      <c r="C19" s="250"/>
+      <c r="D19" s="250"/>
+      <c r="E19" s="250"/>
+      <c r="F19" s="267" t="str">
         <f>구매리스트!G5</f>
         <v>0</v>
       </c>
-      <c r="G19" s="251"/>
-      <c r="H19" s="251"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="252"/>
-      <c r="L19" s="166" t="inlineStr">
+      <c r="G19" s="250"/>
+      <c r="H19" s="250"/>
+      <c r="I19" s="250"/>
+      <c r="J19" s="251"/>
+      <c r="L19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">연월일</t>
           </r>
         </is>
       </c>
-      <c r="M19" s="166" t="inlineStr">
+      <c r="M19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">연월일</t>
           </r>
         </is>
       </c>
-      <c r="N19" s="166" t="inlineStr">
+      <c r="N19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  검    사</t>
           </r>
         </is>
       </c>
-      <c r="O19" s="166" t="inlineStr">
+      <c r="O19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">주  행</t>
@@ -7149,7 +7176,7 @@
           </r>
         </is>
       </c>
-      <c r="Q19" s="166" t="inlineStr">
+      <c r="Q19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">검  사</t>
@@ -7157,7 +7184,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="20" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
         <is>
           <r>
@@ -7172,50 +7199,50 @@
           </r>
         </is>
       </c>
-      <c r="C20" s="253"/>
-      <c r="D20" s="253"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="253"/>
-      <c r="G20" s="253"/>
-      <c r="H20" s="253"/>
-      <c r="I20" s="253"/>
-      <c r="J20" s="254"/>
-      <c r="L20" s="167" t="inlineStr">
+      <c r="C20" s="252"/>
+      <c r="D20" s="252"/>
+      <c r="E20" s="252"/>
+      <c r="F20" s="252"/>
+      <c r="G20" s="252"/>
+      <c r="H20" s="252"/>
+      <c r="I20" s="252"/>
+      <c r="J20" s="253"/>
+      <c r="L20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">부   터</t>
           </r>
         </is>
       </c>
-      <c r="M20" s="167" t="inlineStr">
+      <c r="M20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">까   지</t>
           </r>
         </is>
       </c>
-      <c r="N20" s="167" t="inlineStr">
+      <c r="N20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  시행장소</t>
           </r>
         </is>
       </c>
-      <c r="O20" s="167" t="inlineStr">
+      <c r="O20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">거  리</t>
           </r>
         </is>
       </c>
-      <c r="P20" s="175" t="inlineStr">
+      <c r="P20" s="174" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">임자확인</t>
           </r>
         </is>
       </c>
-      <c r="Q20" s="167" t="inlineStr">
+      <c r="Q20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">구  분</t>
@@ -7223,7 +7250,7 @@
         </is>
       </c>
     </row>
-    <row r="21" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="21" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
         <is>
           <r>
@@ -7238,12 +7265,12 @@
           </r>
         </is>
       </c>
-      <c r="C21" s="256"/>
-      <c r="D21" s="157" t="str">
+      <c r="C21" s="255"/>
+      <c r="D21" s="156" t="str">
         <f>구매리스트!G7</f>
         <v>0</v>
       </c>
-      <c r="E21" s="255"/>
+      <c r="E21" s="254"/>
       <c r="F21" s="16" t="inlineStr">
         <is>
           <r>
@@ -7292,7 +7319,7 @@
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
     </row>
-    <row r="22" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="22" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
         <is>
           <r>
@@ -7307,12 +7334,12 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="256"/>
+      <c r="C22" s="255"/>
       <c r="D22" s="141" t="str">
         <f>구매리스트!G8</f>
         <v>0</v>
       </c>
-      <c r="E22" s="255"/>
+      <c r="E22" s="254"/>
       <c r="F22" s="16" t="inlineStr">
         <is>
           <r>
@@ -7352,7 +7379,7 @@
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
     </row>
-    <row r="23" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="23" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
         <is>
           <r>
@@ -7367,12 +7394,12 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="256"/>
+      <c r="C23" s="255"/>
       <c r="D23" s="141" t="str">
         <f>구매리스트!G9</f>
         <v>0</v>
       </c>
-      <c r="E23" s="255"/>
+      <c r="E23" s="254"/>
       <c r="F23" s="16" t="inlineStr">
         <is>
           <r>
@@ -7411,8 +7438,8 @@
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
     </row>
-    <row r="24" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A24" s="269" t="inlineStr">
+    <row r="24" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A24" s="268" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑱</t>
@@ -7426,23 +7453,23 @@
           </r>
         </is>
       </c>
-      <c r="C24" s="252"/>
-      <c r="D24" s="270" t="str">
+      <c r="C24" s="251"/>
+      <c r="D24" s="269" t="str">
         <f>구매리스트!G10</f>
         <v>0</v>
       </c>
-      <c r="E24" s="251"/>
-      <c r="F24" s="251"/>
-      <c r="G24" s="251"/>
-      <c r="H24" s="251"/>
-      <c r="I24" s="271" t="inlineStr">
+      <c r="E24" s="250"/>
+      <c r="F24" s="250"/>
+      <c r="G24" s="250"/>
+      <c r="H24" s="250"/>
+      <c r="I24" s="270" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">cc,(Ah ,[Ah]</t>
           </r>
         </is>
       </c>
-      <c r="J24" s="252"/>
+      <c r="J24" s="251"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
@@ -7450,8 +7477,8 @@
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
     </row>
-    <row r="25" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A25" s="272"/>
+    <row r="25" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A25" s="271"/>
       <c r="B25" s="144" t="inlineStr">
         <is>
           <r>
@@ -7459,9 +7486,9 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="263"/>
-      <c r="D25" s="272"/>
-      <c r="J25" s="263"/>
+      <c r="C25" s="262"/>
+      <c r="D25" s="271"/>
+      <c r="J25" s="262"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -7469,17 +7496,17 @@
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
     </row>
-    <row r="26" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A26" s="273"/>
-      <c r="B26" s="253"/>
-      <c r="C26" s="254"/>
-      <c r="D26" s="273"/>
-      <c r="E26" s="253"/>
-      <c r="F26" s="253"/>
-      <c r="G26" s="253"/>
-      <c r="H26" s="253"/>
-      <c r="I26" s="253"/>
-      <c r="J26" s="254"/>
+    <row r="26" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A26" s="272"/>
+      <c r="B26" s="252"/>
+      <c r="C26" s="253"/>
+      <c r="D26" s="272"/>
+      <c r="E26" s="252"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="252"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="253"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
@@ -7487,7 +7514,7 @@
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
     </row>
-    <row r="27" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="27" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
         <is>
           <r>
@@ -7502,14 +7529,14 @@
           </r>
         </is>
       </c>
-      <c r="C27" s="256"/>
+      <c r="C27" s="255"/>
       <c r="D27" s="141" t="str">
         <f>구매리스트!G11</f>
         <v>0</v>
       </c>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
       <c r="H27" s="140" t="inlineStr">
         <is>
           <r>
@@ -7517,8 +7544,8 @@
           </r>
         </is>
       </c>
-      <c r="I27" s="255"/>
-      <c r="J27" s="256"/>
+      <c r="I27" s="254"/>
+      <c r="J27" s="255"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
@@ -7526,7 +7553,7 @@
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
     </row>
-    <row r="28" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="28" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
         <is>
           <r>
@@ -7541,15 +7568,15 @@
           </r>
         </is>
       </c>
-      <c r="C28" s="252"/>
-      <c r="D28" s="274" t="str">
+      <c r="C28" s="251"/>
+      <c r="D28" s="273" t="str">
         <f>구매리스트!G12</f>
         <v>0</v>
       </c>
-      <c r="E28" s="251"/>
-      <c r="F28" s="251"/>
-      <c r="G28" s="251"/>
-      <c r="H28" s="251"/>
+      <c r="E28" s="250"/>
+      <c r="F28" s="250"/>
+      <c r="G28" s="250"/>
+      <c r="H28" s="250"/>
       <c r="I28" s="137" t="inlineStr">
         <is>
           <r>
@@ -7557,7 +7584,7 @@
           </r>
         </is>
       </c>
-      <c r="J28" s="252"/>
+      <c r="J28" s="251"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
@@ -7565,17 +7592,17 @@
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
     </row>
-    <row r="29" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A29" s="275" t="inlineStr">
+    <row r="29" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A29" s="274" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(구동축전지정격전압)</t>
           </r>
         </is>
       </c>
-      <c r="C29" s="263"/>
-      <c r="D29" s="272"/>
-      <c r="J29" s="263"/>
+      <c r="C29" s="262"/>
+      <c r="D29" s="271"/>
+      <c r="J29" s="262"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
@@ -7583,23 +7610,23 @@
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
     </row>
-    <row r="30" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A30" s="276" t="inlineStr">
+    <row r="30" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A30" s="275" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">[연료전지 최고출력]</t>
           </r>
         </is>
       </c>
-      <c r="B30" s="253"/>
-      <c r="C30" s="254"/>
-      <c r="D30" s="273"/>
-      <c r="E30" s="253"/>
-      <c r="F30" s="253"/>
-      <c r="G30" s="253"/>
-      <c r="H30" s="253"/>
-      <c r="I30" s="253"/>
-      <c r="J30" s="254"/>
+      <c r="B30" s="252"/>
+      <c r="C30" s="253"/>
+      <c r="D30" s="272"/>
+      <c r="E30" s="252"/>
+      <c r="F30" s="252"/>
+      <c r="G30" s="252"/>
+      <c r="H30" s="252"/>
+      <c r="I30" s="252"/>
+      <c r="J30" s="253"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
@@ -7607,7 +7634,7 @@
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="31" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
         <is>
           <r>
@@ -7615,33 +7642,33 @@
           </r>
         </is>
       </c>
-      <c r="B31" s="160" t="inlineStr">
+      <c r="B31" s="159" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">연료의종류 및 연료소비율</t>
           </r>
         </is>
       </c>
-      <c r="C31" s="256"/>
+      <c r="C31" s="255"/>
       <c r="D31" s="146" t="str">
         <f>구매리스트!G13</f>
         <v>0</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="254"/>
       <c r="F31" s="145" t="str">
         <f>구매리스트!H13</f>
         <v>0</v>
       </c>
-      <c r="G31" s="255"/>
-      <c r="H31" s="161" t="inlineStr">
+      <c r="G31" s="254"/>
+      <c r="H31" s="160" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">km/l,(km/kWh),[km/kg]</t>
           </r>
         </is>
       </c>
-      <c r="I31" s="255"/>
-      <c r="J31" s="256"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="255"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
@@ -7649,7 +7676,7 @@
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
     </row>
-    <row r="32" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="32" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
         <is>
           <r>
@@ -7657,23 +7684,23 @@
           </r>
         </is>
       </c>
-      <c r="B32" s="158" t="inlineStr">
+      <c r="B32" s="157" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">구동축전지 셀의제조사</t>
           </r>
         </is>
       </c>
-      <c r="C32" s="256"/>
-      <c r="D32" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E32" s="255"/>
-      <c r="F32" s="256"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E32" s="254"/>
+      <c r="F32" s="255"/>
       <c r="G32" s="59" t="inlineStr">
         <is>
           <r>
@@ -7688,14 +7715,14 @@
           </r>
         </is>
       </c>
-      <c r="I32" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J32" s="256"/>
+      <c r="I32" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J32" s="255"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
@@ -7703,7 +7730,7 @@
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
     </row>
-    <row r="33" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="33" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
         <is>
           <r>
@@ -7711,23 +7738,23 @@
           </r>
         </is>
       </c>
-      <c r="B33" s="159" t="inlineStr">
+      <c r="B33" s="158" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">구동축전지셀의주요원료</t>
           </r>
         </is>
       </c>
-      <c r="C33" s="256"/>
-      <c r="D33" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E33" s="255"/>
-      <c r="F33" s="256"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E33" s="254"/>
+      <c r="F33" s="255"/>
       <c r="G33" s="136" t="inlineStr">
         <is>
           <r>
@@ -7735,15 +7762,15 @@
           </r>
         </is>
       </c>
-      <c r="H33" s="256"/>
-      <c r="I33" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J33" s="256"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J33" s="255"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
@@ -7751,23 +7778,23 @@
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
     </row>
-    <row r="34" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A34" s="278" t="inlineStr">
+    <row r="34" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A34" s="277" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">유의사항 : ⑱~㉑에서 기재 단위는 사용연료의 종류가 전기인 자동차의 경우는 (),수소전기자동차의 경우는[]을 말합니다.「자동차관리법 시행규칙」별표1 제2회의 특수자동차의 경우 최대적재량은 피견인자동차를 연결하기위해 허용되는 최대수직하중을 말하며 견인능력과는무관합니다,㉒~㉔는 구동축전지를 갖춘 자동차(외부 전기공급원을 통해 충전할 수 없는 구조인 자동차는제외)의경우만 해당합니다.</t>
           </r>
         </is>
       </c>
-      <c r="B34" s="251"/>
-      <c r="C34" s="251"/>
-      <c r="D34" s="251"/>
-      <c r="E34" s="251"/>
-      <c r="F34" s="251"/>
-      <c r="G34" s="251"/>
-      <c r="H34" s="251"/>
-      <c r="I34" s="251"/>
-      <c r="J34" s="252"/>
+      <c r="B34" s="250"/>
+      <c r="C34" s="250"/>
+      <c r="D34" s="250"/>
+      <c r="E34" s="250"/>
+      <c r="F34" s="250"/>
+      <c r="G34" s="250"/>
+      <c r="H34" s="250"/>
+      <c r="I34" s="250"/>
+      <c r="J34" s="251"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
@@ -7775,9 +7802,9 @@
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
     </row>
-    <row r="35" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A35" s="272"/>
-      <c r="J35" s="263"/>
+    <row r="35" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A35" s="271"/>
+      <c r="J35" s="262"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
@@ -7785,9 +7812,9 @@
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
     </row>
-    <row r="36" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A36" s="272"/>
-      <c r="J36" s="263"/>
+    <row r="36" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A36" s="271"/>
+      <c r="J36" s="262"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
@@ -7795,17 +7822,17 @@
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
     </row>
-    <row r="37" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A37" s="273"/>
-      <c r="B37" s="253"/>
-      <c r="C37" s="253"/>
-      <c r="D37" s="253"/>
-      <c r="E37" s="253"/>
-      <c r="F37" s="253"/>
-      <c r="G37" s="253"/>
-      <c r="H37" s="253"/>
-      <c r="I37" s="253"/>
-      <c r="J37" s="254"/>
+    <row r="37" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A37" s="272"/>
+      <c r="B37" s="252"/>
+      <c r="C37" s="252"/>
+      <c r="D37" s="252"/>
+      <c r="E37" s="252"/>
+      <c r="F37" s="252"/>
+      <c r="G37" s="252"/>
+      <c r="H37" s="252"/>
+      <c r="I37" s="252"/>
+      <c r="J37" s="253"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
@@ -7813,79 +7840,79 @@
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
     </row>
-    <row r="38" spans="1:20" customHeight="1" ht="25.5" s="246" customFormat="1">
-      <c r="A38" s="173" t="inlineStr">
+    <row r="38" spans="1:20" customHeight="1" ht="25.5" s="245" customFormat="1">
+      <c r="A38" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2.등록번호판 교부 및 봉인</t>
           </r>
         </is>
       </c>
-      <c r="B38" s="255"/>
-      <c r="C38" s="255"/>
-      <c r="D38" s="255"/>
-      <c r="E38" s="255"/>
-      <c r="F38" s="255"/>
-      <c r="G38" s="255"/>
-      <c r="H38" s="255"/>
-      <c r="I38" s="255"/>
-      <c r="J38" s="256"/>
-      <c r="L38" s="279" t="inlineStr">
+      <c r="B38" s="254"/>
+      <c r="C38" s="254"/>
+      <c r="D38" s="254"/>
+      <c r="E38" s="254"/>
+      <c r="F38" s="254"/>
+      <c r="G38" s="254"/>
+      <c r="H38" s="254"/>
+      <c r="I38" s="254"/>
+      <c r="J38" s="255"/>
+      <c r="L38" s="278" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ 주의사항 :      ㉚ 항 첫째란에는 신규등록일을 적습니다.</t>
           </r>
         </is>
       </c>
-      <c r="M38" s="251"/>
-      <c r="N38" s="251"/>
-      <c r="O38" s="251"/>
-      <c r="P38" s="251"/>
-      <c r="Q38" s="252"/>
-    </row>
-    <row r="39" spans="1:20" customHeight="1" ht="25.5" s="246" customFormat="1">
-      <c r="A39" s="280" t="inlineStr">
+      <c r="M38" s="250"/>
+      <c r="N38" s="250"/>
+      <c r="O38" s="250"/>
+      <c r="P38" s="250"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:20" customHeight="1" ht="25.5" s="245" customFormat="1">
+      <c r="A39" s="279" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉕ 구분</t>
           </r>
         </is>
       </c>
-      <c r="B39" s="255"/>
-      <c r="C39" s="256"/>
-      <c r="D39" s="173" t="inlineStr">
+      <c r="B39" s="254"/>
+      <c r="C39" s="255"/>
+      <c r="D39" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> ㉖ 번호판발급일</t>
           </r>
         </is>
       </c>
-      <c r="E39" s="255"/>
-      <c r="F39" s="255"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="280" t="inlineStr">
+      <c r="E39" s="254"/>
+      <c r="F39" s="254"/>
+      <c r="G39" s="255"/>
+      <c r="H39" s="279" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉗ 발급대행자확인</t>
           </r>
         </is>
       </c>
-      <c r="I39" s="255"/>
-      <c r="J39" s="256"/>
-      <c r="L39" s="281" t="inlineStr">
+      <c r="I39" s="254"/>
+      <c r="J39" s="255"/>
+      <c r="L39" s="280" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">   비고</t>
           </r>
         </is>
       </c>
-      <c r="M39" s="251"/>
-      <c r="N39" s="251"/>
-      <c r="O39" s="251"/>
-      <c r="P39" s="251"/>
-      <c r="Q39" s="252"/>
-    </row>
-    <row r="40" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
+      <c r="M39" s="250"/>
+      <c r="N39" s="250"/>
+      <c r="O39" s="250"/>
+      <c r="P39" s="250"/>
+      <c r="Q39" s="251"/>
+    </row>
+    <row r="40" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
         <is>
           <r>
@@ -7893,7 +7920,7 @@
           </r>
         </is>
       </c>
-      <c r="B40" s="256"/>
+      <c r="B40" s="255"/>
       <c r="C40" s="136" t="inlineStr">
         <is>
           <r>
@@ -7901,8 +7928,8 @@
           </r>
         </is>
       </c>
-      <c r="D40" s="255"/>
-      <c r="E40" s="256"/>
+      <c r="D40" s="254"/>
+      <c r="E40" s="255"/>
       <c r="F40" s="136" t="inlineStr">
         <is>
           <r>
@@ -7910,7 +7937,7 @@
           </r>
         </is>
       </c>
-      <c r="G40" s="256"/>
+      <c r="G40" s="255"/>
       <c r="H40" s="136" t="inlineStr">
         <is>
           <r>
@@ -7918,12 +7945,12 @@
           </r>
         </is>
       </c>
-      <c r="I40" s="255"/>
-      <c r="J40" s="256"/>
+      <c r="I40" s="254"/>
+      <c r="J40" s="255"/>
       <c r="L40" s="4"/>
       <c r="Q40" s="5"/>
     </row>
-    <row r="41" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="41" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
         <is>
           <r>
@@ -7931,7 +7958,7 @@
           </r>
         </is>
       </c>
-      <c r="B41" s="256"/>
+      <c r="B41" s="255"/>
       <c r="C41" s="136" t="inlineStr">
         <is>
           <r>
@@ -7939,8 +7966,8 @@
           </r>
         </is>
       </c>
-      <c r="D41" s="255"/>
-      <c r="E41" s="256"/>
+      <c r="D41" s="254"/>
+      <c r="E41" s="255"/>
       <c r="F41" s="136" t="inlineStr">
         <is>
           <r>
@@ -7948,7 +7975,7 @@
           </r>
         </is>
       </c>
-      <c r="G41" s="256"/>
+      <c r="G41" s="255"/>
       <c r="H41" s="136" t="inlineStr">
         <is>
           <r>
@@ -7956,10 +7983,10 @@
           </r>
         </is>
       </c>
-      <c r="I41" s="255"/>
-      <c r="J41" s="256"/>
+      <c r="I41" s="254"/>
+      <c r="J41" s="255"/>
       <c r="L41" s="4"/>
-      <c r="O41" s="246" t="inlineStr">
+      <c r="O41" s="245" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -7968,8 +7995,8 @@
       </c>
       <c r="Q41" s="5"/>
     </row>
-    <row r="42" spans="1:20" customHeight="1" ht="33" s="246" customFormat="1">
-      <c r="A42" s="267" t="inlineStr">
+    <row r="42" spans="1:20" customHeight="1" ht="33" s="245" customFormat="1">
+      <c r="A42" s="266" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3. 저당권등록사실(저당권등록의 내용은 자동차등록원부(을)를
@@ -7977,45 +8004,45 @@
           </r>
         </is>
       </c>
-      <c r="B42" s="255"/>
-      <c r="C42" s="255"/>
-      <c r="D42" s="255"/>
-      <c r="E42" s="255"/>
-      <c r="F42" s="255"/>
-      <c r="G42" s="255"/>
-      <c r="H42" s="255"/>
-      <c r="I42" s="255"/>
-      <c r="J42" s="256"/>
+      <c r="B42" s="254"/>
+      <c r="C42" s="254"/>
+      <c r="D42" s="254"/>
+      <c r="E42" s="254"/>
+      <c r="F42" s="254"/>
+      <c r="G42" s="254"/>
+      <c r="H42" s="254"/>
+      <c r="I42" s="254"/>
+      <c r="J42" s="255"/>
       <c r="L42" s="4"/>
       <c r="Q42" s="5"/>
     </row>
-    <row r="43" spans="1:20" customHeight="1" ht="22.5" s="246" customFormat="1">
-      <c r="A43" s="282" t="inlineStr">
+    <row r="43" spans="1:20" customHeight="1" ht="22.5" s="245" customFormat="1">
+      <c r="A43" s="281" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉘ 구분(설정 또는 말소)</t>
           </r>
         </is>
       </c>
-      <c r="B43" s="255"/>
-      <c r="C43" s="255"/>
-      <c r="D43" s="255"/>
-      <c r="E43" s="255"/>
-      <c r="F43" s="255"/>
-      <c r="G43" s="256"/>
-      <c r="H43" s="162" t="inlineStr">
+      <c r="B43" s="254"/>
+      <c r="C43" s="254"/>
+      <c r="D43" s="254"/>
+      <c r="E43" s="254"/>
+      <c r="F43" s="254"/>
+      <c r="G43" s="255"/>
+      <c r="H43" s="161" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉙ 날         짜</t>
           </r>
         </is>
       </c>
-      <c r="I43" s="255"/>
-      <c r="J43" s="256"/>
+      <c r="I43" s="254"/>
+      <c r="J43" s="255"/>
       <c r="L43" s="4"/>
       <c r="Q43" s="5"/>
     </row>
-    <row r="44" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="44" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
         <is>
           <r>
@@ -8023,12 +8050,12 @@
           </r>
         </is>
       </c>
-      <c r="B44" s="255"/>
-      <c r="C44" s="255"/>
-      <c r="D44" s="255"/>
-      <c r="E44" s="255"/>
-      <c r="F44" s="255"/>
-      <c r="G44" s="256"/>
+      <c r="B44" s="254"/>
+      <c r="C44" s="254"/>
+      <c r="D44" s="254"/>
+      <c r="E44" s="254"/>
+      <c r="F44" s="254"/>
+      <c r="G44" s="255"/>
       <c r="H44" s="136" t="inlineStr">
         <is>
           <r>
@@ -8036,12 +8063,12 @@
           </r>
         </is>
       </c>
-      <c r="I44" s="255"/>
-      <c r="J44" s="256"/>
+      <c r="I44" s="254"/>
+      <c r="J44" s="255"/>
       <c r="L44" s="4"/>
       <c r="Q44" s="5"/>
     </row>
-    <row r="45" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="45" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
         <is>
           <r>
@@ -8049,12 +8076,12 @@
           </r>
         </is>
       </c>
-      <c r="B45" s="255"/>
-      <c r="C45" s="255"/>
-      <c r="D45" s="255"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="255"/>
-      <c r="G45" s="256"/>
+      <c r="B45" s="254"/>
+      <c r="C45" s="254"/>
+      <c r="D45" s="254"/>
+      <c r="E45" s="254"/>
+      <c r="F45" s="254"/>
+      <c r="G45" s="255"/>
       <c r="H45" s="136" t="inlineStr">
         <is>
           <r>
@@ -8062,8 +8089,8 @@
           </r>
         </is>
       </c>
-      <c r="I45" s="255"/>
-      <c r="J45" s="256"/>
+      <c r="I45" s="254"/>
+      <c r="J45" s="255"/>
       <c r="K45" s="8"/>
       <c r="L45" s="7"/>
       <c r="M45" s="8"/>
@@ -8072,16 +8099,16 @@
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
     </row>
-    <row r="46" spans="1:20" customHeight="1" ht="6" s="246" customFormat="1"/>
-    <row r="47" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="G47" s="163" t="inlineStr">
+    <row r="46" spans="1:20" customHeight="1" ht="6" s="245" customFormat="1"/>
+    <row r="47" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="G47" s="162" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ 뒷면의 '유의사항'을 꼭 읽어보시기 바랍니다.</t>
           </r>
         </is>
       </c>
-      <c r="N47" s="164" t="inlineStr">
+      <c r="N47" s="163" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">210㎜ x 297㎜[백상지 또는 중질지 80g/㎡]</t>
@@ -8205,22 +8232,22 @@
   <dimension ref="A1:W47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="3.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="4.125" customWidth="true" style="246"/>
-    <col min="3" max="3" width="11.125" customWidth="true" style="246"/>
-    <col min="4" max="4" width="4.125" customWidth="true" style="246"/>
-    <col min="5" max="5" width="4.125" customWidth="true" style="246"/>
-    <col min="6" max="6" width="4.75" customWidth="true" style="246"/>
-    <col min="7" max="7" width="3.25" customWidth="true" style="246"/>
-    <col min="8" max="8" width="11.625" customWidth="true" style="246"/>
-    <col min="9" max="9" width="8.25" customWidth="true" style="246"/>
-    <col min="10" max="10" width="4.875" customWidth="true" style="246"/>
-    <col min="11" max="11" width="2.125" customWidth="true" style="246"/>
-    <col min="12" max="12" width="10.875" customWidth="true" style="246"/>
-    <col min="13" max="13" width="12.375" customWidth="true" style="246"/>
-    <col min="14" max="14" width="9.5" customWidth="true" style="246"/>
-    <col min="16" max="16" width="10.625" customWidth="true" style="246"/>
-    <col min="17" max="17" width="9.125" customWidth="true" style="246"/>
+    <col min="1" max="1" width="3.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="4.125" customWidth="true" style="245"/>
+    <col min="3" max="3" width="11.125" customWidth="true" style="245"/>
+    <col min="4" max="4" width="4.125" customWidth="true" style="245"/>
+    <col min="5" max="5" width="4.125" customWidth="true" style="245"/>
+    <col min="6" max="6" width="4.75" customWidth="true" style="245"/>
+    <col min="7" max="7" width="3.25" customWidth="true" style="245"/>
+    <col min="8" max="8" width="11.625" customWidth="true" style="245"/>
+    <col min="9" max="9" width="8.25" customWidth="true" style="245"/>
+    <col min="10" max="10" width="4.875" customWidth="true" style="245"/>
+    <col min="11" max="11" width="2.125" customWidth="true" style="245"/>
+    <col min="12" max="12" width="10.875" customWidth="true" style="245"/>
+    <col min="13" max="13" width="12.375" customWidth="true" style="245"/>
+    <col min="14" max="14" width="9.5" customWidth="true" style="245"/>
+    <col min="16" max="16" width="10.625" customWidth="true" style="245"/>
+    <col min="17" max="17" width="9.125" customWidth="true" style="245"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -8254,32 +8281,32 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:23" customHeight="1" ht="60" s="246" customFormat="1">
-      <c r="A2" s="283" t="inlineStr">
+    <row r="2" spans="1:23" customHeight="1" ht="60" s="245" customFormat="1">
+      <c r="A2" s="282" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Certificate of Registration of Automobile</t>
           </r>
         </is>
       </c>
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="251"/>
-      <c r="O2" s="251"/>
-      <c r="P2" s="251"/>
-      <c r="Q2" s="252"/>
-    </row>
-    <row r="3" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="250"/>
+      <c r="E2" s="250"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="250"/>
+      <c r="J2" s="250"/>
+      <c r="K2" s="250"/>
+      <c r="L2" s="250"/>
+      <c r="M2" s="250"/>
+      <c r="N2" s="250"/>
+      <c r="O2" s="250"/>
+      <c r="P2" s="250"/>
+      <c r="Q2" s="251"/>
+    </row>
+    <row r="3" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -8292,10 +8319,10 @@
         <f>구매리스트!G3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="252"/>
       <c r="H3" s="17" t="inlineStr">
         <is>
           <r>
@@ -8310,43 +8337,43 @@
           </r>
         </is>
       </c>
-      <c r="J3" s="165" t="inlineStr">
+      <c r="J3" s="164" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">First Registration Date : </t>
           </r>
         </is>
       </c>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="253"/>
-      <c r="O3" s="176" t="str">
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="M3" s="252"/>
+      <c r="N3" s="252"/>
+      <c r="O3" s="175" t="str">
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="254"/>
-    </row>
-    <row r="4" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A4" s="173" t="inlineStr">
+      <c r="P3" s="252"/>
+      <c r="Q3" s="253"/>
+    </row>
+    <row r="4" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A4" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">① Registration No.</t>
           </r>
         </is>
       </c>
-      <c r="B4" s="255"/>
-      <c r="C4" s="255"/>
-      <c r="D4" s="256"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="255"/>
       <c r="E4" s="151" t="str">
         <f>구매리스트!D4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="256"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="255"/>
       <c r="J4" s="138" t="inlineStr">
         <is>
           <r>
@@ -8354,13 +8381,13 @@
           </r>
         </is>
       </c>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
-      <c r="M4" s="177" t="str">
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="176" t="str">
         <f>구매리스트!I6</f>
         <v>0</v>
       </c>
-      <c r="N4" s="256"/>
+      <c r="N4" s="255"/>
       <c r="O4" s="136" t="inlineStr">
         <is>
           <r>
@@ -8368,146 +8395,146 @@
           </r>
         </is>
       </c>
-      <c r="P4" s="178" t="inlineStr">
+      <c r="P4" s="177" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Private car</t>
           </r>
         </is>
       </c>
-      <c r="Q4" s="256"/>
-    </row>
-    <row r="5" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A5" s="173" t="inlineStr">
+      <c r="Q4" s="255"/>
+    </row>
+    <row r="5" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A5" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">④ Car Name</t>
           </r>
         </is>
       </c>
-      <c r="B5" s="255"/>
-      <c r="C5" s="255"/>
-      <c r="D5" s="256"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="255"/>
       <c r="E5" s="151" t="str">
         <f>구매리스트!B5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="173" t="inlineStr">
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑤ Model &amp;Year</t>
           </r>
         </is>
       </c>
-      <c r="K5" s="255"/>
-      <c r="L5" s="256"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="255"/>
       <c r="M5" s="134" t="str">
         <f>구매리스트!G4</f>
         <v>0</v>
       </c>
-      <c r="N5" s="255"/>
-      <c r="O5" s="255"/>
-      <c r="P5" s="257" t="str">
+      <c r="N5" s="254"/>
+      <c r="O5" s="254"/>
+      <c r="P5" s="256" t="str">
         <f>구매리스트!I5</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="256"/>
-      <c r="S5" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A6" s="173" t="inlineStr">
+      <c r="Q5" s="255"/>
+      <c r="S5" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A6" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑥ Vehicle ID No.</t>
           </r>
         </is>
       </c>
-      <c r="B6" s="255"/>
-      <c r="C6" s="255"/>
-      <c r="D6" s="256"/>
+      <c r="B6" s="254"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="255"/>
       <c r="E6" s="151" t="str">
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="F6" s="255"/>
-      <c r="G6" s="255"/>
-      <c r="H6" s="255"/>
-      <c r="I6" s="256"/>
-      <c r="J6" s="173" t="inlineStr">
+      <c r="F6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="254"/>
+      <c r="I6" s="255"/>
+      <c r="J6" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑦ Motor Type</t>
           </r>
         </is>
       </c>
-      <c r="K6" s="255"/>
-      <c r="L6" s="256"/>
+      <c r="K6" s="254"/>
+      <c r="L6" s="255"/>
       <c r="M6" s="151" t="str">
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
-      <c r="N6" s="255"/>
-      <c r="O6" s="255"/>
-      <c r="P6" s="255"/>
-      <c r="Q6" s="256"/>
-      <c r="S6" s="284" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="7" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A7" s="173" t="inlineStr">
+      <c r="N6" s="254"/>
+      <c r="O6" s="254"/>
+      <c r="P6" s="254"/>
+      <c r="Q6" s="255"/>
+      <c r="S6" s="283" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A7" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑧ Usage Basc</t>
           </r>
         </is>
       </c>
-      <c r="B7" s="255"/>
-      <c r="C7" s="255"/>
-      <c r="D7" s="256"/>
-      <c r="E7" s="258" t="inlineStr">
+      <c r="B7" s="254"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="257" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea </t>
           </r>
         </is>
       </c>
-      <c r="F7" s="255"/>
-      <c r="G7" s="255"/>
-      <c r="H7" s="255"/>
-      <c r="I7" s="255"/>
-      <c r="J7" s="255"/>
-      <c r="K7" s="255"/>
-      <c r="L7" s="255"/>
-      <c r="M7" s="255"/>
-      <c r="N7" s="255"/>
-      <c r="O7" s="255"/>
-      <c r="P7" s="255"/>
-      <c r="Q7" s="256"/>
-    </row>
-    <row r="8" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A8" s="259" t="inlineStr">
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="254"/>
+      <c r="O7" s="254"/>
+      <c r="P7" s="254"/>
+      <c r="Q7" s="255"/>
+    </row>
+    <row r="8" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A8" s="258" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Owner</t>
           </r>
         </is>
       </c>
-      <c r="B8" s="256"/>
+      <c r="B8" s="255"/>
       <c r="C8" s="135" t="inlineStr">
         <is>
           <r>
@@ -8515,47 +8542,47 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="255"/>
-      <c r="E8" s="260" t="inlineStr">
+      <c r="D8" s="254"/>
+      <c r="E8" s="259" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR LTD,. </t>
           </r>
         </is>
       </c>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="255"/>
-      <c r="I8" s="256"/>
-      <c r="J8" s="261" t="inlineStr">
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="254"/>
+      <c r="I8" s="255"/>
+      <c r="J8" s="260" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">      ID Card No.</t>
           </r>
         </is>
       </c>
-      <c r="K8" s="255"/>
-      <c r="L8" s="256"/>
-      <c r="M8" s="260" t="inlineStr">
+      <c r="K8" s="254"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="259" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">120111-0922270</t>
           </r>
         </is>
       </c>
-      <c r="N8" s="255"/>
-      <c r="O8" s="255"/>
-      <c r="P8" s="255"/>
-      <c r="Q8" s="256"/>
-      <c r="R8" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="1:23" customHeight="1" ht="6.75" s="246" customFormat="1">
+      <c r="N8" s="254"/>
+      <c r="O8" s="254"/>
+      <c r="P8" s="254"/>
+      <c r="Q8" s="255"/>
+      <c r="R8" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:23" customHeight="1" ht="6.75" s="245" customFormat="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -8574,28 +8601,28 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:23" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A10" s="285" t="inlineStr">
+    <row r="10" spans="1:23" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A10" s="284" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">「It is proved that it was registered as above in accordance with Article 8 of the Motor Vehicle Management Act.</t>
           </r>
         </is>
       </c>
-      <c r="Q10" s="263"/>
-    </row>
-    <row r="11" spans="1:23" customHeight="1" ht="22.5" s="246" customFormat="1">
+      <c r="Q10" s="262"/>
+    </row>
+    <row r="11" spans="1:23" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="168" t="inlineStr">
+      <c r="B11" s="167" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ Note: In the case of an electric vehicle or hydrogen fuel cell vehicle, the 'prime motor type' in column ⑦ refers to the 'drive motor type</t>
           </r>
         </is>
       </c>
-      <c r="Q11" s="263"/>
-    </row>
-    <row r="12" spans="1:23" customHeight="1" ht="20.25" s="246" customFormat="1">
+      <c r="Q11" s="262"/>
+    </row>
+    <row r="12" spans="1:23" customHeight="1" ht="20.25" s="245" customFormat="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8620,7 +8647,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:23" customHeight="1" ht="26.25" s="246" customFormat="1">
+    <row r="13" spans="1:23" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <r>
@@ -8628,30 +8655,30 @@
           </r>
         </is>
       </c>
-      <c r="B13" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J13" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="L13" s="169" t="str">
+      <c r="B13" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J13" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="L13" s="168" t="str">
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
-      <c r="O13" s="246"/>
-      <c r="P13" s="264"/>
+      <c r="O13" s="245"/>
+      <c r="P13" s="263"/>
       <c r="Q13" s="5"/>
       <c r="S13" s="72"/>
     </row>
-    <row r="14" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
+    <row r="14" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A14" s="4"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
@@ -8659,25 +8686,21 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:23" customHeight="1" ht="39" s="246" customFormat="1">
+    <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="156" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="Q15" s="263"/>
-      <c r="W15" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="16" spans="1:23" customHeight="1" ht="9" s="246" customFormat="1">
+      <c r="J15" s="397" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q15" s="262"/>
+      <c r="W15" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:23" customHeight="1" ht="9" s="245" customFormat="1">
       <c r="A16" s="7"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -8696,54 +8719,54 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
     </row>
-    <row r="17" spans="1:23" customHeight="1" ht="8.25" s="246" customFormat="1">
+    <row r="17" spans="1:23" customHeight="1" ht="8.25" s="245" customFormat="1">
       <c r="A17" s="4"/>
-      <c r="B17" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I17" s="265"/>
-      <c r="J17" s="265"/>
-      <c r="K17" s="265"/>
-      <c r="L17" s="265"/>
-      <c r="M17" s="265"/>
-      <c r="N17" s="265"/>
+      <c r="B17" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="264"/>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:23" customHeight="1" ht="21.75" s="246" customFormat="1">
-      <c r="A18" s="266" t="inlineStr">
+    <row r="18" spans="1:23" customHeight="1" ht="21.75" s="245" customFormat="1">
+      <c r="A18" s="265" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1.Specifications</t>
           </r>
         </is>
       </c>
-      <c r="B18" s="255"/>
-      <c r="C18" s="255"/>
-      <c r="D18" s="255"/>
-      <c r="E18" s="255"/>
-      <c r="F18" s="255"/>
-      <c r="G18" s="255"/>
-      <c r="H18" s="255"/>
-      <c r="I18" s="255"/>
-      <c r="J18" s="256"/>
-      <c r="L18" s="267" t="inlineStr">
+      <c r="B18" s="254"/>
+      <c r="C18" s="254"/>
+      <c r="D18" s="254"/>
+      <c r="E18" s="254"/>
+      <c r="F18" s="254"/>
+      <c r="G18" s="254"/>
+      <c r="H18" s="254"/>
+      <c r="I18" s="254"/>
+      <c r="J18" s="255"/>
+      <c r="L18" s="266" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  4. Validity period of inspection</t>
           </r>
         </is>
       </c>
-      <c r="M18" s="255"/>
-      <c r="N18" s="255"/>
-      <c r="O18" s="255"/>
-      <c r="P18" s="255"/>
-      <c r="Q18" s="256"/>
-    </row>
-    <row r="19" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="M18" s="254"/>
+      <c r="N18" s="254"/>
+      <c r="O18" s="254"/>
+      <c r="P18" s="254"/>
+      <c r="Q18" s="255"/>
+    </row>
+    <row r="19" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
         <is>
           <r>
@@ -8751,25 +8774,25 @@
           </r>
         </is>
       </c>
-      <c r="B19" s="170" t="inlineStr">
+      <c r="B19" s="169" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Specification Control Number</t>
           </r>
         </is>
       </c>
-      <c r="C19" s="251"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="251"/>
-      <c r="F19" s="268" t="str">
+      <c r="C19" s="250"/>
+      <c r="D19" s="250"/>
+      <c r="E19" s="250"/>
+      <c r="F19" s="267" t="str">
         <f>구매리스트!G5</f>
         <v>0</v>
       </c>
-      <c r="G19" s="251"/>
-      <c r="H19" s="251"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="252"/>
-      <c r="L19" s="286" t="inlineStr">
+      <c r="G19" s="250"/>
+      <c r="H19" s="250"/>
+      <c r="I19" s="250"/>
+      <c r="J19" s="251"/>
+      <c r="L19" s="285" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    Date
@@ -8777,7 +8800,7 @@
           </r>
         </is>
       </c>
-      <c r="M19" s="286" t="inlineStr">
+      <c r="M19" s="285" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    Date
@@ -8785,7 +8808,7 @@
           </r>
         </is>
       </c>
-      <c r="N19" s="287" t="inlineStr">
+      <c r="N19" s="286" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> Place of
@@ -8793,21 +8816,21 @@
           </r>
         </is>
       </c>
-      <c r="O19" s="288" t="inlineStr">
+      <c r="O19" s="287" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">mileage</t>
           </r>
         </is>
       </c>
-      <c r="P19" s="289" t="inlineStr">
+      <c r="P19" s="288" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> Inspect manager check</t>
           </r>
         </is>
       </c>
-      <c r="Q19" s="290" t="inlineStr">
+      <c r="Q19" s="289" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Prosecutor
@@ -8816,7 +8839,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="20" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
         <is>
           <r>
@@ -8824,29 +8847,29 @@
           </r>
         </is>
       </c>
-      <c r="B20" s="174" t="inlineStr">
+      <c r="B20" s="173" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(Type approval number)</t>
           </r>
         </is>
       </c>
-      <c r="C20" s="253"/>
-      <c r="D20" s="253"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="253"/>
-      <c r="G20" s="253"/>
-      <c r="H20" s="253"/>
-      <c r="I20" s="253"/>
-      <c r="J20" s="254"/>
-      <c r="L20" s="291"/>
-      <c r="M20" s="291"/>
-      <c r="N20" s="291"/>
-      <c r="O20" s="291"/>
-      <c r="P20" s="291"/>
-      <c r="Q20" s="291"/>
-    </row>
-    <row r="21" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="C20" s="252"/>
+      <c r="D20" s="252"/>
+      <c r="E20" s="252"/>
+      <c r="F20" s="252"/>
+      <c r="G20" s="252"/>
+      <c r="H20" s="252"/>
+      <c r="I20" s="252"/>
+      <c r="J20" s="253"/>
+      <c r="L20" s="290"/>
+      <c r="M20" s="290"/>
+      <c r="N20" s="290"/>
+      <c r="O20" s="290"/>
+      <c r="P20" s="290"/>
+      <c r="Q20" s="290"/>
+    </row>
+    <row r="21" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
         <is>
           <r>
@@ -8861,12 +8884,12 @@
           </r>
         </is>
       </c>
-      <c r="C21" s="256"/>
-      <c r="D21" s="157" t="str">
+      <c r="C21" s="255"/>
+      <c r="D21" s="156" t="str">
         <f>구매리스트!G7</f>
         <v>0</v>
       </c>
-      <c r="E21" s="255"/>
+      <c r="E21" s="254"/>
       <c r="F21" s="16" t="inlineStr">
         <is>
           <r>
@@ -8914,15 +8937,15 @@
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
-      <c r="R21" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="22" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="R21" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
         <is>
           <r>
@@ -8937,12 +8960,12 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="256"/>
+      <c r="C22" s="255"/>
       <c r="D22" s="141" t="str">
         <f>구매리스트!G8</f>
         <v>0</v>
       </c>
-      <c r="E22" s="255"/>
+      <c r="E22" s="254"/>
       <c r="F22" s="16" t="inlineStr">
         <is>
           <r>
@@ -8981,15 +9004,15 @@
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
-      <c r="S22" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="23" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="S22" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
         <is>
           <r>
@@ -8997,19 +9020,19 @@
           </r>
         </is>
       </c>
-      <c r="B23" s="158" t="inlineStr">
+      <c r="B23" s="157" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Passenger Capacity</t>
           </r>
         </is>
       </c>
-      <c r="C23" s="256"/>
+      <c r="C23" s="255"/>
       <c r="D23" s="141" t="str">
         <f>구매리스트!G9</f>
         <v>0</v>
       </c>
-      <c r="E23" s="255"/>
+      <c r="E23" s="254"/>
       <c r="F23" s="73" t="inlineStr">
         <is>
           <r>
@@ -9048,55 +9071,55 @@
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
     </row>
-    <row r="24" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A24" s="269" t="inlineStr">
+    <row r="24" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A24" s="268" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑱</t>
           </r>
         </is>
       </c>
-      <c r="B24" s="171" t="inlineStr">
+      <c r="B24" s="170" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Displacement or</t>
           </r>
         </is>
       </c>
-      <c r="C24" s="252"/>
-      <c r="D24" s="270" t="str">
+      <c r="C24" s="251"/>
+      <c r="D24" s="269" t="str">
         <f>구매리스트!G10</f>
         <v>0</v>
       </c>
-      <c r="E24" s="251"/>
-      <c r="F24" s="251"/>
-      <c r="G24" s="251"/>
-      <c r="H24" s="251"/>
-      <c r="I24" s="271" t="inlineStr">
+      <c r="E24" s="250"/>
+      <c r="F24" s="250"/>
+      <c r="G24" s="250"/>
+      <c r="H24" s="250"/>
+      <c r="I24" s="270" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">cc,(Ah ,[Ah]</t>
           </r>
         </is>
       </c>
-      <c r="J24" s="252"/>
+      <c r="J24" s="251"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
-      <c r="S24" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="25" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A25" s="272"/>
-      <c r="B25" s="292" t="inlineStr">
+      <c r="S24" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A25" s="271"/>
+      <c r="B25" s="291" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Drive battery 
@@ -9104,9 +9127,9 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="263"/>
-      <c r="D25" s="272"/>
-      <c r="J25" s="263"/>
+      <c r="C25" s="262"/>
+      <c r="D25" s="271"/>
+      <c r="J25" s="262"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -9114,32 +9137,32 @@
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
     </row>
-    <row r="26" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A26" s="273"/>
-      <c r="B26" s="253"/>
-      <c r="C26" s="254"/>
-      <c r="D26" s="273"/>
-      <c r="E26" s="253"/>
-      <c r="F26" s="253"/>
-      <c r="G26" s="253"/>
-      <c r="H26" s="253"/>
-      <c r="I26" s="253"/>
-      <c r="J26" s="254"/>
+    <row r="26" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A26" s="272"/>
+      <c r="B26" s="252"/>
+      <c r="C26" s="253"/>
+      <c r="D26" s="272"/>
+      <c r="E26" s="252"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="252"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="253"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
-      <c r="S26" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="27" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="S26" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
         <is>
           <r>
@@ -9154,14 +9177,14 @@
           </r>
         </is>
       </c>
-      <c r="C27" s="256"/>
+      <c r="C27" s="255"/>
       <c r="D27" s="141" t="str">
         <f>구매리스트!G11</f>
         <v>0</v>
       </c>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
       <c r="H27" s="140" t="inlineStr">
         <is>
           <r>
@@ -9169,8 +9192,8 @@
           </r>
         </is>
       </c>
-      <c r="I27" s="255"/>
-      <c r="J27" s="256"/>
+      <c r="I27" s="254"/>
+      <c r="J27" s="255"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
@@ -9178,7 +9201,7 @@
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
     </row>
-    <row r="28" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="28" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
         <is>
           <r>
@@ -9186,22 +9209,22 @@
           </r>
         </is>
       </c>
-      <c r="B28" s="172" t="inlineStr">
+      <c r="B28" s="171" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Number of Cylinders</t>
           </r>
         </is>
       </c>
-      <c r="C28" s="252"/>
-      <c r="D28" s="274" t="str">
+      <c r="C28" s="251"/>
+      <c r="D28" s="273" t="str">
         <f>구매리스트!G12</f>
         <v>0</v>
       </c>
-      <c r="E28" s="251"/>
-      <c r="F28" s="251"/>
-      <c r="G28" s="251"/>
-      <c r="H28" s="251"/>
+      <c r="E28" s="250"/>
+      <c r="F28" s="250"/>
+      <c r="G28" s="250"/>
+      <c r="H28" s="250"/>
       <c r="I28" s="139" t="inlineStr">
         <is>
           <r>
@@ -9210,7 +9233,7 @@
           </r>
         </is>
       </c>
-      <c r="J28" s="252"/>
+      <c r="J28" s="251"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
@@ -9218,17 +9241,17 @@
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
     </row>
-    <row r="29" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A29" s="293" t="inlineStr">
+    <row r="29" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A29" s="292" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(Drive Storage Voltage)</t>
           </r>
         </is>
       </c>
-      <c r="C29" s="263"/>
-      <c r="D29" s="272"/>
-      <c r="J29" s="263"/>
+      <c r="C29" s="262"/>
+      <c r="D29" s="271"/>
+      <c r="J29" s="262"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
@@ -9236,23 +9259,23 @@
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
     </row>
-    <row r="30" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A30" s="294" t="inlineStr">
+    <row r="30" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A30" s="293" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">[Maximum Fuel Cell Output]</t>
           </r>
         </is>
       </c>
-      <c r="B30" s="253"/>
-      <c r="C30" s="254"/>
-      <c r="D30" s="273"/>
-      <c r="E30" s="253"/>
-      <c r="F30" s="253"/>
-      <c r="G30" s="253"/>
-      <c r="H30" s="253"/>
-      <c r="I30" s="253"/>
-      <c r="J30" s="254"/>
+      <c r="B30" s="252"/>
+      <c r="C30" s="253"/>
+      <c r="D30" s="272"/>
+      <c r="E30" s="252"/>
+      <c r="F30" s="252"/>
+      <c r="G30" s="252"/>
+      <c r="H30" s="252"/>
+      <c r="I30" s="252"/>
+      <c r="J30" s="253"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
@@ -9260,7 +9283,7 @@
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="31" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
         <is>
           <r>
@@ -9268,7 +9291,7 @@
           </r>
         </is>
       </c>
-      <c r="B31" s="295" t="inlineStr">
+      <c r="B31" s="294" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Type of fuel and fuel 
@@ -9276,26 +9299,26 @@
           </r>
         </is>
       </c>
-      <c r="C31" s="256"/>
+      <c r="C31" s="255"/>
       <c r="D31" s="146" t="str">
         <f>구매리스트!I13</f>
         <v>0</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="254"/>
       <c r="F31" s="145" t="str">
         <f>구매리스트!H13</f>
         <v>0</v>
       </c>
-      <c r="G31" s="255"/>
-      <c r="H31" s="161" t="inlineStr">
+      <c r="G31" s="254"/>
+      <c r="H31" s="160" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">km/l,(km/kWh),[km/kg]</t>
           </r>
         </is>
       </c>
-      <c r="I31" s="255"/>
-      <c r="J31" s="256"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="255"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
@@ -9303,7 +9326,7 @@
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
     </row>
-    <row r="32" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="32" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
         <is>
           <r>
@@ -9311,7 +9334,7 @@
           </r>
         </is>
       </c>
-      <c r="B32" s="295" t="inlineStr">
+      <c r="B32" s="294" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Manufacturer of 
@@ -9319,16 +9342,16 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="256"/>
-      <c r="D32" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E32" s="255"/>
-      <c r="F32" s="256"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E32" s="254"/>
+      <c r="F32" s="255"/>
       <c r="G32" s="59" t="inlineStr">
         <is>
           <r>
@@ -9343,14 +9366,14 @@
           </r>
         </is>
       </c>
-      <c r="I32" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J32" s="256"/>
+      <c r="I32" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J32" s="255"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
@@ -9358,7 +9381,7 @@
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
     </row>
-    <row r="33" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="33" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
         <is>
           <r>
@@ -9366,7 +9389,7 @@
           </r>
         </is>
       </c>
-      <c r="B33" s="296" t="inlineStr">
+      <c r="B33" s="295" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Main raw materials of 
@@ -9374,16 +9397,16 @@
           </r>
         </is>
       </c>
-      <c r="C33" s="256"/>
-      <c r="D33" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E33" s="255"/>
-      <c r="F33" s="256"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E33" s="254"/>
+      <c r="F33" s="255"/>
       <c r="G33" s="136" t="inlineStr">
         <is>
           <r>
@@ -9391,15 +9414,15 @@
           </r>
         </is>
       </c>
-      <c r="H33" s="256"/>
-      <c r="I33" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J33" s="256"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J33" s="255"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
@@ -9407,23 +9430,23 @@
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
     </row>
-    <row r="34" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A34" s="278" t="inlineStr">
+    <row r="34" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A34" s="277" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Note: In (18)~(21), the unit used refers to () in the case of an electric vehicle and [] in the case of a hydrogen fuel electric vehicle. In the case of special vehicles in Schedule 1 2 of the Enforcement Regulations of the Motor Vehicle Management Act, the maximum load refers to the maximum vertical load allowed to connect the towed vehicle and is not related to the towing capacity, (22)~(24) applies only to vehicles equipped with drive storage batteries (excluding vehicles with structures that cannot be charged through an external electricity source).</t>
           </r>
         </is>
       </c>
-      <c r="B34" s="251"/>
-      <c r="C34" s="251"/>
-      <c r="D34" s="251"/>
-      <c r="E34" s="251"/>
-      <c r="F34" s="251"/>
-      <c r="G34" s="251"/>
-      <c r="H34" s="251"/>
-      <c r="I34" s="251"/>
-      <c r="J34" s="252"/>
+      <c r="B34" s="250"/>
+      <c r="C34" s="250"/>
+      <c r="D34" s="250"/>
+      <c r="E34" s="250"/>
+      <c r="F34" s="250"/>
+      <c r="G34" s="250"/>
+      <c r="H34" s="250"/>
+      <c r="I34" s="250"/>
+      <c r="J34" s="251"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
@@ -9431,9 +9454,9 @@
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
     </row>
-    <row r="35" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A35" s="272"/>
-      <c r="J35" s="263"/>
+    <row r="35" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A35" s="271"/>
+      <c r="J35" s="262"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
@@ -9441,9 +9464,9 @@
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
     </row>
-    <row r="36" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A36" s="272"/>
-      <c r="J36" s="263"/>
+    <row r="36" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A36" s="271"/>
+      <c r="J36" s="262"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
@@ -9451,17 +9474,17 @@
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
     </row>
-    <row r="37" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A37" s="273"/>
-      <c r="B37" s="253"/>
-      <c r="C37" s="253"/>
-      <c r="D37" s="253"/>
-      <c r="E37" s="253"/>
-      <c r="F37" s="253"/>
-      <c r="G37" s="253"/>
-      <c r="H37" s="253"/>
-      <c r="I37" s="253"/>
-      <c r="J37" s="254"/>
+    <row r="37" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A37" s="272"/>
+      <c r="B37" s="252"/>
+      <c r="C37" s="252"/>
+      <c r="D37" s="252"/>
+      <c r="E37" s="252"/>
+      <c r="F37" s="252"/>
+      <c r="G37" s="252"/>
+      <c r="H37" s="252"/>
+      <c r="I37" s="252"/>
+      <c r="J37" s="253"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
@@ -9469,47 +9492,47 @@
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
     </row>
-    <row r="38" spans="1:23" customHeight="1" ht="25.5" s="246" customFormat="1">
-      <c r="A38" s="173" t="inlineStr">
+    <row r="38" spans="1:23" customHeight="1" ht="25.5" s="245" customFormat="1">
+      <c r="A38" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2.Registration plate issued and sealed</t>
           </r>
         </is>
       </c>
-      <c r="B38" s="255"/>
-      <c r="C38" s="255"/>
-      <c r="D38" s="255"/>
-      <c r="E38" s="255"/>
-      <c r="F38" s="255"/>
-      <c r="G38" s="255"/>
-      <c r="H38" s="255"/>
-      <c r="I38" s="255"/>
-      <c r="J38" s="256"/>
-      <c r="L38" s="297" t="inlineStr">
+      <c r="B38" s="254"/>
+      <c r="C38" s="254"/>
+      <c r="D38" s="254"/>
+      <c r="E38" s="254"/>
+      <c r="F38" s="254"/>
+      <c r="G38" s="254"/>
+      <c r="H38" s="254"/>
+      <c r="I38" s="254"/>
+      <c r="J38" s="255"/>
+      <c r="L38" s="296" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ Note: In the first column of paragraph ㉚, write the date of new registration.</t>
           </r>
         </is>
       </c>
-      <c r="M38" s="251"/>
-      <c r="N38" s="251"/>
-      <c r="O38" s="251"/>
-      <c r="P38" s="251"/>
-      <c r="Q38" s="252"/>
-    </row>
-    <row r="39" spans="1:23" customHeight="1" ht="25.5" s="246" customFormat="1">
-      <c r="A39" s="280" t="inlineStr">
+      <c r="M38" s="250"/>
+      <c r="N38" s="250"/>
+      <c r="O38" s="250"/>
+      <c r="P38" s="250"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:23" customHeight="1" ht="25.5" s="245" customFormat="1">
+      <c r="A39" s="279" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉕ Classification</t>
           </r>
         </is>
       </c>
-      <c r="B39" s="255"/>
-      <c r="C39" s="256"/>
-      <c r="D39" s="298" t="inlineStr">
+      <c r="B39" s="254"/>
+      <c r="C39" s="255"/>
+      <c r="D39" s="297" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> ㉖ License plate 
@@ -9517,32 +9540,32 @@
           </r>
         </is>
       </c>
-      <c r="E39" s="255"/>
-      <c r="F39" s="255"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="299" t="inlineStr">
+      <c r="E39" s="254"/>
+      <c r="F39" s="254"/>
+      <c r="G39" s="255"/>
+      <c r="H39" s="298" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉗ Confirmation of issuing agent</t>
           </r>
         </is>
       </c>
-      <c r="I39" s="255"/>
-      <c r="J39" s="256"/>
-      <c r="L39" s="300" t="inlineStr">
+      <c r="I39" s="254"/>
+      <c r="J39" s="255"/>
+      <c r="L39" s="299" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> REMARKS</t>
           </r>
         </is>
       </c>
-      <c r="M39" s="251"/>
-      <c r="N39" s="251"/>
-      <c r="O39" s="251"/>
-      <c r="P39" s="251"/>
-      <c r="Q39" s="252"/>
-    </row>
-    <row r="40" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
+      <c r="M39" s="250"/>
+      <c r="N39" s="250"/>
+      <c r="O39" s="250"/>
+      <c r="P39" s="250"/>
+      <c r="Q39" s="251"/>
+    </row>
+    <row r="40" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
         <is>
           <r>
@@ -9550,7 +9573,7 @@
           </r>
         </is>
       </c>
-      <c r="B40" s="256"/>
+      <c r="B40" s="255"/>
       <c r="C40" s="136" t="inlineStr">
         <is>
           <r>
@@ -9558,8 +9581,8 @@
           </r>
         </is>
       </c>
-      <c r="D40" s="255"/>
-      <c r="E40" s="256"/>
+      <c r="D40" s="254"/>
+      <c r="E40" s="255"/>
       <c r="F40" s="136" t="inlineStr">
         <is>
           <r>
@@ -9567,7 +9590,7 @@
           </r>
         </is>
       </c>
-      <c r="G40" s="256"/>
+      <c r="G40" s="255"/>
       <c r="H40" s="136" t="inlineStr">
         <is>
           <r>
@@ -9575,12 +9598,12 @@
           </r>
         </is>
       </c>
-      <c r="I40" s="255"/>
-      <c r="J40" s="256"/>
+      <c r="I40" s="254"/>
+      <c r="J40" s="255"/>
       <c r="L40" s="4"/>
       <c r="Q40" s="5"/>
     </row>
-    <row r="41" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="41" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
         <is>
           <r>
@@ -9588,7 +9611,7 @@
           </r>
         </is>
       </c>
-      <c r="B41" s="256"/>
+      <c r="B41" s="255"/>
       <c r="C41" s="136" t="inlineStr">
         <is>
           <r>
@@ -9596,8 +9619,8 @@
           </r>
         </is>
       </c>
-      <c r="D41" s="255"/>
-      <c r="E41" s="256"/>
+      <c r="D41" s="254"/>
+      <c r="E41" s="255"/>
       <c r="F41" s="136" t="inlineStr">
         <is>
           <r>
@@ -9605,7 +9628,7 @@
           </r>
         </is>
       </c>
-      <c r="G41" s="256"/>
+      <c r="G41" s="255"/>
       <c r="H41" s="136" t="inlineStr">
         <is>
           <r>
@@ -9613,10 +9636,10 @@
           </r>
         </is>
       </c>
-      <c r="I41" s="255"/>
-      <c r="J41" s="256"/>
+      <c r="I41" s="254"/>
+      <c r="J41" s="255"/>
       <c r="L41" s="4"/>
-      <c r="O41" s="246" t="inlineStr">
+      <c r="O41" s="245" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -9625,53 +9648,53 @@
       </c>
       <c r="Q41" s="5"/>
     </row>
-    <row r="42" spans="1:23" customHeight="1" ht="33" s="246" customFormat="1">
-      <c r="A42" s="298" t="inlineStr">
+    <row r="42" spans="1:23" customHeight="1" ht="33" s="245" customFormat="1">
+      <c r="A42" s="297" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3. Fact of mortgage registration (The contents of the mortgage registration are in the motor vehicle registration ledgerPlease perusal and confirm)</t>
           </r>
         </is>
       </c>
-      <c r="B42" s="255"/>
-      <c r="C42" s="255"/>
-      <c r="D42" s="255"/>
-      <c r="E42" s="255"/>
-      <c r="F42" s="255"/>
-      <c r="G42" s="255"/>
-      <c r="H42" s="255"/>
-      <c r="I42" s="255"/>
-      <c r="J42" s="256"/>
+      <c r="B42" s="254"/>
+      <c r="C42" s="254"/>
+      <c r="D42" s="254"/>
+      <c r="E42" s="254"/>
+      <c r="F42" s="254"/>
+      <c r="G42" s="254"/>
+      <c r="H42" s="254"/>
+      <c r="I42" s="254"/>
+      <c r="J42" s="255"/>
       <c r="L42" s="4"/>
       <c r="Q42" s="5"/>
     </row>
-    <row r="43" spans="1:23" customHeight="1" ht="22.5" s="246" customFormat="1">
-      <c r="A43" s="301" t="inlineStr">
+    <row r="43" spans="1:23" customHeight="1" ht="22.5" s="245" customFormat="1">
+      <c r="A43" s="300" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉘ Classification (setting or erasure)</t>
           </r>
         </is>
       </c>
-      <c r="B43" s="255"/>
-      <c r="C43" s="255"/>
-      <c r="D43" s="255"/>
-      <c r="E43" s="255"/>
-      <c r="F43" s="255"/>
-      <c r="G43" s="256"/>
-      <c r="H43" s="162" t="inlineStr">
+      <c r="B43" s="254"/>
+      <c r="C43" s="254"/>
+      <c r="D43" s="254"/>
+      <c r="E43" s="254"/>
+      <c r="F43" s="254"/>
+      <c r="G43" s="255"/>
+      <c r="H43" s="161" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉙ Date</t>
           </r>
         </is>
       </c>
-      <c r="I43" s="255"/>
-      <c r="J43" s="256"/>
+      <c r="I43" s="254"/>
+      <c r="J43" s="255"/>
       <c r="L43" s="4"/>
       <c r="Q43" s="5"/>
     </row>
-    <row r="44" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="44" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
         <is>
           <r>
@@ -9679,12 +9702,12 @@
           </r>
         </is>
       </c>
-      <c r="B44" s="255"/>
-      <c r="C44" s="255"/>
-      <c r="D44" s="255"/>
-      <c r="E44" s="255"/>
-      <c r="F44" s="255"/>
-      <c r="G44" s="256"/>
+      <c r="B44" s="254"/>
+      <c r="C44" s="254"/>
+      <c r="D44" s="254"/>
+      <c r="E44" s="254"/>
+      <c r="F44" s="254"/>
+      <c r="G44" s="255"/>
       <c r="H44" s="136" t="inlineStr">
         <is>
           <r>
@@ -9692,12 +9715,12 @@
           </r>
         </is>
       </c>
-      <c r="I44" s="255"/>
-      <c r="J44" s="256"/>
+      <c r="I44" s="254"/>
+      <c r="J44" s="255"/>
       <c r="L44" s="4"/>
       <c r="Q44" s="5"/>
     </row>
-    <row r="45" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="45" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
         <is>
           <r>
@@ -9705,12 +9728,12 @@
           </r>
         </is>
       </c>
-      <c r="B45" s="255"/>
-      <c r="C45" s="255"/>
-      <c r="D45" s="255"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="255"/>
-      <c r="G45" s="256"/>
+      <c r="B45" s="254"/>
+      <c r="C45" s="254"/>
+      <c r="D45" s="254"/>
+      <c r="E45" s="254"/>
+      <c r="F45" s="254"/>
+      <c r="G45" s="255"/>
       <c r="H45" s="136" t="inlineStr">
         <is>
           <r>
@@ -9718,8 +9741,8 @@
           </r>
         </is>
       </c>
-      <c r="I45" s="255"/>
-      <c r="J45" s="256"/>
+      <c r="I45" s="254"/>
+      <c r="J45" s="255"/>
       <c r="K45" s="8"/>
       <c r="L45" s="7"/>
       <c r="M45" s="8"/>
@@ -9728,16 +9751,16 @@
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
     </row>
-    <row r="46" spans="1:23" customHeight="1" ht="6" s="246" customFormat="1"/>
-    <row r="47" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="G47" s="163" t="inlineStr">
+    <row r="46" spans="1:23" customHeight="1" ht="6" s="245" customFormat="1"/>
+    <row r="47" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="G47" s="162" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ Please read the 'Notes' on the back.</t>
           </r>
         </is>
       </c>
-      <c r="N47" s="164" t="inlineStr">
+      <c r="N47" s="163" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">210mm x 297mm [white or heavy paper 80g/㎡]</t>
@@ -9867,25 +9890,25 @@
   <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="14" customWidth="true" style="246"/>
-    <col min="3" max="3" width="6.25" customWidth="true" style="246"/>
-    <col min="4" max="4" width="16.875" customWidth="true" style="246"/>
-    <col min="5" max="5" width="6.375" customWidth="true" style="246"/>
-    <col min="6" max="6" width="8.125" customWidth="true" style="246"/>
-    <col min="7" max="7" width="17.625" customWidth="true" style="246"/>
-    <col min="8" max="8" width="5.875" customWidth="true" style="246"/>
-    <col min="9" max="9" width="2.125" customWidth="true" style="246"/>
-    <col min="10" max="10" width="23.625" customWidth="true" style="246"/>
-    <col min="11" max="11" width="19" customWidth="true" style="246"/>
-    <col min="12" max="12" width="3.5" customWidth="true" style="246"/>
-    <col min="13" max="13" width="2.875" customWidth="true" style="246"/>
-    <col min="14" max="14" width="8.375" customWidth="true" style="246"/>
-    <col min="15" max="15" width="5.25" customWidth="true" style="246"/>
+    <col min="1" max="1" width="6.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="14" customWidth="true" style="245"/>
+    <col min="3" max="3" width="6.25" customWidth="true" style="245"/>
+    <col min="4" max="4" width="16.875" customWidth="true" style="245"/>
+    <col min="5" max="5" width="6.375" customWidth="true" style="245"/>
+    <col min="6" max="6" width="8.125" customWidth="true" style="245"/>
+    <col min="7" max="7" width="17.625" customWidth="true" style="245"/>
+    <col min="8" max="8" width="5.875" customWidth="true" style="245"/>
+    <col min="9" max="9" width="2.125" customWidth="true" style="245"/>
+    <col min="10" max="10" width="23.625" customWidth="true" style="245"/>
+    <col min="11" max="11" width="19" customWidth="true" style="245"/>
+    <col min="12" max="12" width="3.5" customWidth="true" style="245"/>
+    <col min="13" max="13" width="2.875" customWidth="true" style="245"/>
+    <col min="14" max="14" width="8.375" customWidth="true" style="245"/>
+    <col min="15" max="15" width="5.25" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customHeight="1" ht="17.25" s="246" customFormat="1">
-      <c r="A1" s="201" t="inlineStr">
+    <row r="1" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
+      <c r="A1" s="200" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">■ 자동차등록규칙 [별지 제 20호 서식] &lt;개정 2025. 1. 10.&gt;</t>
@@ -9893,8 +9916,8 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:15" customHeight="1" ht="17.25" s="246" customFormat="1">
-      <c r="A2" s="201" t="inlineStr">
+    <row r="2" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
+      <c r="A2" s="200" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">■ 자동차등록규칙 [별지 제 20호 서식] &lt;개정 2025. 1. 10.&gt;</t>
@@ -9902,8 +9925,8 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:15" customHeight="1" ht="17.25" s="246" customFormat="1">
-      <c r="A3" s="201" t="inlineStr">
+    <row r="3" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
+      <c r="A3" s="200" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">     Motor vehicle Registration Rules [Annex Form 20]</t>
@@ -9911,8 +9934,8 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:15" customHeight="1" ht="38.25" s="246" customFormat="1">
-      <c r="A4" s="197" t="inlineStr">
+    <row r="4" spans="1:15" customHeight="1" ht="38.25" s="245" customFormat="1">
+      <c r="A4" s="196" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자동차말소등록사실증명서</t>
@@ -9920,8 +9943,8 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:15" customHeight="1" ht="27.75" s="246" customFormat="1">
-      <c r="A5" s="204" t="inlineStr">
+    <row r="5" spans="1:15" customHeight="1" ht="27.75" s="245" customFormat="1">
+      <c r="A5" s="203" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Certificate of De-registration of Motor Vehicle</t>
@@ -9929,7 +9952,7 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:15" customHeight="1" ht="24.95" s="246" customFormat="1">
+    <row r="6" spans="1:15" customHeight="1" ht="24.95" s="245" customFormat="1">
       <c r="A6" s="92" t="inlineStr">
         <is>
           <r>
@@ -9937,43 +9960,43 @@
           </r>
         </is>
       </c>
-      <c r="B6" s="205" t="str">
+      <c r="B6" s="204" t="str">
         <f>구매리스트!D3</f>
         <v>0</v>
       </c>
-      <c r="C6" s="255"/>
-      <c r="D6" s="255"/>
-      <c r="E6" s="255"/>
-      <c r="F6" s="206" t="inlineStr">
+      <c r="C6" s="254"/>
+      <c r="D6" s="254"/>
+      <c r="E6" s="254"/>
+      <c r="F6" s="205" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">호 (No.        )</t>
           </r>
         </is>
       </c>
-      <c r="G6" s="255"/>
+      <c r="G6" s="254"/>
       <c r="H6" s="93"/>
       <c r="I6" s="93"/>
       <c r="J6" s="93"/>
-      <c r="K6" s="198" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="L6" s="255"/>
-      <c r="M6" s="302" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="N6" s="255"/>
-      <c r="O6" s="255"/>
-    </row>
-    <row r="7" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
+      <c r="K6" s="197" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="L6" s="254"/>
+      <c r="M6" s="301" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="N6" s="254"/>
+      <c r="O6" s="254"/>
+    </row>
+    <row r="7" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A7" s="74"/>
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
@@ -9990,8 +10013,8 @@
       <c r="N7" s="74"/>
       <c r="O7" s="74"/>
     </row>
-    <row r="8" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="A8" s="303" t="inlineStr">
+    <row r="8" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A8" s="302" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자동차의
@@ -10001,39 +10024,39 @@
           </r>
         </is>
       </c>
-      <c r="B8" s="304"/>
-      <c r="C8" s="207" t="inlineStr">
+      <c r="B8" s="303"/>
+      <c r="C8" s="206" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자동차등록번호</t>
           </r>
         </is>
       </c>
-      <c r="D8" s="304"/>
-      <c r="E8" s="199" t="str">
+      <c r="D8" s="303"/>
+      <c r="E8" s="198" t="str">
         <f>구매리스트!B4</f>
         <v>0</v>
       </c>
-      <c r="F8" s="251"/>
-      <c r="G8" s="304"/>
-      <c r="H8" s="207" t="inlineStr">
+      <c r="F8" s="250"/>
+      <c r="G8" s="303"/>
+      <c r="H8" s="206" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">차종 및 주행거리</t>
           </r>
         </is>
       </c>
-      <c r="I8" s="251"/>
-      <c r="J8" s="304"/>
-      <c r="K8" s="208" t="inlineStr">
+      <c r="I8" s="250"/>
+      <c r="J8" s="303"/>
+      <c r="K8" s="207" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">승용</t>
           </r>
         </is>
       </c>
-      <c r="L8" s="251"/>
-      <c r="M8" s="251"/>
+      <c r="L8" s="250"/>
+      <c r="M8" s="250"/>
       <c r="N8" s="80" t="inlineStr">
         <is>
           <r>
@@ -10043,162 +10066,162 @@
       </c>
       <c r="O8" s="81"/>
     </row>
-    <row r="9" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B9" s="305"/>
-      <c r="C9" s="181" t="inlineStr">
+    <row r="9" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B9" s="304"/>
+      <c r="C9" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Registration No.</t>
           </r>
         </is>
       </c>
-      <c r="D9" s="305"/>
-      <c r="E9" s="306"/>
-      <c r="G9" s="305"/>
-      <c r="H9" s="181" t="inlineStr">
+      <c r="D9" s="304"/>
+      <c r="E9" s="305"/>
+      <c r="G9" s="304"/>
+      <c r="H9" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Vehicle Type and Mileage</t>
           </r>
         </is>
       </c>
-      <c r="J9" s="305"/>
-      <c r="K9" s="203" t="str">
+      <c r="J9" s="304"/>
+      <c r="K9" s="202" t="str">
         <f>구매리스트!D7</f>
         <v>0</v>
       </c>
       <c r="N9" s="82"/>
       <c r="O9" s="83"/>
     </row>
-    <row r="10" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B10" s="305"/>
-      <c r="C10" s="202" t="inlineStr">
+    <row r="10" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B10" s="304"/>
+      <c r="C10" s="201" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">차명</t>
           </r>
         </is>
       </c>
-      <c r="D10" s="307"/>
-      <c r="E10" s="308" t="str">
+      <c r="D10" s="306"/>
+      <c r="E10" s="307" t="str">
         <f>구매리스트!B5</f>
         <v>0</v>
       </c>
-      <c r="F10" s="309"/>
-      <c r="G10" s="307"/>
-      <c r="H10" s="202" t="inlineStr">
+      <c r="F10" s="308"/>
+      <c r="G10" s="306"/>
+      <c r="H10" s="201" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">차대번호</t>
           </r>
         </is>
       </c>
-      <c r="I10" s="309"/>
-      <c r="J10" s="307"/>
-      <c r="K10" s="310" t="str">
+      <c r="I10" s="308"/>
+      <c r="J10" s="306"/>
+      <c r="K10" s="309" t="str">
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="L10" s="309"/>
-      <c r="M10" s="309"/>
-      <c r="N10" s="309"/>
-      <c r="O10" s="309"/>
-    </row>
-    <row r="11" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B11" s="305"/>
-      <c r="C11" s="200" t="inlineStr">
+      <c r="L10" s="308"/>
+      <c r="M10" s="308"/>
+      <c r="N10" s="308"/>
+      <c r="O10" s="308"/>
+    </row>
+    <row r="11" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B11" s="304"/>
+      <c r="C11" s="199" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Model</t>
           </r>
         </is>
       </c>
-      <c r="D11" s="311"/>
-      <c r="E11" s="312"/>
-      <c r="F11" s="313"/>
-      <c r="G11" s="311"/>
-      <c r="H11" s="200" t="inlineStr">
+      <c r="D11" s="310"/>
+      <c r="E11" s="311"/>
+      <c r="F11" s="312"/>
+      <c r="G11" s="310"/>
+      <c r="H11" s="199" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Chassis No.</t>
           </r>
         </is>
       </c>
-      <c r="I11" s="313"/>
-      <c r="J11" s="311"/>
-      <c r="K11" s="312"/>
-      <c r="L11" s="313"/>
-      <c r="M11" s="313"/>
-      <c r="N11" s="313"/>
-      <c r="O11" s="313"/>
-    </row>
-    <row r="12" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B12" s="305"/>
-      <c r="C12" s="181" t="inlineStr">
+      <c r="I11" s="312"/>
+      <c r="J11" s="310"/>
+      <c r="K11" s="311"/>
+      <c r="L11" s="312"/>
+      <c r="M11" s="312"/>
+      <c r="N11" s="312"/>
+      <c r="O11" s="312"/>
+    </row>
+    <row r="12" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B12" s="304"/>
+      <c r="C12" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">원동기형식</t>
           </r>
         </is>
       </c>
-      <c r="D12" s="305"/>
-      <c r="E12" s="185" t="str">
+      <c r="D12" s="304"/>
+      <c r="E12" s="184" t="str">
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
-      <c r="G12" s="305"/>
-      <c r="H12" s="181" t="inlineStr">
+      <c r="G12" s="304"/>
+      <c r="H12" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">모델연도</t>
           </r>
         </is>
       </c>
-      <c r="J12" s="305"/>
-      <c r="K12" s="184" t="str">
+      <c r="J12" s="304"/>
+      <c r="K12" s="183" t="str">
         <f>구매리스트!D6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B13" s="305"/>
-      <c r="C13" s="181" t="inlineStr">
+    <row r="13" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B13" s="304"/>
+      <c r="C13" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Type of Engine</t>
           </r>
         </is>
       </c>
-      <c r="D13" s="305"/>
-      <c r="E13" s="306"/>
-      <c r="G13" s="305"/>
-      <c r="H13" s="181" t="inlineStr">
+      <c r="D13" s="304"/>
+      <c r="E13" s="305"/>
+      <c r="G13" s="304"/>
+      <c r="H13" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Model Year</t>
           </r>
         </is>
       </c>
-      <c r="J13" s="305"/>
-      <c r="K13" s="306"/>
-    </row>
-    <row r="14" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B14" s="305"/>
-      <c r="C14" s="179" t="inlineStr">
+      <c r="J13" s="304"/>
+      <c r="K13" s="305"/>
+    </row>
+    <row r="14" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B14" s="304"/>
+      <c r="C14" s="178" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">제원관리번호</t>
           </r>
         </is>
       </c>
-      <c r="D14" s="314"/>
-      <c r="E14" s="315" t="str">
+      <c r="D14" s="313"/>
+      <c r="E14" s="314" t="str">
         <f>구매리스트!G5</f>
         <v>0</v>
       </c>
-      <c r="F14" s="316"/>
-      <c r="G14" s="314"/>
-      <c r="H14" s="317" t="inlineStr">
+      <c r="F14" s="315"/>
+      <c r="G14" s="313"/>
+      <c r="H14" s="316" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">용도
@@ -10206,141 +10229,141 @@
           </r>
         </is>
       </c>
-      <c r="I14" s="316"/>
-      <c r="J14" s="314"/>
-      <c r="K14" s="318" t="inlineStr">
+      <c r="I14" s="315"/>
+      <c r="J14" s="313"/>
+      <c r="K14" s="317" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자가용</t>
           </r>
         </is>
       </c>
-      <c r="L14" s="316"/>
-      <c r="M14" s="316"/>
-      <c r="N14" s="316"/>
-      <c r="O14" s="316"/>
-    </row>
-    <row r="15" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="B15" s="305"/>
-      <c r="C15" s="181" t="inlineStr">
+      <c r="L14" s="315"/>
+      <c r="M14" s="315"/>
+      <c r="N14" s="315"/>
+      <c r="O14" s="315"/>
+    </row>
+    <row r="15" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="B15" s="304"/>
+      <c r="C15" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Specification</t>
           </r>
         </is>
       </c>
-      <c r="D15" s="305"/>
-      <c r="E15" s="306"/>
-      <c r="G15" s="305"/>
-      <c r="H15" s="306"/>
-      <c r="J15" s="305"/>
-      <c r="K15" s="306"/>
-    </row>
-    <row r="16" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="B16" s="305"/>
-      <c r="C16" s="180" t="inlineStr">
+      <c r="D15" s="304"/>
+      <c r="E15" s="305"/>
+      <c r="G15" s="304"/>
+      <c r="H15" s="305"/>
+      <c r="J15" s="304"/>
+      <c r="K15" s="305"/>
+    </row>
+    <row r="16" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="B16" s="304"/>
+      <c r="C16" s="179" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Management no.</t>
           </r>
         </is>
       </c>
-      <c r="D16" s="319"/>
-      <c r="E16" s="320"/>
-      <c r="F16" s="321"/>
-      <c r="G16" s="319"/>
-      <c r="H16" s="320"/>
-      <c r="I16" s="321"/>
-      <c r="J16" s="319"/>
-      <c r="K16" s="320"/>
-      <c r="L16" s="321"/>
-      <c r="M16" s="321"/>
-      <c r="N16" s="321"/>
-      <c r="O16" s="321"/>
-    </row>
-    <row r="17" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B17" s="305"/>
-      <c r="C17" s="181" t="inlineStr">
+      <c r="D16" s="318"/>
+      <c r="E16" s="319"/>
+      <c r="F16" s="320"/>
+      <c r="G16" s="318"/>
+      <c r="H16" s="319"/>
+      <c r="I16" s="320"/>
+      <c r="J16" s="318"/>
+      <c r="K16" s="319"/>
+      <c r="L16" s="320"/>
+      <c r="M16" s="320"/>
+      <c r="N16" s="320"/>
+      <c r="O16" s="320"/>
+    </row>
+    <row r="17" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B17" s="304"/>
+      <c r="C17" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">최초등록일</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="305"/>
-      <c r="E17" s="188" t="str">
+      <c r="D17" s="304"/>
+      <c r="E17" s="187" t="str">
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
-      <c r="G17" s="305"/>
-      <c r="H17" s="181" t="inlineStr">
+      <c r="G17" s="304"/>
+      <c r="H17" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">사업용사용기간</t>
           </r>
         </is>
       </c>
-      <c r="J17" s="305"/>
-      <c r="K17" s="210" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="18" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="B18" s="305"/>
-      <c r="C18" s="181" t="inlineStr">
+      <c r="J17" s="304"/>
+      <c r="K17" s="209" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="B18" s="304"/>
+      <c r="C18" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Dete of initial</t>
           </r>
         </is>
       </c>
-      <c r="D18" s="305"/>
-      <c r="E18" s="306"/>
-      <c r="G18" s="305"/>
-      <c r="H18" s="181" t="inlineStr">
+      <c r="D18" s="304"/>
+      <c r="E18" s="305"/>
+      <c r="G18" s="304"/>
+      <c r="H18" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Period of</t>
           </r>
         </is>
       </c>
-      <c r="J18" s="305"/>
-      <c r="K18" s="306"/>
-    </row>
-    <row r="19" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A19" s="253"/>
-      <c r="B19" s="322"/>
-      <c r="C19" s="183" t="inlineStr">
+      <c r="J18" s="304"/>
+      <c r="K18" s="305"/>
+    </row>
+    <row r="19" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A19" s="252"/>
+      <c r="B19" s="321"/>
+      <c r="C19" s="182" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Registraton</t>
           </r>
         </is>
       </c>
-      <c r="D19" s="322"/>
-      <c r="E19" s="323"/>
-      <c r="F19" s="253"/>
-      <c r="G19" s="322"/>
-      <c r="H19" s="183" t="inlineStr">
+      <c r="D19" s="321"/>
+      <c r="E19" s="322"/>
+      <c r="F19" s="252"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="182" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Business Usage</t>
           </r>
         </is>
       </c>
-      <c r="I19" s="253"/>
-      <c r="J19" s="322"/>
-      <c r="K19" s="323"/>
-      <c r="L19" s="253"/>
-      <c r="M19" s="253"/>
-      <c r="N19" s="253"/>
-      <c r="O19" s="253"/>
-    </row>
-    <row r="20" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
+      <c r="I19" s="252"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="322"/>
+      <c r="L19" s="252"/>
+      <c r="M19" s="252"/>
+      <c r="N19" s="252"/>
+      <c r="O19" s="252"/>
+    </row>
+    <row r="20" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A20" s="84"/>
       <c r="B20" s="84"/>
       <c r="C20" s="84"/>
@@ -10357,74 +10380,74 @@
       <c r="N20" s="84"/>
       <c r="O20" s="84"/>
     </row>
-    <row r="21" spans="1:15" customHeight="1" ht="33.75" s="246" customFormat="1">
-      <c r="A21" s="209" t="inlineStr">
+    <row r="21" spans="1:15" customHeight="1" ht="33.75" s="245" customFormat="1">
+      <c r="A21" s="208" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">소유자</t>
           </r>
         </is>
       </c>
-      <c r="B21" s="304"/>
-      <c r="C21" s="207" t="inlineStr">
+      <c r="B21" s="303"/>
+      <c r="C21" s="206" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">성명 (명칭)</t>
           </r>
         </is>
       </c>
-      <c r="D21" s="304"/>
-      <c r="E21" s="324" t="inlineStr">
+      <c r="D21" s="303"/>
+      <c r="E21" s="323" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">주식회사싼카</t>
           </r>
         </is>
       </c>
-      <c r="F21" s="251"/>
-      <c r="G21" s="304"/>
-      <c r="H21" s="186" t="inlineStr">
+      <c r="F21" s="250"/>
+      <c r="G21" s="303"/>
+      <c r="H21" s="185" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">생년월일(법인등록번호)</t>
           </r>
         </is>
       </c>
-      <c r="I21" s="251"/>
-      <c r="J21" s="304"/>
-      <c r="K21" s="324" t="inlineStr">
+      <c r="I21" s="250"/>
+      <c r="J21" s="303"/>
+      <c r="K21" s="323" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">120111-0922270</t>
           </r>
         </is>
       </c>
-      <c r="L21" s="251"/>
-      <c r="M21" s="251"/>
-      <c r="N21" s="251"/>
-      <c r="O21" s="304"/>
-    </row>
-    <row r="22" spans="1:15" customHeight="1" ht="33.75" s="246" customFormat="1">
-      <c r="A22" s="212" t="inlineStr">
+      <c r="L21" s="250"/>
+      <c r="M21" s="250"/>
+      <c r="N21" s="250"/>
+      <c r="O21" s="303"/>
+    </row>
+    <row r="22" spans="1:15" customHeight="1" ht="33.75" s="245" customFormat="1">
+      <c r="A22" s="211" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Owner</t>
           </r>
         </is>
       </c>
-      <c r="B22" s="322"/>
-      <c r="C22" s="183" t="inlineStr">
+      <c r="B22" s="321"/>
+      <c r="C22" s="182" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Name</t>
           </r>
         </is>
       </c>
-      <c r="D22" s="322"/>
-      <c r="E22" s="323"/>
-      <c r="F22" s="253"/>
-      <c r="G22" s="322"/>
-      <c r="H22" s="187" t="inlineStr">
+      <c r="D22" s="321"/>
+      <c r="E22" s="322"/>
+      <c r="F22" s="252"/>
+      <c r="G22" s="321"/>
+      <c r="H22" s="186" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Date of birth
@@ -10432,15 +10455,15 @@
           </r>
         </is>
       </c>
-      <c r="I22" s="253"/>
-      <c r="J22" s="322"/>
-      <c r="K22" s="323"/>
-      <c r="L22" s="253"/>
-      <c r="M22" s="253"/>
-      <c r="N22" s="253"/>
-      <c r="O22" s="322"/>
-    </row>
-    <row r="23" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
+      <c r="I22" s="252"/>
+      <c r="J22" s="321"/>
+      <c r="K22" s="322"/>
+      <c r="L22" s="252"/>
+      <c r="M22" s="252"/>
+      <c r="N22" s="252"/>
+      <c r="O22" s="321"/>
+    </row>
+    <row r="23" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A23" s="84"/>
       <c r="B23" s="84"/>
       <c r="C23" s="84"/>
@@ -10457,98 +10480,98 @@
       <c r="N23" s="84"/>
       <c r="O23" s="84"/>
     </row>
-    <row r="24" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A24" s="213" t="inlineStr">
+    <row r="24" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A24" s="212" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일</t>
           </r>
         </is>
       </c>
-      <c r="B24" s="251"/>
-      <c r="C24" s="251"/>
-      <c r="D24" s="304"/>
-      <c r="E24" s="325" t="str">
+      <c r="B24" s="250"/>
+      <c r="C24" s="250"/>
+      <c r="D24" s="303"/>
+      <c r="E24" s="324" t="str">
         <f>구매리스트!B7</f>
         <v>0</v>
       </c>
-      <c r="F24" s="251"/>
-      <c r="G24" s="304"/>
-      <c r="H24" s="207" t="inlineStr">
+      <c r="F24" s="250"/>
+      <c r="G24" s="303"/>
+      <c r="H24" s="206" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">증명서 용도</t>
           </r>
         </is>
       </c>
-      <c r="I24" s="251"/>
-      <c r="J24" s="304"/>
-      <c r="K24" s="326" t="inlineStr">
+      <c r="I24" s="250"/>
+      <c r="J24" s="303"/>
+      <c r="K24" s="325" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">증명용</t>
           </r>
         </is>
       </c>
-      <c r="L24" s="251"/>
-      <c r="M24" s="251"/>
-      <c r="N24" s="251"/>
-      <c r="O24" s="304"/>
-    </row>
-    <row r="25" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A25" s="215" t="inlineStr">
+      <c r="L24" s="250"/>
+      <c r="M24" s="250"/>
+      <c r="N24" s="250"/>
+      <c r="O24" s="303"/>
+    </row>
+    <row r="25" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A25" s="214" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Date of De-reglstration</t>
           </r>
         </is>
       </c>
-      <c r="B25" s="327"/>
-      <c r="C25" s="327"/>
-      <c r="D25" s="328"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="327"/>
-      <c r="G25" s="328"/>
-      <c r="H25" s="216" t="inlineStr">
+      <c r="B25" s="326"/>
+      <c r="C25" s="326"/>
+      <c r="D25" s="327"/>
+      <c r="E25" s="328"/>
+      <c r="F25" s="326"/>
+      <c r="G25" s="327"/>
+      <c r="H25" s="215" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Use of Certificate</t>
           </r>
         </is>
       </c>
-      <c r="I25" s="327"/>
-      <c r="J25" s="328"/>
-      <c r="K25" s="329"/>
-      <c r="L25" s="327"/>
-      <c r="M25" s="327"/>
-      <c r="N25" s="327"/>
-      <c r="O25" s="328"/>
-    </row>
-    <row r="26" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A26" s="214" t="inlineStr">
+      <c r="I25" s="326"/>
+      <c r="J25" s="327"/>
+      <c r="K25" s="328"/>
+      <c r="L25" s="326"/>
+      <c r="M25" s="326"/>
+      <c r="N25" s="326"/>
+      <c r="O25" s="327"/>
+    </row>
+    <row r="26" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A26" s="213" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록구분</t>
           </r>
         </is>
       </c>
-      <c r="D26" s="305"/>
-      <c r="E26" s="217" t="inlineStr">
+      <c r="D26" s="304"/>
+      <c r="E26" s="216" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">수출예정(수출말소)</t>
           </r>
         </is>
       </c>
-      <c r="G26" s="305"/>
-      <c r="H26" s="181" t="inlineStr">
+      <c r="G26" s="304"/>
+      <c r="H26" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">권리관계여부</t>
           </r>
         </is>
       </c>
-      <c r="J26" s="305"/>
+      <c r="J26" s="304"/>
       <c r="K26" s="94" t="inlineStr">
         <is>
           <r>
@@ -10575,29 +10598,29 @@
         </is>
       </c>
     </row>
-    <row r="27" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A27" s="211" t="inlineStr">
+    <row r="27" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A27" s="210" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reason for De-registration</t>
           </r>
         </is>
       </c>
-      <c r="B27" s="253"/>
-      <c r="C27" s="253"/>
-      <c r="D27" s="322"/>
-      <c r="E27" s="323"/>
-      <c r="F27" s="253"/>
-      <c r="G27" s="322"/>
-      <c r="H27" s="183" t="inlineStr">
+      <c r="B27" s="252"/>
+      <c r="C27" s="252"/>
+      <c r="D27" s="321"/>
+      <c r="E27" s="322"/>
+      <c r="F27" s="252"/>
+      <c r="G27" s="321"/>
+      <c r="H27" s="182" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Relation of Rights</t>
           </r>
         </is>
       </c>
-      <c r="I27" s="253"/>
-      <c r="J27" s="322"/>
+      <c r="I27" s="252"/>
+      <c r="J27" s="321"/>
       <c r="K27" s="98" t="inlineStr">
         <is>
           <r>
@@ -10624,7 +10647,7 @@
         </is>
       </c>
     </row>
-    <row r="28" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
+    <row r="28" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A28" s="77"/>
       <c r="B28" s="77"/>
       <c r="C28" s="77"/>
@@ -10641,8 +10664,8 @@
       <c r="N28" s="77"/>
       <c r="O28" s="77"/>
     </row>
-    <row r="29" spans="1:15" customHeight="1" ht="32.25" s="246" customFormat="1">
-      <c r="A29" s="218" t="inlineStr">
+    <row r="29" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
+      <c r="A29" s="217" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">「자동차관리법」제13조 및 「자동차등록규칙」제40조에 따라 말소등록 되었음을 증명합니다.</t>
@@ -10650,8 +10673,8 @@
         </is>
       </c>
     </row>
-    <row r="30" spans="1:15" customHeight="1" ht="32.25" s="246" customFormat="1">
-      <c r="A30" s="218" t="inlineStr">
+    <row r="30" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
+      <c r="A30" s="217" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  This is to certify that the above vehicle was de-registered in accordance with Article 13 of the Motor</t>
@@ -10659,8 +10682,8 @@
         </is>
       </c>
     </row>
-    <row r="31" spans="1:15" customHeight="1" ht="32.25" s="246" customFormat="1">
-      <c r="A31" s="218" t="inlineStr">
+    <row r="31" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
+      <c r="A31" s="217" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Vehicle Management Act and Article 40 of the Motor Vehicle Registration Rules.</t>
@@ -10668,7 +10691,7 @@
         </is>
       </c>
     </row>
-    <row r="32" spans="1:15" customHeight="1" ht="9.75" s="246" customFormat="1">
+    <row r="32" spans="1:15" customHeight="1" ht="9.75" s="245" customFormat="1">
       <c r="A32" s="77"/>
       <c r="B32" s="77"/>
       <c r="C32" s="77"/>
@@ -10685,7 +10708,7 @@
       <c r="N32" s="77"/>
       <c r="O32" s="77"/>
     </row>
-    <row r="33" spans="1:15" customHeight="1" ht="35.25" s="246" customFormat="1">
+    <row r="33" spans="1:15" customHeight="1" ht="35.25" s="245" customFormat="1">
       <c r="A33" s="77" t="inlineStr">
         <is>
           <r>
@@ -10704,27 +10727,29 @@
       <c r="D33" s="77"/>
       <c r="E33" s="77"/>
       <c r="F33" s="77"/>
-      <c r="G33" s="191" t="inlineStr">
+      <c r="G33" s="190" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">발행 연월일 Date of Issue :</t>
           </r>
         </is>
       </c>
-      <c r="K33" s="219" t="str">
+      <c r="K33" s="218" t="str">
         <f>E24</f>
         <v>0</v>
       </c>
       <c r="O33" s="77"/>
     </row>
-    <row r="34" spans="1:15" customHeight="1" ht="85.5" s="246" customFormat="1">
+    <row r="34" spans="1:15" customHeight="1" ht="85.5" s="245" customFormat="1">
       <c r="A34" s="77"/>
       <c r="B34" s="77"/>
       <c r="C34" s="77"/>
       <c r="D34" s="77"/>
       <c r="E34" s="77"/>
       <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
+      <c r="G34" s="398" t="s">
+        <v>104</v>
+      </c>
       <c r="H34" s="77"/>
       <c r="I34" s="77"/>
       <c r="J34" s="77"/>
@@ -10734,8 +10759,8 @@
       <c r="N34" s="78"/>
       <c r="O34" s="77"/>
     </row>
-    <row r="35" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A35" s="191" t="inlineStr">
+    <row r="35" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A35" s="190" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Speial Metropolitan City Mayor ' Metropolitan City Mayor'</t>
@@ -10745,8 +10770,8 @@
       <c r="N35" s="77"/>
       <c r="O35" s="77"/>
     </row>
-    <row r="36" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A36" s="191" t="inlineStr">
+    <row r="36" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A36" s="190" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Special Self-Governing City Mayor ' Do Governor ' Special Self-Governign Province Governor</t>
@@ -10756,8 +10781,8 @@
       <c r="N36" s="78"/>
       <c r="O36" s="77"/>
     </row>
-    <row r="37" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A37" s="191" t="inlineStr">
+    <row r="37" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A37" s="190" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(The Head of a Si / Gun / Gu</t>
@@ -10767,54 +10792,54 @@
       <c r="N37" s="86"/>
       <c r="O37" s="87"/>
     </row>
-    <row r="38" spans="1:15" customHeight="1" ht="24.95" s="246" customFormat="1">
-      <c r="A38" s="220" t="inlineStr">
+    <row r="38" spans="1:15" customHeight="1" ht="24.95" s="245" customFormat="1">
+      <c r="A38" s="219" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">유의사항</t>
           </r>
         </is>
       </c>
-      <c r="B38" s="330"/>
-      <c r="C38" s="330"/>
-      <c r="D38" s="330"/>
-      <c r="E38" s="330"/>
-      <c r="F38" s="330"/>
-      <c r="G38" s="330"/>
-      <c r="H38" s="330"/>
-      <c r="I38" s="330"/>
-      <c r="J38" s="330"/>
-      <c r="K38" s="330"/>
-      <c r="L38" s="330"/>
-      <c r="M38" s="330"/>
-      <c r="N38" s="330"/>
-      <c r="O38" s="330"/>
-    </row>
-    <row r="39" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A39" s="221" t="inlineStr">
+      <c r="B38" s="329"/>
+      <c r="C38" s="329"/>
+      <c r="D38" s="329"/>
+      <c r="E38" s="329"/>
+      <c r="F38" s="329"/>
+      <c r="G38" s="329"/>
+      <c r="H38" s="329"/>
+      <c r="I38" s="329"/>
+      <c r="J38" s="329"/>
+      <c r="K38" s="329"/>
+      <c r="L38" s="329"/>
+      <c r="M38" s="329"/>
+      <c r="N38" s="329"/>
+      <c r="O38" s="329"/>
+    </row>
+    <row r="39" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A39" s="220" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1. 말소등록된 자동차를 다시 등록하여 사용하려는 경우에는 「자동차등록령」 제20조 및 아래 표의 구분에 따른 기간에 신규등록을 신청해야 하며,그 </t>
           </r>
         </is>
       </c>
-      <c r="B39" s="331"/>
-      <c r="C39" s="331"/>
-      <c r="D39" s="331"/>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
-      <c r="G39" s="331"/>
-      <c r="H39" s="331"/>
-      <c r="I39" s="331"/>
-      <c r="J39" s="331"/>
-      <c r="K39" s="331"/>
-      <c r="L39" s="331"/>
-      <c r="M39" s="331"/>
-      <c r="N39" s="331"/>
-      <c r="O39" s="331"/>
-    </row>
-    <row r="40" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A40" s="192" t="inlineStr">
+      <c r="B39" s="330"/>
+      <c r="C39" s="330"/>
+      <c r="D39" s="330"/>
+      <c r="E39" s="330"/>
+      <c r="F39" s="330"/>
+      <c r="G39" s="330"/>
+      <c r="H39" s="330"/>
+      <c r="I39" s="330"/>
+      <c r="J39" s="330"/>
+      <c r="K39" s="330"/>
+      <c r="L39" s="330"/>
+      <c r="M39" s="330"/>
+      <c r="N39" s="330"/>
+      <c r="O39" s="330"/>
+    </row>
+    <row r="40" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A40" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    신청기간을 경과한 때에는 「자동차관리법」제84조제4항제7호에 따라 100만원 이하의 과태료를 납부해야 합니다. </t>
@@ -10822,8 +10847,8 @@
         </is>
       </c>
     </row>
-    <row r="41" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A41" s="192" t="inlineStr">
+    <row r="41" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A41" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2. 말소등록 당시에 압류 및 저당권 등이 등록된 자동차는 「자동차관리법」제13조제10항 후단에 따라 해당 관리관계가 소멸되었음을 「자동차등록규칙」</t>
@@ -10831,8 +10856,8 @@
         </is>
       </c>
     </row>
-    <row r="42" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A42" s="192" t="inlineStr">
+    <row r="42" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A42" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    제27조제3항에 따라 증명한 경우에만 신규등록을 신청할 수 있습니다. </t>
@@ -10840,36 +10865,36 @@
         </is>
       </c>
     </row>
-    <row r="43" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A43" s="222" t="inlineStr">
+    <row r="43" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A43" s="221" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록 사유</t>
           </r>
         </is>
       </c>
-      <c r="B43" s="332"/>
-      <c r="C43" s="332"/>
-      <c r="D43" s="332"/>
-      <c r="E43" s="332"/>
-      <c r="F43" s="332"/>
-      <c r="G43" s="332"/>
-      <c r="H43" s="332"/>
-      <c r="I43" s="332"/>
-      <c r="J43" s="333"/>
-      <c r="K43" s="223" t="inlineStr">
+      <c r="B43" s="331"/>
+      <c r="C43" s="331"/>
+      <c r="D43" s="331"/>
+      <c r="E43" s="331"/>
+      <c r="F43" s="331"/>
+      <c r="G43" s="331"/>
+      <c r="H43" s="331"/>
+      <c r="I43" s="331"/>
+      <c r="J43" s="332"/>
+      <c r="K43" s="222" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">신규등록 신청 기간</t>
           </r>
         </is>
       </c>
-      <c r="L43" s="332"/>
-      <c r="M43" s="332"/>
-      <c r="N43" s="332"/>
-      <c r="O43" s="333"/>
-    </row>
-    <row r="44" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
+      <c r="L43" s="331"/>
+      <c r="M43" s="331"/>
+      <c r="N43" s="331"/>
+      <c r="O43" s="332"/>
+    </row>
+    <row r="44" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="76" t="inlineStr">
         <is>
           <r>
@@ -10886,19 +10911,19 @@
       <c r="H44" s="76"/>
       <c r="I44" s="76"/>
       <c r="J44" s="76"/>
-      <c r="K44" s="182" t="inlineStr">
+      <c r="K44" s="181" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 3개월 이내</t>
           </r>
         </is>
       </c>
-      <c r="L44" s="309"/>
-      <c r="M44" s="309"/>
-      <c r="N44" s="309"/>
-      <c r="O44" s="334"/>
-    </row>
-    <row r="45" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
+      <c r="L44" s="308"/>
+      <c r="M44" s="308"/>
+      <c r="N44" s="308"/>
+      <c r="O44" s="333"/>
+    </row>
+    <row r="45" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="76" t="inlineStr">
         <is>
           <r>
@@ -10915,163 +10940,163 @@
       <c r="H45" s="76"/>
       <c r="I45" s="76"/>
       <c r="J45" s="76"/>
-      <c r="K45" s="335"/>
-      <c r="O45" s="336"/>
-    </row>
-    <row r="46" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A46" s="224" t="inlineStr">
+      <c r="K45" s="334"/>
+      <c r="O45" s="335"/>
+    </row>
+    <row r="46" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A46" s="223" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2. 자동차를 교육,연구의 목적으로 사용하는 등 「자동차등록령」제31조제5항에 해당하는 사유로 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="K46" s="335"/>
-      <c r="O46" s="336"/>
-    </row>
-    <row r="47" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A47" s="192" t="inlineStr">
+      <c r="K46" s="334"/>
+      <c r="O46" s="335"/>
+    </row>
+    <row r="47" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A47" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3. 자동차의 차대[차대가 없는 자동차의 경우에는 차체(車體)를 말합니다. 이하 이 호에서 같습니다]가 등록원부상의</t>
           </r>
         </is>
       </c>
-      <c r="K47" s="335"/>
-      <c r="O47" s="336"/>
-    </row>
-    <row r="48" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A48" s="192" t="inlineStr">
+      <c r="K47" s="334"/>
+      <c r="O47" s="335"/>
+    </row>
+    <row r="48" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A48" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    차대와 달라 직권으로 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="K48" s="335"/>
-      <c r="O48" s="336"/>
-    </row>
-    <row r="49" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A49" s="192" t="inlineStr">
+      <c r="K48" s="334"/>
+      <c r="O48" s="335"/>
+    </row>
+    <row r="49" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A49" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4. 속임수나 그밖의 부정한 방법으로 등록되어 직권으로 말소등록된경우</t>
           </r>
         </is>
       </c>
-      <c r="B49" s="246"/>
-      <c r="K49" s="335"/>
-      <c r="O49" s="336"/>
-    </row>
-    <row r="50" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A50" s="196" t="inlineStr">
+      <c r="B49" s="245"/>
+      <c r="K49" s="334"/>
+      <c r="O49" s="335"/>
+    </row>
+    <row r="50" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A50" s="195" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">5. 자동차를 제작.조립 또는 수입하는 자(이들로부터 자동차의 판매위탁을 받은 자를 포함합니다)에게 반품(「자동차</t>
           </r>
         </is>
       </c>
-      <c r="B50" s="309"/>
-      <c r="C50" s="309"/>
-      <c r="D50" s="309"/>
-      <c r="E50" s="309"/>
-      <c r="F50" s="309"/>
-      <c r="G50" s="309"/>
-      <c r="H50" s="309"/>
-      <c r="I50" s="309"/>
-      <c r="J50" s="309"/>
-      <c r="K50" s="337" t="inlineStr">
+      <c r="B50" s="308"/>
+      <c r="C50" s="308"/>
+      <c r="D50" s="308"/>
+      <c r="E50" s="308"/>
+      <c r="F50" s="308"/>
+      <c r="G50" s="308"/>
+      <c r="H50" s="308"/>
+      <c r="I50" s="308"/>
+      <c r="J50" s="308"/>
+      <c r="K50" s="336" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 6개월 이내</t>
           </r>
         </is>
       </c>
-      <c r="L50" s="309"/>
-      <c r="M50" s="309"/>
-      <c r="N50" s="309"/>
-      <c r="O50" s="334"/>
-    </row>
-    <row r="51" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A51" s="193" t="inlineStr">
+      <c r="L50" s="308"/>
+      <c r="M50" s="308"/>
+      <c r="N50" s="308"/>
+      <c r="O50" s="333"/>
+    </row>
+    <row r="51" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A51" s="192" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">     관리법」제47조의2의 교환 또는 환불 요구에 따라 반품된 경우를 포함합니다)하여 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="B51" s="313"/>
-      <c r="C51" s="313"/>
-      <c r="D51" s="313"/>
-      <c r="E51" s="313"/>
-      <c r="F51" s="313"/>
-      <c r="G51" s="313"/>
-      <c r="H51" s="313"/>
-      <c r="I51" s="313"/>
-      <c r="J51" s="313"/>
-      <c r="K51" s="338"/>
-      <c r="L51" s="313"/>
-      <c r="M51" s="313"/>
-      <c r="N51" s="313"/>
-      <c r="O51" s="339"/>
-    </row>
-    <row r="52" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A52" s="194" t="inlineStr">
+      <c r="B51" s="312"/>
+      <c r="C51" s="312"/>
+      <c r="D51" s="312"/>
+      <c r="E51" s="312"/>
+      <c r="F51" s="312"/>
+      <c r="G51" s="312"/>
+      <c r="H51" s="312"/>
+      <c r="I51" s="312"/>
+      <c r="J51" s="312"/>
+      <c r="K51" s="337"/>
+      <c r="L51" s="312"/>
+      <c r="M51" s="312"/>
+      <c r="N51" s="312"/>
+      <c r="O51" s="338"/>
+    </row>
+    <row r="52" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A52" s="193" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6. 수출로 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="B52" s="340"/>
-      <c r="C52" s="340"/>
-      <c r="D52" s="340"/>
-      <c r="E52" s="340"/>
-      <c r="F52" s="340"/>
-      <c r="G52" s="340"/>
-      <c r="H52" s="340"/>
-      <c r="I52" s="340"/>
-      <c r="J52" s="340"/>
-      <c r="K52" s="195" t="inlineStr">
+      <c r="B52" s="339"/>
+      <c r="C52" s="339"/>
+      <c r="D52" s="339"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
+      <c r="G52" s="339"/>
+      <c r="H52" s="339"/>
+      <c r="I52" s="339"/>
+      <c r="J52" s="339"/>
+      <c r="K52" s="194" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 1년 이내</t>
           </r>
         </is>
       </c>
-      <c r="L52" s="340"/>
-      <c r="M52" s="340"/>
-      <c r="N52" s="340"/>
-      <c r="O52" s="341"/>
-    </row>
-    <row r="53" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A53" s="190" t="inlineStr">
+      <c r="L52" s="339"/>
+      <c r="M52" s="339"/>
+      <c r="N52" s="339"/>
+      <c r="O52" s="340"/>
+    </row>
+    <row r="53" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A53" s="189" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">7. 도난,횡령 또는 편취 당하여 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="B53" s="253"/>
-      <c r="C53" s="253"/>
-      <c r="D53" s="253"/>
-      <c r="E53" s="253"/>
-      <c r="F53" s="253"/>
-      <c r="G53" s="253"/>
-      <c r="H53" s="253"/>
-      <c r="I53" s="253"/>
-      <c r="J53" s="342"/>
-      <c r="K53" s="189" t="inlineStr">
+      <c r="B53" s="252"/>
+      <c r="C53" s="252"/>
+      <c r="D53" s="252"/>
+      <c r="E53" s="252"/>
+      <c r="F53" s="252"/>
+      <c r="G53" s="252"/>
+      <c r="H53" s="252"/>
+      <c r="I53" s="252"/>
+      <c r="J53" s="341"/>
+      <c r="K53" s="188" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">해당 자동차를 회수한 날부터 3개월 이내</t>
           </r>
         </is>
       </c>
-      <c r="L53" s="253"/>
-      <c r="M53" s="253"/>
-      <c r="N53" s="253"/>
-      <c r="O53" s="253"/>
+      <c r="L53" s="252"/>
+      <c r="M53" s="252"/>
+      <c r="N53" s="252"/>
+      <c r="O53" s="252"/>
     </row>
     <row r="54" spans="1:15" customHeight="1" ht="20.25" s="89" customFormat="1">
       <c r="A54" s="88" t="inlineStr">
@@ -11106,7 +11131,7 @@
       </c>
     </row>
     <row r="56" spans="1:15">
-      <c r="A56" s="246"/>
+      <c r="A56" s="245"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -11199,6 +11224,7 @@
     <mergeCell ref="K50:O51"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="H25:J25"/>
+    <mergeCell ref="G34:K34"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.31496062992126" right="0.23622047244094" top="0.45" bottom="0.51181102362205" header="0.31496062992126" footer="0.31496062992126"/>
@@ -11226,68 +11252,68 @@
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="4.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="21.625" customWidth="true" style="246"/>
-    <col min="3" max="3" width="7.5" customWidth="true" style="246"/>
-    <col min="4" max="4" width="23.625" customWidth="true" style="246"/>
-    <col min="5" max="5" width="7.75" customWidth="true" style="246"/>
-    <col min="6" max="6" width="2.125" customWidth="true" style="246"/>
-    <col min="7" max="7" width="12.25" customWidth="true" style="246"/>
-    <col min="8" max="8" width="13.75" customWidth="true" style="246"/>
-    <col min="9" max="9" width="13.25" customWidth="true" style="246"/>
+    <col min="1" max="1" width="4.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="21.625" customWidth="true" style="245"/>
+    <col min="3" max="3" width="7.5" customWidth="true" style="245"/>
+    <col min="4" max="4" width="23.625" customWidth="true" style="245"/>
+    <col min="5" max="5" width="7.75" customWidth="true" style="245"/>
+    <col min="6" max="6" width="2.125" customWidth="true" style="245"/>
+    <col min="7" max="7" width="12.25" customWidth="true" style="245"/>
+    <col min="8" max="8" width="13.75" customWidth="true" style="245"/>
+    <col min="9" max="9" width="13.25" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customHeight="1" ht="47.25" s="246" customFormat="1">
-      <c r="A1" s="343" t="inlineStr">
+    <row r="1" spans="1:10" customHeight="1" ht="47.25" s="245" customFormat="1">
+      <c r="A1" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL INVOICE</t>
           </r>
         </is>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="255"/>
-      <c r="I1" s="256"/>
-    </row>
-    <row r="2" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A2" s="344" t="inlineStr">
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="255"/>
+    </row>
+    <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
           </r>
         </is>
       </c>
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="252"/>
-      <c r="E2" s="225" t="inlineStr">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="224" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reference No.      DFSU6646075</t>
           </r>
         </is>
       </c>
-      <c r="F2" s="251"/>
+      <c r="F2" s="250"/>
       <c r="G2" s="128" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
-      <c r="H2" s="345" t="inlineStr">
+      <c r="H2" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
           </r>
         </is>
       </c>
-      <c r="I2" s="252"/>
-    </row>
-    <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A3" s="346" t="inlineStr">
+      <c r="I2" s="251"/>
+    </row>
+    <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A3" s="345" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR LTD.,
@@ -11298,8 +11324,8 @@
           </r>
         </is>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="229" t="inlineStr">
+      <c r="D3" s="262"/>
+      <c r="E3" s="228" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reference code.   DFSU6646075</t>
@@ -11310,122 +11336,122 @@
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
-      <c r="H3" s="273"/>
-      <c r="I3" s="254"/>
-    </row>
-    <row r="4" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A4" s="272"/>
-      <c r="D4" s="263"/>
-      <c r="E4" s="347" t="inlineStr">
+      <c r="H3" s="272"/>
+      <c r="I3" s="253"/>
+    </row>
+    <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A4" s="271"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
           </r>
         </is>
       </c>
-      <c r="I4" s="263"/>
-    </row>
-    <row r="5" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A5" s="272"/>
-      <c r="D5" s="263"/>
-      <c r="E5" s="272"/>
-      <c r="I5" s="263"/>
-    </row>
-    <row r="6" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A6" s="272"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="348" t="inlineStr">
+      <c r="I4" s="262"/>
+    </row>
+    <row r="5" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A5" s="271"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="271"/>
+      <c r="I5" s="262"/>
+    </row>
+    <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A6" s="271"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
           </r>
         </is>
       </c>
-      <c r="I6" s="263"/>
-    </row>
-    <row r="7" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A7" s="273"/>
-      <c r="B7" s="253"/>
-      <c r="C7" s="253"/>
-      <c r="D7" s="254"/>
-      <c r="E7" s="348" t="inlineStr">
+      <c r="I6" s="262"/>
+    </row>
+    <row r="7" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A7" s="272"/>
+      <c r="B7" s="252"/>
+      <c r="C7" s="252"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
           </r>
         </is>
       </c>
-      <c r="I7" s="263"/>
-    </row>
-    <row r="8" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A8" s="344" t="inlineStr">
+      <c r="I7" s="262"/>
+    </row>
+    <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A8" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
           </r>
         </is>
       </c>
-      <c r="B8" s="251"/>
-      <c r="C8" s="251"/>
-      <c r="D8" s="252"/>
-      <c r="E8" s="349" t="inlineStr">
+      <c r="B8" s="250"/>
+      <c r="C8" s="250"/>
+      <c r="D8" s="251"/>
+      <c r="E8" s="348" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
           </r>
         </is>
       </c>
-      <c r="F8" s="253"/>
-      <c r="G8" s="253"/>
-      <c r="H8" s="253"/>
-      <c r="I8" s="254"/>
-    </row>
-    <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
-      <c r="A9" s="350" t="str">
+      <c r="F8" s="252"/>
+      <c r="G8" s="252"/>
+      <c r="H8" s="252"/>
+      <c r="I8" s="253"/>
+    </row>
+    <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
+      <c r="A9" s="349" t="str">
         <f>구매리스트!B14</f>
         <v>0</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="E9" s="235" t="inlineStr">
+      <c r="D9" s="262"/>
+      <c r="E9" s="234" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> *Remark</t>
           </r>
         </is>
       </c>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A10" s="272"/>
-      <c r="D10" s="263"/>
-      <c r="E10" s="226" t="inlineStr">
+      <c r="F9" s="250"/>
+      <c r="G9" s="250"/>
+      <c r="H9" s="250"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A10" s="271"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">8) No. &amp; date of invoice</t>
           </r>
         </is>
       </c>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="252"/>
-    </row>
-    <row r="11" spans="1:10" customHeight="1" ht="35.25" s="246" customFormat="1">
-      <c r="A11" s="273"/>
-      <c r="B11" s="253"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="254"/>
-      <c r="E11" s="227" t="str">
+      <c r="F10" s="250"/>
+      <c r="G10" s="250"/>
+      <c r="H10" s="250"/>
+      <c r="I10" s="251"/>
+    </row>
+    <row r="11" spans="1:10" customHeight="1" ht="35.25" s="245" customFormat="1">
+      <c r="A11" s="272"/>
+      <c r="B11" s="252"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="226" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
@@ -11434,151 +11460,151 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A12" s="344" t="inlineStr">
+    <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
           </r>
         </is>
       </c>
-      <c r="B12" s="251"/>
-      <c r="C12" s="251"/>
-      <c r="D12" s="252"/>
-      <c r="E12" s="344" t="inlineStr">
+      <c r="B12" s="250"/>
+      <c r="C12" s="250"/>
+      <c r="D12" s="251"/>
+      <c r="E12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
           </r>
         </is>
       </c>
-      <c r="F12" s="251"/>
-      <c r="G12" s="251"/>
-      <c r="H12" s="251"/>
-      <c r="I12" s="252"/>
-    </row>
-    <row r="13" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A13" s="351" t="inlineStr">
+      <c r="F12" s="250"/>
+      <c r="G12" s="250"/>
+      <c r="H12" s="250"/>
+      <c r="I12" s="251"/>
+    </row>
+    <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A13" s="350" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
           </r>
         </is>
       </c>
-      <c r="D13" s="263"/>
-      <c r="E13" s="230" t="inlineStr">
+      <c r="D13" s="262"/>
+      <c r="E13" s="229" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">TTR BASE</t>
           </r>
         </is>
       </c>
-      <c r="I13" s="263"/>
-    </row>
-    <row r="14" spans="1:10" customHeight="1" ht="9.75" s="246" customFormat="1">
-      <c r="A14" s="273"/>
-      <c r="B14" s="253"/>
-      <c r="C14" s="253"/>
-      <c r="D14" s="254"/>
-      <c r="E14" s="253"/>
-      <c r="F14" s="253"/>
-      <c r="G14" s="253"/>
-      <c r="H14" s="253"/>
-      <c r="I14" s="254"/>
-    </row>
-    <row r="15" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A15" s="344" t="inlineStr">
+      <c r="I13" s="262"/>
+    </row>
+    <row r="14" spans="1:10" customHeight="1" ht="9.75" s="245" customFormat="1">
+      <c r="A14" s="272"/>
+      <c r="B14" s="252"/>
+      <c r="C14" s="252"/>
+      <c r="D14" s="253"/>
+      <c r="E14" s="252"/>
+      <c r="F14" s="252"/>
+      <c r="G14" s="252"/>
+      <c r="H14" s="252"/>
+      <c r="I14" s="253"/>
+    </row>
+    <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
+      <c r="A15" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="252"/>
-      <c r="C15" s="226" t="inlineStr">
+      <c r="B15" s="251"/>
+      <c r="C15" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">5) Final Destination</t>
           </r>
         </is>
       </c>
-      <c r="D15" s="252"/>
-      <c r="E15" s="226" t="inlineStr">
+      <c r="D15" s="251"/>
+      <c r="E15" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">10) L/C issuing bank</t>
           </r>
         </is>
       </c>
-      <c r="F15" s="251"/>
-      <c r="G15" s="251"/>
-      <c r="H15" s="251"/>
-      <c r="I15" s="252"/>
-    </row>
-    <row r="16" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A16" s="232" t="str">
+      <c r="F15" s="250"/>
+      <c r="G15" s="250"/>
+      <c r="H15" s="250"/>
+      <c r="I15" s="251"/>
+    </row>
+    <row r="16" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A16" s="231" t="str">
         <f>구매리스트!B10</f>
         <v>0</v>
       </c>
-      <c r="B16" s="253"/>
-      <c r="C16" s="352" t="str">
+      <c r="B16" s="252"/>
+      <c r="C16" s="351" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
-      <c r="D16" s="254"/>
-      <c r="E16" s="353" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I16" s="263"/>
-    </row>
-    <row r="17" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A17" s="344" t="inlineStr">
+      <c r="D16" s="253"/>
+      <c r="E16" s="352" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I16" s="262"/>
+    </row>
+    <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
+      <c r="A17" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
           </r>
         </is>
       </c>
-      <c r="B17" s="252"/>
-      <c r="C17" s="226" t="inlineStr">
+      <c r="B17" s="251"/>
+      <c r="C17" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">7) Sailing on or about</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="354" t="str">
+      <c r="D17" s="251"/>
+      <c r="E17" s="353" t="str">
         <f>구매리스트!D12</f>
         <v>0</v>
       </c>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="252"/>
-    </row>
-    <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A18" s="352" t="str">
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="251"/>
+    </row>
+    <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A18" s="351" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
-      <c r="B18" s="254"/>
-      <c r="C18" s="355" t="str">
+      <c r="B18" s="253"/>
+      <c r="C18" s="354" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="D18" s="254"/>
-      <c r="E18" s="273"/>
-      <c r="F18" s="253"/>
-      <c r="G18" s="253"/>
-      <c r="H18" s="253"/>
-      <c r="I18" s="254"/>
-    </row>
-    <row r="19" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
+      <c r="D18" s="253"/>
+      <c r="E18" s="272"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="253"/>
+    </row>
+    <row r="19" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
           <r>
@@ -11595,14 +11621,14 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="356" t="inlineStr">
+      <c r="E19" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
           </r>
         </is>
       </c>
-      <c r="F19" s="256"/>
+      <c r="F19" s="255"/>
       <c r="G19" s="22" t="inlineStr">
         <is>
           <r>
@@ -11625,7 +11651,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:10" customHeight="1" ht="10.5" s="246" customFormat="1">
+    <row r="20" spans="1:10" customHeight="1" ht="10.5" s="245" customFormat="1">
       <c r="A20" s="30"/>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -11636,7 +11662,7 @@
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
     </row>
-    <row r="21" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
+    <row r="21" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
           <r>
@@ -11665,29 +11691,29 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="357" t="inlineStr">
+      <c r="E21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
           </r>
         </is>
       </c>
-      <c r="F21" s="256"/>
-      <c r="G21" s="358" t="inlineStr">
+      <c r="F21" s="255"/>
+      <c r="G21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="359" t="inlineStr">
+      <c r="H21" s="358" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
           </r>
         </is>
       </c>
-      <c r="I21" s="360" t="inlineStr">
+      <c r="I21" s="359" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Shipping</t>
@@ -11696,8 +11722,8 @@
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A22" s="361">
+    <row r="22" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A22" s="360">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -11712,10 +11738,10 @@
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="E22" s="362">
+      <c r="E22" s="361">
         <v>1</v>
       </c>
-      <c r="F22" s="256"/>
+      <c r="F22" s="255"/>
       <c r="G22" s="126" t="str">
         <f>구매리스트!B15</f>
         <v>0</v>
@@ -11733,23 +11759,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A23" s="364"/>
-      <c r="B23" s="365"/>
-      <c r="C23" s="255"/>
-      <c r="D23" s="255"/>
-      <c r="E23" s="255"/>
-      <c r="F23" s="255"/>
-      <c r="G23" s="255"/>
-      <c r="H23" s="255"/>
-      <c r="I23" s="256"/>
-      <c r="J23" s="363"/>
-    </row>
-    <row r="24" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A24" s="364">
+    <row r="23" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A23" s="363"/>
+      <c r="B23" s="364"/>
+      <c r="C23" s="254"/>
+      <c r="D23" s="254"/>
+      <c r="E23" s="254"/>
+      <c r="F23" s="254"/>
+      <c r="G23" s="254"/>
+      <c r="H23" s="254"/>
+      <c r="I23" s="255"/>
+      <c r="J23" s="362"/>
+    </row>
+    <row r="24" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A24" s="363">
         <v>2</v>
       </c>
-      <c r="B24" s="366" t="inlineStr">
+      <c r="B24" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11770,9 +11796,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="367"/>
-      <c r="F24" s="256"/>
-      <c r="G24" s="368" t="inlineStr">
+      <c r="E24" s="366"/>
+      <c r="F24" s="255"/>
+      <c r="G24" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11786,40 +11812,40 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="363">
+      <c r="I24" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="362">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A25" s="364"/>
-      <c r="B25" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C25" s="255"/>
-      <c r="D25" s="255"/>
-      <c r="E25" s="255"/>
-      <c r="F25" s="255"/>
-      <c r="G25" s="255"/>
-      <c r="H25" s="255"/>
-      <c r="I25" s="256"/>
-      <c r="J25" s="363"/>
-    </row>
-    <row r="26" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A26" s="364">
+    <row r="25" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A25" s="363"/>
+      <c r="B25" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="254"/>
+      <c r="D25" s="254"/>
+      <c r="E25" s="254"/>
+      <c r="F25" s="254"/>
+      <c r="G25" s="254"/>
+      <c r="H25" s="254"/>
+      <c r="I25" s="255"/>
+      <c r="J25" s="362"/>
+    </row>
+    <row r="26" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A26" s="363">
         <v>3</v>
       </c>
-      <c r="B26" s="366" t="inlineStr">
+      <c r="B26" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11840,9 +11866,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="367"/>
-      <c r="F26" s="256"/>
-      <c r="G26" s="368" t="inlineStr">
+      <c r="E26" s="366"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11856,40 +11882,40 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="363">
+      <c r="I26" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="362">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A27" s="364"/>
-      <c r="B27" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C27" s="255"/>
-      <c r="D27" s="255"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="256"/>
-      <c r="J27" s="363"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A28" s="364">
+    <row r="27" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A27" s="363"/>
+      <c r="B27" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="254"/>
+      <c r="D27" s="254"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
+      <c r="H27" s="254"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="362"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A28" s="363">
         <v>4</v>
       </c>
-      <c r="B28" s="370" t="inlineStr">
+      <c r="B28" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11910,9 +11936,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="367"/>
-      <c r="F28" s="256"/>
-      <c r="G28" s="368" t="inlineStr">
+      <c r="E28" s="366"/>
+      <c r="F28" s="255"/>
+      <c r="G28" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11926,46 +11952,46 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="363">
+      <c r="I28" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="362">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A29" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C29" s="255"/>
-      <c r="D29" s="255"/>
-      <c r="E29" s="255"/>
-      <c r="F29" s="255"/>
-      <c r="G29" s="255"/>
-      <c r="H29" s="255"/>
-      <c r="I29" s="256"/>
+    <row r="29" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A29" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="254"/>
+      <c r="D29" s="254"/>
+      <c r="E29" s="254"/>
+      <c r="F29" s="254"/>
+      <c r="G29" s="254"/>
+      <c r="H29" s="254"/>
+      <c r="I29" s="255"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A30" s="364">
+    <row r="30" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A30" s="363">
         <v>5</v>
       </c>
-      <c r="B30" s="370" t="inlineStr">
+      <c r="B30" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11986,9 +12012,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="367"/>
-      <c r="F30" s="256"/>
-      <c r="G30" s="368" t="inlineStr">
+      <c r="E30" s="366"/>
+      <c r="F30" s="255"/>
+      <c r="G30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12002,7 +12028,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="369" t="inlineStr">
+      <c r="I30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12011,76 +12037,76 @@
       </c>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A31" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C31" s="255"/>
-      <c r="D31" s="255"/>
-      <c r="E31" s="255"/>
-      <c r="F31" s="255"/>
-      <c r="G31" s="255"/>
-      <c r="H31" s="255"/>
-      <c r="I31" s="256"/>
+    <row r="31" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A31" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="254"/>
+      <c r="D31" s="254"/>
+      <c r="E31" s="254"/>
+      <c r="F31" s="254"/>
+      <c r="G31" s="254"/>
+      <c r="H31" s="254"/>
+      <c r="I31" s="255"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="39.75" s="246" customFormat="1">
+    <row r="32" spans="1:10" customHeight="1" ht="39.75" s="245" customFormat="1">
       <c r="A32" s="27"/>
-      <c r="B32" s="233" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C32" s="371"/>
-      <c r="D32" s="234" t="inlineStr">
+      <c r="B32" s="232" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C32" s="370"/>
+      <c r="D32" s="233" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> GRAND TOTAL :</t>
           </r>
         </is>
       </c>
-      <c r="E32" s="371"/>
-      <c r="F32" s="234"/>
-      <c r="G32" s="234"/>
-      <c r="H32" s="228" t="str">
+      <c r="E32" s="370"/>
+      <c r="F32" s="233"/>
+      <c r="G32" s="233"/>
+      <c r="H32" s="227" t="str">
         <f>SUM(H22:I22,H24:I24,H26:I26,H28:I28,H30:I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="372"/>
+      <c r="I32" s="371"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="28"/>
-      <c r="B33" s="231"/>
-      <c r="C33" s="231"/>
-      <c r="D33" s="231" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E33" s="231" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="G33" s="246"/>
+      <c r="B33" s="230"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E33" s="230" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="G33" s="245"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -12095,7 +12121,7 @@
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
-      <c r="E34" s="231" t="inlineStr">
+      <c r="E34" s="230" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Signed By    </t>
@@ -12252,68 +12278,68 @@
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="4.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="21.625" customWidth="true" style="246"/>
-    <col min="3" max="3" width="7.5" customWidth="true" style="246"/>
-    <col min="4" max="4" width="23.625" customWidth="true" style="246"/>
-    <col min="5" max="5" width="7.75" customWidth="true" style="246"/>
-    <col min="6" max="6" width="2.125" customWidth="true" style="246"/>
-    <col min="7" max="7" width="12.25" customWidth="true" style="246"/>
-    <col min="8" max="8" width="13.75" customWidth="true" style="246"/>
-    <col min="9" max="9" width="14" customWidth="true" style="246"/>
+    <col min="1" max="1" width="4.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="21.625" customWidth="true" style="245"/>
+    <col min="3" max="3" width="7.5" customWidth="true" style="245"/>
+    <col min="4" max="4" width="23.625" customWidth="true" style="245"/>
+    <col min="5" max="5" width="7.75" customWidth="true" style="245"/>
+    <col min="6" max="6" width="2.125" customWidth="true" style="245"/>
+    <col min="7" max="7" width="12.25" customWidth="true" style="245"/>
+    <col min="8" max="8" width="13.75" customWidth="true" style="245"/>
+    <col min="9" max="9" width="14" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customHeight="1" ht="47.25" s="246" customFormat="1">
-      <c r="A1" s="343" t="inlineStr">
+    <row r="1" spans="1:10" customHeight="1" ht="47.25" s="245" customFormat="1">
+      <c r="A1" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL PACKING LIST</t>
           </r>
         </is>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="255"/>
-      <c r="I1" s="256"/>
-    </row>
-    <row r="2" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A2" s="344" t="inlineStr">
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="255"/>
+    </row>
+    <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
           </r>
         </is>
       </c>
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="252"/>
-      <c r="E2" s="225" t="inlineStr">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="224" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reference No.      DFSU6646075</t>
           </r>
         </is>
       </c>
-      <c r="F2" s="251"/>
+      <c r="F2" s="250"/>
       <c r="G2" s="128" t="str">
         <f>차량인보이스!G2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="345" t="inlineStr">
+      <c r="H2" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
           </r>
         </is>
       </c>
-      <c r="I2" s="252"/>
-    </row>
-    <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A3" s="346" t="inlineStr">
+      <c r="I2" s="251"/>
+    </row>
+    <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A3" s="345" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR LTD.,
@@ -12324,8 +12350,8 @@
           </r>
         </is>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="229" t="inlineStr">
+      <c r="D3" s="262"/>
+      <c r="E3" s="228" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reference code.   DFSU6646075</t>
@@ -12336,122 +12362,122 @@
         <f>차량인보이스!G3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="273"/>
-      <c r="I3" s="254"/>
-    </row>
-    <row r="4" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A4" s="272"/>
-      <c r="D4" s="263"/>
-      <c r="E4" s="347" t="inlineStr">
+      <c r="H3" s="272"/>
+      <c r="I3" s="253"/>
+    </row>
+    <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A4" s="271"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
           </r>
         </is>
       </c>
-      <c r="I4" s="263"/>
-    </row>
-    <row r="5" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A5" s="272"/>
-      <c r="D5" s="263"/>
-      <c r="E5" s="272"/>
-      <c r="I5" s="263"/>
-    </row>
-    <row r="6" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A6" s="272"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="348" t="inlineStr">
+      <c r="I4" s="262"/>
+    </row>
+    <row r="5" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A5" s="271"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="271"/>
+      <c r="I5" s="262"/>
+    </row>
+    <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A6" s="271"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
           </r>
         </is>
       </c>
-      <c r="I6" s="263"/>
-    </row>
-    <row r="7" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A7" s="273"/>
-      <c r="B7" s="253"/>
-      <c r="C7" s="253"/>
-      <c r="D7" s="254"/>
-      <c r="E7" s="348" t="inlineStr">
+      <c r="I6" s="262"/>
+    </row>
+    <row r="7" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A7" s="272"/>
+      <c r="B7" s="252"/>
+      <c r="C7" s="252"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
           </r>
         </is>
       </c>
-      <c r="I7" s="263"/>
-    </row>
-    <row r="8" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A8" s="344" t="inlineStr">
+      <c r="I7" s="262"/>
+    </row>
+    <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A8" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
           </r>
         </is>
       </c>
-      <c r="B8" s="251"/>
-      <c r="C8" s="251"/>
-      <c r="D8" s="252"/>
-      <c r="E8" s="349" t="inlineStr">
+      <c r="B8" s="250"/>
+      <c r="C8" s="250"/>
+      <c r="D8" s="251"/>
+      <c r="E8" s="348" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
           </r>
         </is>
       </c>
-      <c r="F8" s="253"/>
-      <c r="G8" s="253"/>
-      <c r="H8" s="253"/>
-      <c r="I8" s="254"/>
-    </row>
-    <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
-      <c r="A9" s="373" t="str">
+      <c r="F8" s="252"/>
+      <c r="G8" s="252"/>
+      <c r="H8" s="252"/>
+      <c r="I8" s="253"/>
+    </row>
+    <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
+      <c r="A9" s="372" t="str">
         <f>차량인보이스!A9</f>
         <v>0</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="E9" s="235" t="inlineStr">
+      <c r="D9" s="262"/>
+      <c r="E9" s="234" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> *Remark</t>
           </r>
         </is>
       </c>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A10" s="272"/>
-      <c r="D10" s="263"/>
-      <c r="E10" s="226" t="inlineStr">
+      <c r="F9" s="250"/>
+      <c r="G9" s="250"/>
+      <c r="H9" s="250"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A10" s="271"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">8) No. &amp; date of invoice</t>
           </r>
         </is>
       </c>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="252"/>
-    </row>
-    <row r="11" spans="1:10" customHeight="1" ht="35.25" s="246" customFormat="1">
-      <c r="A11" s="273"/>
-      <c r="B11" s="253"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="254"/>
-      <c r="E11" s="227" t="str">
+      <c r="F10" s="250"/>
+      <c r="G10" s="250"/>
+      <c r="H10" s="250"/>
+      <c r="I10" s="251"/>
+    </row>
+    <row r="11" spans="1:10" customHeight="1" ht="35.25" s="245" customFormat="1">
+      <c r="A11" s="272"/>
+      <c r="B11" s="252"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="226" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
@@ -12460,151 +12486,151 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A12" s="344" t="inlineStr">
+    <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
           </r>
         </is>
       </c>
-      <c r="B12" s="251"/>
-      <c r="C12" s="251"/>
-      <c r="D12" s="252"/>
-      <c r="E12" s="344" t="inlineStr">
+      <c r="B12" s="250"/>
+      <c r="C12" s="250"/>
+      <c r="D12" s="251"/>
+      <c r="E12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
           </r>
         </is>
       </c>
-      <c r="F12" s="251"/>
-      <c r="G12" s="251"/>
-      <c r="H12" s="251"/>
-      <c r="I12" s="252"/>
-    </row>
-    <row r="13" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A13" s="351" t="inlineStr">
+      <c r="F12" s="250"/>
+      <c r="G12" s="250"/>
+      <c r="H12" s="250"/>
+      <c r="I12" s="251"/>
+    </row>
+    <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A13" s="350" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
           </r>
         </is>
       </c>
-      <c r="D13" s="263"/>
-      <c r="E13" s="230" t="inlineStr">
+      <c r="D13" s="262"/>
+      <c r="E13" s="229" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">TTR BASE</t>
           </r>
         </is>
       </c>
-      <c r="I13" s="263"/>
-    </row>
-    <row r="14" spans="1:10" customHeight="1" ht="9.75" s="246" customFormat="1">
-      <c r="A14" s="273"/>
-      <c r="B14" s="253"/>
-      <c r="C14" s="253"/>
-      <c r="D14" s="254"/>
-      <c r="E14" s="253"/>
-      <c r="F14" s="253"/>
-      <c r="G14" s="253"/>
-      <c r="H14" s="253"/>
-      <c r="I14" s="254"/>
-    </row>
-    <row r="15" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A15" s="344" t="inlineStr">
+      <c r="I13" s="262"/>
+    </row>
+    <row r="14" spans="1:10" customHeight="1" ht="9.75" s="245" customFormat="1">
+      <c r="A14" s="272"/>
+      <c r="B14" s="252"/>
+      <c r="C14" s="252"/>
+      <c r="D14" s="253"/>
+      <c r="E14" s="252"/>
+      <c r="F14" s="252"/>
+      <c r="G14" s="252"/>
+      <c r="H14" s="252"/>
+      <c r="I14" s="253"/>
+    </row>
+    <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
+      <c r="A15" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="252"/>
-      <c r="C15" s="226" t="inlineStr">
+      <c r="B15" s="251"/>
+      <c r="C15" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">5) Final Destination</t>
           </r>
         </is>
       </c>
-      <c r="D15" s="252"/>
-      <c r="E15" s="226" t="inlineStr">
+      <c r="D15" s="251"/>
+      <c r="E15" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">10) L/C issuing bank</t>
           </r>
         </is>
       </c>
-      <c r="F15" s="251"/>
-      <c r="G15" s="251"/>
-      <c r="H15" s="251"/>
-      <c r="I15" s="252"/>
-    </row>
-    <row r="16" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A16" s="232" t="str">
+      <c r="F15" s="250"/>
+      <c r="G15" s="250"/>
+      <c r="H15" s="250"/>
+      <c r="I15" s="251"/>
+    </row>
+    <row r="16" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A16" s="231" t="str">
         <f>구매리스트!B10</f>
         <v>0</v>
       </c>
-      <c r="B16" s="253"/>
-      <c r="C16" s="352" t="str">
+      <c r="B16" s="252"/>
+      <c r="C16" s="351" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
-      <c r="D16" s="254"/>
-      <c r="E16" s="353" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I16" s="263"/>
-    </row>
-    <row r="17" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A17" s="344" t="inlineStr">
+      <c r="D16" s="253"/>
+      <c r="E16" s="352" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I16" s="262"/>
+    </row>
+    <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
+      <c r="A17" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
           </r>
         </is>
       </c>
-      <c r="B17" s="252"/>
-      <c r="C17" s="226" t="inlineStr">
+      <c r="B17" s="251"/>
+      <c r="C17" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">7) Sailing on or about</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="354" t="str">
+      <c r="D17" s="251"/>
+      <c r="E17" s="353" t="str">
         <f>차량인보이스!E17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="252"/>
-    </row>
-    <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A18" s="352" t="str">
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="251"/>
+    </row>
+    <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A18" s="351" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
-      <c r="B18" s="254"/>
-      <c r="C18" s="355" t="str">
+      <c r="B18" s="253"/>
+      <c r="C18" s="354" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="D18" s="254"/>
-      <c r="E18" s="273"/>
-      <c r="F18" s="253"/>
-      <c r="G18" s="253"/>
-      <c r="H18" s="253"/>
-      <c r="I18" s="254"/>
-    </row>
-    <row r="19" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
+      <c r="D18" s="253"/>
+      <c r="E18" s="272"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="253"/>
+    </row>
+    <row r="19" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
           <r>
@@ -12621,14 +12647,14 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="356" t="inlineStr">
+      <c r="E19" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
           </r>
         </is>
       </c>
-      <c r="F19" s="256"/>
+      <c r="F19" s="255"/>
       <c r="G19" s="22" t="inlineStr">
         <is>
           <r>
@@ -12651,7 +12677,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:10" customHeight="1" ht="10.5" s="246" customFormat="1">
+    <row r="20" spans="1:10" customHeight="1" ht="10.5" s="245" customFormat="1">
       <c r="A20" s="30"/>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -12662,7 +12688,7 @@
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
     </row>
-    <row r="21" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
+    <row r="21" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
           <r>
@@ -12691,22 +12717,22 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="357" t="inlineStr">
+      <c r="E21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
           </r>
         </is>
       </c>
-      <c r="F21" s="256"/>
-      <c r="G21" s="358" t="inlineStr">
+      <c r="F21" s="255"/>
+      <c r="G21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="359" t="inlineStr">
+      <c r="H21" s="358" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
@@ -12723,8 +12749,8 @@
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A22" s="361">
+    <row r="22" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A22" s="360">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -12739,19 +12765,19 @@
         <f>차량인보이스!D22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="362" t="str">
+      <c r="E22" s="361" t="str">
         <f>차량인보이스!E22</f>
         <v>0</v>
       </c>
-      <c r="F22" s="256"/>
-      <c r="G22" s="374" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="H22" s="374" t="inlineStr">
+      <c r="F22" s="255"/>
+      <c r="G22" s="373" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H22" s="373" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12762,31 +12788,31 @@
         <f>구매리스트!I8</f>
         <v>0</v>
       </c>
-      <c r="J22" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="23" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A23" s="364"/>
-      <c r="B23" s="365"/>
-      <c r="C23" s="255"/>
-      <c r="D23" s="255"/>
-      <c r="E23" s="255"/>
-      <c r="F23" s="255"/>
-      <c r="G23" s="255"/>
-      <c r="H23" s="255"/>
-      <c r="I23" s="256"/>
-      <c r="J23" s="363"/>
-    </row>
-    <row r="24" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A24" s="364">
+      <c r="J22" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A23" s="363"/>
+      <c r="B23" s="364"/>
+      <c r="C23" s="254"/>
+      <c r="D23" s="254"/>
+      <c r="E23" s="254"/>
+      <c r="F23" s="254"/>
+      <c r="G23" s="254"/>
+      <c r="H23" s="254"/>
+      <c r="I23" s="255"/>
+      <c r="J23" s="362"/>
+    </row>
+    <row r="24" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A24" s="363">
         <v>2</v>
       </c>
-      <c r="B24" s="366" t="inlineStr">
+      <c r="B24" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12807,9 +12833,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="367"/>
-      <c r="F24" s="256"/>
-      <c r="G24" s="368" t="inlineStr">
+      <c r="E24" s="366"/>
+      <c r="F24" s="255"/>
+      <c r="G24" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12823,44 +12849,44 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="25" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A25" s="364"/>
-      <c r="B25" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C25" s="255"/>
-      <c r="D25" s="255"/>
-      <c r="E25" s="255"/>
-      <c r="F25" s="255"/>
-      <c r="G25" s="255"/>
-      <c r="H25" s="255"/>
-      <c r="I25" s="256"/>
-      <c r="J25" s="363"/>
-    </row>
-    <row r="26" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A26" s="364">
+      <c r="I24" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A25" s="363"/>
+      <c r="B25" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="254"/>
+      <c r="D25" s="254"/>
+      <c r="E25" s="254"/>
+      <c r="F25" s="254"/>
+      <c r="G25" s="254"/>
+      <c r="H25" s="254"/>
+      <c r="I25" s="255"/>
+      <c r="J25" s="362"/>
+    </row>
+    <row r="26" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A26" s="363">
         <v>3</v>
       </c>
-      <c r="B26" s="366" t="inlineStr">
+      <c r="B26" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12881,9 +12907,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="367"/>
-      <c r="F26" s="256"/>
-      <c r="G26" s="368" t="inlineStr">
+      <c r="E26" s="366"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12897,44 +12923,44 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="27" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A27" s="364"/>
-      <c r="B27" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C27" s="255"/>
-      <c r="D27" s="255"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="256"/>
-      <c r="J27" s="363"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A28" s="364">
+      <c r="I26" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A27" s="363"/>
+      <c r="B27" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="254"/>
+      <c r="D27" s="254"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
+      <c r="H27" s="254"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="362"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A28" s="363">
         <v>4</v>
       </c>
-      <c r="B28" s="370" t="inlineStr">
+      <c r="B28" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12955,9 +12981,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="367"/>
-      <c r="F28" s="256"/>
-      <c r="G28" s="368" t="inlineStr">
+      <c r="E28" s="366"/>
+      <c r="F28" s="255"/>
+      <c r="G28" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12971,50 +12997,50 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="29" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A29" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C29" s="255"/>
-      <c r="D29" s="255"/>
-      <c r="E29" s="255"/>
-      <c r="F29" s="255"/>
-      <c r="G29" s="255"/>
-      <c r="H29" s="255"/>
-      <c r="I29" s="256"/>
+      <c r="I28" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A29" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="254"/>
+      <c r="D29" s="254"/>
+      <c r="E29" s="254"/>
+      <c r="F29" s="254"/>
+      <c r="G29" s="254"/>
+      <c r="H29" s="254"/>
+      <c r="I29" s="255"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A30" s="364">
+    <row r="30" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A30" s="363">
         <v>5</v>
       </c>
-      <c r="B30" s="370" t="inlineStr">
+      <c r="B30" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13035,9 +13061,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="367"/>
-      <c r="F30" s="256"/>
-      <c r="G30" s="368" t="inlineStr">
+      <c r="E30" s="366"/>
+      <c r="F30" s="255"/>
+      <c r="G30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13051,7 +13077,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="369" t="inlineStr">
+      <c r="I30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13060,76 +13086,76 @@
       </c>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A31" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C31" s="255"/>
-      <c r="D31" s="255"/>
-      <c r="E31" s="255"/>
-      <c r="F31" s="255"/>
-      <c r="G31" s="255"/>
-      <c r="H31" s="255"/>
-      <c r="I31" s="256"/>
+    <row r="31" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A31" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="254"/>
+      <c r="D31" s="254"/>
+      <c r="E31" s="254"/>
+      <c r="F31" s="254"/>
+      <c r="G31" s="254"/>
+      <c r="H31" s="254"/>
+      <c r="I31" s="255"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="39.75" s="246" customFormat="1">
+    <row r="32" spans="1:10" customHeight="1" ht="39.75" s="245" customFormat="1">
       <c r="A32" s="27"/>
-      <c r="B32" s="233" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C32" s="371"/>
-      <c r="D32" s="236" t="inlineStr">
+      <c r="B32" s="232" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C32" s="370"/>
+      <c r="D32" s="235" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> GRAND TOTAL :</t>
           </r>
         </is>
       </c>
-      <c r="E32" s="371"/>
-      <c r="F32" s="236"/>
-      <c r="G32" s="236"/>
-      <c r="H32" s="237" t="str">
+      <c r="E32" s="370"/>
+      <c r="F32" s="235"/>
+      <c r="G32" s="235"/>
+      <c r="H32" s="236" t="str">
         <f>SUM(I22,I24,I26,I28,I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="372"/>
+      <c r="I32" s="371"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="28"/>
-      <c r="B33" s="231"/>
-      <c r="C33" s="231"/>
-      <c r="D33" s="231" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E33" s="231" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="G33" s="246"/>
+      <c r="B33" s="230"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E33" s="230" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="G33" s="245"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -13144,7 +13170,7 @@
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
-      <c r="E34" s="231" t="inlineStr">
+      <c r="E34" s="230" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Signed By    </t>
@@ -13300,20 +13326,20 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="7.625" customWidth="true" style="246"/>
-    <col min="2" max="2" width="14.875" customWidth="true" style="246"/>
-    <col min="3" max="3" width="26.375" customWidth="true" style="246"/>
-    <col min="4" max="4" width="10.5" customWidth="true" style="246"/>
-    <col min="5" max="5" width="18.875" customWidth="true" style="246"/>
-    <col min="6" max="6" width="18" customWidth="true" style="246"/>
-    <col min="7" max="7" width="15.25" customWidth="true" style="246"/>
+    <col min="1" max="1" width="7.625" customWidth="true" style="245"/>
+    <col min="2" max="2" width="14.875" customWidth="true" style="245"/>
+    <col min="3" max="3" width="26.375" customWidth="true" style="245"/>
+    <col min="4" max="4" width="10.5" customWidth="true" style="245"/>
+    <col min="5" max="5" width="18.875" customWidth="true" style="245"/>
+    <col min="6" max="6" width="18" customWidth="true" style="245"/>
+    <col min="7" max="7" width="15.25" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" customHeight="1" ht="84" s="246" customFormat="1">
-      <c r="A1" s="243"/>
+    <row r="1" spans="1:7" customHeight="1" ht="84" s="245" customFormat="1">
+      <c r="A1" s="242"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
-      <c r="E1" s="242" t="inlineStr">
+      <c r="E1" s="241" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">PROFORM INVOICE</t>
@@ -13321,18 +13347,18 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:7" customHeight="1" ht="11.25" s="246" customFormat="1">
-      <c r="A2" s="244" t="inlineStr">
+    <row r="2" spans="1:7" customHeight="1" ht="11.25" s="245" customFormat="1">
+      <c r="A2" s="243" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Ssancar LTD 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea   Phone: +82-505-366-9977</t>
           </r>
         </is>
       </c>
-      <c r="D2" s="244"/>
-    </row>
-    <row r="3" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="D3" s="244"/>
+      <c r="D2" s="243"/>
+    </row>
+    <row r="3" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="D3" s="243"/>
       <c r="E3" s="44" t="inlineStr">
         <is>
           <r>
@@ -13340,13 +13366,13 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="375" t="str">
+      <c r="F3" s="374" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="G3" s="376"/>
-    </row>
-    <row r="4" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
+      <c r="G3" s="375"/>
+    </row>
+    <row r="4" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A4" s="47"/>
       <c r="B4" s="47"/>
       <c r="C4" s="47"/>
@@ -13358,15 +13384,15 @@
           </r>
         </is>
       </c>
-      <c r="F4" s="377" t="str">
+      <c r="F4" s="376" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
-      <c r="G4" s="378"/>
-    </row>
-    <row r="5" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A5" s="239"/>
-      <c r="B5" s="239"/>
+      <c r="G4" s="377"/>
+    </row>
+    <row r="5" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A5" s="238"/>
+      <c r="B5" s="238"/>
       <c r="E5" s="44" t="inlineStr">
         <is>
           <r>
@@ -13374,15 +13400,15 @@
           </r>
         </is>
       </c>
-      <c r="F5" s="379" t="str">
+      <c r="F5" s="378" t="str">
         <f>구매리스트!D14</f>
         <v>0</v>
       </c>
-      <c r="G5" s="378"/>
-    </row>
-    <row r="6" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A6" s="239"/>
-      <c r="B6" s="239"/>
+      <c r="G5" s="377"/>
+    </row>
+    <row r="6" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A6" s="238"/>
+      <c r="B6" s="238"/>
       <c r="E6" s="44" t="inlineStr">
         <is>
           <r>
@@ -13390,11 +13416,11 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="380"/>
-      <c r="G6" s="378"/>
-    </row>
-    <row r="7" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A7" s="239"/>
+      <c r="F6" s="379"/>
+      <c r="G6" s="377"/>
+    </row>
+    <row r="7" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A7" s="238"/>
       <c r="E7" s="44" t="inlineStr">
         <is>
           <r>
@@ -13402,11 +13428,11 @@
           </r>
         </is>
       </c>
-      <c r="F7" s="381"/>
-      <c r="G7" s="378"/>
-    </row>
-    <row r="8" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A8" s="239"/>
+      <c r="F7" s="380"/>
+      <c r="G7" s="377"/>
+    </row>
+    <row r="8" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A8" s="238"/>
       <c r="E8" s="44" t="inlineStr">
         <is>
           <r>
@@ -13414,12 +13440,12 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="382"/>
-      <c r="G8" s="378"/>
-    </row>
-    <row r="9" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A9" s="239"/>
-      <c r="B9" s="239"/>
+      <c r="F8" s="381"/>
+      <c r="G8" s="377"/>
+    </row>
+    <row r="9" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
       <c r="E9" s="44" t="inlineStr">
         <is>
           <r>
@@ -13427,18 +13453,18 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="380"/>
-      <c r="G9" s="378"/>
-    </row>
-    <row r="10" spans="1:7" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A10" s="239"/>
+      <c r="F9" s="379"/>
+      <c r="G9" s="377"/>
+    </row>
+    <row r="10" spans="1:7" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A10" s="238"/>
       <c r="E10" s="44"/>
       <c r="F10" s="46"/>
       <c r="G10" s="45"/>
     </row>
-    <row r="11" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="A11" s="238"/>
-      <c r="B11" s="238"/>
+    <row r="11" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A11" s="237"/>
+      <c r="B11" s="237"/>
       <c r="E11" s="44" t="inlineStr">
         <is>
           <r>
@@ -13446,14 +13472,14 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="383" t="str">
+      <c r="F11" s="382" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G11" s="378"/>
-    </row>
-    <row r="12" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="A12" s="238"/>
+      <c r="G11" s="377"/>
+    </row>
+    <row r="12" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A12" s="237"/>
       <c r="E12" s="44" t="inlineStr">
         <is>
           <r>
@@ -13461,14 +13487,14 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="383" t="str">
+      <c r="F12" s="382" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G12" s="378"/>
-    </row>
-    <row r="13" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="A13" s="245"/>
+      <c r="G12" s="377"/>
+    </row>
+    <row r="13" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A13" s="244"/>
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44" t="inlineStr">
@@ -13478,138 +13504,138 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="384" t="str">
+      <c r="F13" s="383" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="378"/>
-    </row>
-    <row r="14" spans="1:7" customHeight="1" ht="17.25" s="246" customFormat="1">
-      <c r="A14" s="245"/>
+      <c r="G13" s="377"/>
+    </row>
+    <row r="14" spans="1:7" customHeight="1" ht="17.25" s="245" customFormat="1">
+      <c r="A14" s="244"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
-      <c r="E14" s="385"/>
-    </row>
-    <row r="15" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A15" s="386" t="inlineStr">
+      <c r="E14" s="384"/>
+    </row>
+    <row r="15" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A15" s="385" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">BANK ACCOUNT INFORMATION</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="387"/>
-      <c r="C15" s="387"/>
-      <c r="D15" s="387"/>
-      <c r="E15" s="387"/>
-      <c r="F15" s="387"/>
-      <c r="G15" s="388"/>
-    </row>
-    <row r="16" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A16" s="240" t="inlineStr">
+      <c r="B15" s="386"/>
+      <c r="C15" s="386"/>
+      <c r="D15" s="386"/>
+      <c r="E15" s="386"/>
+      <c r="F15" s="386"/>
+      <c r="G15" s="387"/>
+    </row>
+    <row r="16" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A16" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Beneficiary</t>
           </r>
         </is>
       </c>
-      <c r="B16" s="388"/>
-      <c r="C16" s="389" t="inlineStr">
+      <c r="B16" s="387"/>
+      <c r="C16" s="388" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR CO LTD</t>
           </r>
         </is>
       </c>
-      <c r="D16" s="388"/>
-      <c r="E16" s="240" t="inlineStr">
+      <c r="D16" s="387"/>
+      <c r="E16" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bank Name</t>
           </r>
         </is>
       </c>
-      <c r="F16" s="390" t="inlineStr">
+      <c r="F16" s="389" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHINHAN BANK</t>
           </r>
         </is>
       </c>
-      <c r="G16" s="388"/>
-    </row>
-    <row r="17" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A17" s="240" t="inlineStr">
+      <c r="G16" s="387"/>
+    </row>
+    <row r="17" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A17" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Swift Cose</t>
           </r>
         </is>
       </c>
-      <c r="B17" s="388"/>
-      <c r="C17" s="389" t="inlineStr">
+      <c r="B17" s="387"/>
+      <c r="C17" s="388" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHBKKRSE</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="388"/>
-      <c r="E17" s="240" t="inlineStr">
+      <c r="D17" s="387"/>
+      <c r="E17" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bank Adress</t>
           </r>
         </is>
       </c>
-      <c r="F17" s="241" t="inlineStr">
+      <c r="F17" s="240" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">20,Sejong-Daero9-Gil,Jung-Gu Seoul South Korea</t>
           </r>
         </is>
       </c>
-      <c r="G17" s="388"/>
-    </row>
-    <row r="18" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A18" s="240" t="inlineStr">
+      <c r="G17" s="387"/>
+    </row>
+    <row r="18" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A18" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bank Account Number</t>
           </r>
         </is>
       </c>
-      <c r="B18" s="388"/>
-      <c r="C18" s="389" t="inlineStr">
+      <c r="B18" s="387"/>
+      <c r="C18" s="388" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">180-008-400167</t>
           </r>
         </is>
       </c>
-      <c r="D18" s="388"/>
-      <c r="E18" s="240" t="inlineStr">
+      <c r="D18" s="387"/>
+      <c r="E18" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Beneficiary Adress</t>
           </r>
         </is>
       </c>
-      <c r="F18" s="391" t="inlineStr">
+      <c r="F18" s="390" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do,   SOUTH KOREA</t>
           </r>
         </is>
       </c>
-      <c r="G18" s="388"/>
+      <c r="G18" s="387"/>
     </row>
     <row r="19" spans="1:7">
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="385"/>
-    </row>
-    <row r="20" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="E19" s="384"/>
+    </row>
+    <row r="20" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A20" s="42" t="inlineStr">
         <is>
           <r>
@@ -13652,9 +13678,9 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="388"/>
-    </row>
-    <row r="21" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="G20" s="387"/>
+    </row>
+    <row r="21" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A21" s="133" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
@@ -13672,67 +13698,67 @@
         <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="392" t="str">
+      <c r="F21" s="391" t="str">
         <f>차량인보이스!H22</f>
         <v>0</v>
       </c>
-      <c r="G21" s="388"/>
-    </row>
-    <row r="22" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="G21" s="387"/>
+    </row>
+    <row r="22" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A22" s="41"/>
       <c r="B22" s="41"/>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="393"/>
-      <c r="G22" s="388"/>
-    </row>
-    <row r="23" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F22" s="392"/>
+      <c r="G22" s="387"/>
+    </row>
+    <row r="23" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A23" s="41"/>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="393"/>
-      <c r="G23" s="388"/>
-    </row>
-    <row r="24" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F23" s="392"/>
+      <c r="G23" s="387"/>
+    </row>
+    <row r="24" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A24" s="41"/>
       <c r="B24" s="41"/>
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="393"/>
-      <c r="G24" s="388"/>
-    </row>
-    <row r="25" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F24" s="392"/>
+      <c r="G24" s="387"/>
+    </row>
+    <row r="25" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A25" s="41"/>
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="393"/>
-      <c r="G25" s="388"/>
-    </row>
-    <row r="26" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F25" s="392"/>
+      <c r="G25" s="387"/>
+    </row>
+    <row r="26" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A26" s="41"/>
       <c r="B26" s="41"/>
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="393"/>
-      <c r="G26" s="388"/>
-    </row>
-    <row r="27" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F26" s="392"/>
+      <c r="G26" s="387"/>
+    </row>
+    <row r="27" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A27" s="41"/>
       <c r="B27" s="41"/>
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="393"/>
-      <c r="G27" s="388"/>
-    </row>
-    <row r="28" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="F27" s="392"/>
+      <c r="G27" s="387"/>
+    </row>
+    <row r="28" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A28" s="38"/>
       <c r="B28" s="38"/>
       <c r="C28" s="38"/>
@@ -13744,13 +13770,13 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="394" t="str">
+      <c r="F28" s="393" t="str">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="388"/>
-    </row>
-    <row r="29" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="G28" s="387"/>
+    </row>
+    <row r="29" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A29" s="38"/>
       <c r="B29" s="38"/>
       <c r="C29" s="39"/>
@@ -13762,22 +13788,22 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="394" t="str">
+      <c r="F29" s="393" t="str">
         <f>차량인보이스!I22</f>
         <v>0</v>
       </c>
-      <c r="G29" s="388"/>
-    </row>
-    <row r="30" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="G29" s="387"/>
+    </row>
+    <row r="30" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A30" s="38"/>
       <c r="B30" s="38"/>
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
       <c r="E30" s="50"/>
-      <c r="F30" s="395"/>
-      <c r="G30" s="396"/>
-    </row>
-    <row r="31" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="F30" s="394"/>
+      <c r="G30" s="395"/>
+    </row>
+    <row r="31" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A31" s="38"/>
       <c r="B31" s="38"/>
       <c r="C31" s="38"/>
@@ -13789,11 +13815,11 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="394" t="str">
+      <c r="F31" s="393" t="str">
         <f>SUM(F28:G29)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="388"/>
+      <c r="G31" s="387"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="38"/>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -10076,8 +10076,12 @@
         </is>
       </c>
       <c r="D9" s="304"/>
-      <c r="E9" s="305"/>
-      <c r="G9" s="304"/>
+      <c r="E9" s="184" t="str">
+        <f>구매리스트!D4</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
       <c r="H9" s="180" t="inlineStr">
         <is>
           <r>
@@ -11147,7 +11151,6 @@
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="E8:G9"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="K33:N33"/>
     <mergeCell ref="A49:J49"/>
@@ -11225,6 +11228,8 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="G34:K34"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.31496062992126" right="0.23622047244094" top="0.45" bottom="0.51181102362205" header="0.31496062992126" footer="0.31496062992126"/>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="380">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -207,6 +207,9 @@
     <r>
       <t xml:space="preserve">5</t>
     </r>
+  </si>
+  <si>
+    <t>최대적재량</t>
   </si>
   <si>
     <r>
@@ -3524,7 +3527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="399">
+  <cellXfs count="401">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4476,9 +4479,6 @@
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4721,6 +4721,15 @@
     </xf>
     <xf xfId="0" fontId="73" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="29" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5948,12 +5957,8 @@
           </r>
         </is>
       </c>
-      <c r="H9" s="103" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
+      <c r="H9" s="103" t="s">
+        <v>36</v>
       </c>
       <c r="I9" s="101" t="inlineStr">
         <is>
@@ -7044,8 +7049,8 @@
     </row>
     <row r="15" spans="1:20" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="396" t="s">
-        <v>104</v>
+      <c r="J15" s="395" t="s">
+        <v>105</v>
       </c>
       <c r="Q15" s="262"/>
     </row>
@@ -7421,7 +7426,8 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="11" t="str">
+        <f>구매리스트!I9</f>
         <v>0</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -8688,8 +8694,8 @@
     </row>
     <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="397" t="s">
-        <v>190</v>
+      <c r="J15" s="396" t="s">
+        <v>191</v>
       </c>
       <c r="Q15" s="262"/>
       <c r="W15" s="245" t="inlineStr">
@@ -9054,7 +9060,8 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="120">
+      <c r="I23" s="400" t="str">
+        <f>구매리스트!I9</f>
         <v>0</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -10235,12 +10242,9 @@
       </c>
       <c r="I14" s="315"/>
       <c r="J14" s="313"/>
-      <c r="K14" s="317" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">자가용</t>
-          </r>
-        </is>
+      <c r="K14" s="309" t="str">
+        <f>구매리스트!B8</f>
+        <v>0</v>
       </c>
       <c r="L14" s="315"/>
       <c r="M14" s="315"/>
@@ -10272,18 +10276,18 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="318"/>
-      <c r="E16" s="319"/>
-      <c r="F16" s="320"/>
-      <c r="G16" s="318"/>
-      <c r="H16" s="319"/>
-      <c r="I16" s="320"/>
-      <c r="J16" s="318"/>
-      <c r="K16" s="319"/>
-      <c r="L16" s="320"/>
-      <c r="M16" s="320"/>
-      <c r="N16" s="320"/>
-      <c r="O16" s="320"/>
+      <c r="D16" s="317"/>
+      <c r="E16" s="318"/>
+      <c r="F16" s="319"/>
+      <c r="G16" s="317"/>
+      <c r="H16" s="318"/>
+      <c r="I16" s="319"/>
+      <c r="J16" s="317"/>
+      <c r="K16" s="318"/>
+      <c r="L16" s="319"/>
+      <c r="M16" s="319"/>
+      <c r="N16" s="319"/>
+      <c r="O16" s="319"/>
     </row>
     <row r="17" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
       <c r="B17" s="304"/>
@@ -10340,7 +10344,7 @@
     </row>
     <row r="19" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A19" s="252"/>
-      <c r="B19" s="321"/>
+      <c r="B19" s="320"/>
       <c r="C19" s="182" t="inlineStr">
         <is>
           <r>
@@ -10348,10 +10352,10 @@
           </r>
         </is>
       </c>
-      <c r="D19" s="321"/>
-      <c r="E19" s="322"/>
+      <c r="D19" s="320"/>
+      <c r="E19" s="321"/>
       <c r="F19" s="252"/>
-      <c r="G19" s="321"/>
+      <c r="G19" s="320"/>
       <c r="H19" s="182" t="inlineStr">
         <is>
           <r>
@@ -10360,8 +10364,8 @@
         </is>
       </c>
       <c r="I19" s="252"/>
-      <c r="J19" s="321"/>
-      <c r="K19" s="322"/>
+      <c r="J19" s="320"/>
+      <c r="K19" s="321"/>
       <c r="L19" s="252"/>
       <c r="M19" s="252"/>
       <c r="N19" s="252"/>
@@ -10401,7 +10405,7 @@
         </is>
       </c>
       <c r="D21" s="303"/>
-      <c r="E21" s="323" t="inlineStr">
+      <c r="E21" s="398" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">주식회사싼카</t>
@@ -10419,7 +10423,7 @@
       </c>
       <c r="I21" s="250"/>
       <c r="J21" s="303"/>
-      <c r="K21" s="323" t="inlineStr">
+      <c r="K21" s="322" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">120111-0922270</t>
@@ -10439,7 +10443,7 @@
           </r>
         </is>
       </c>
-      <c r="B22" s="321"/>
+      <c r="B22" s="320"/>
       <c r="C22" s="182" t="inlineStr">
         <is>
           <r>
@@ -10447,10 +10451,10 @@
           </r>
         </is>
       </c>
-      <c r="D22" s="321"/>
-      <c r="E22" s="322"/>
+      <c r="D22" s="320"/>
+      <c r="E22" s="321"/>
       <c r="F22" s="252"/>
-      <c r="G22" s="321"/>
+      <c r="G22" s="320"/>
       <c r="H22" s="186" t="inlineStr">
         <is>
           <r>
@@ -10460,12 +10464,12 @@
         </is>
       </c>
       <c r="I22" s="252"/>
-      <c r="J22" s="321"/>
-      <c r="K22" s="322"/>
+      <c r="J22" s="320"/>
+      <c r="K22" s="321"/>
       <c r="L22" s="252"/>
       <c r="M22" s="252"/>
       <c r="N22" s="252"/>
-      <c r="O22" s="321"/>
+      <c r="O22" s="320"/>
     </row>
     <row r="23" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A23" s="84"/>
@@ -10495,7 +10499,7 @@
       <c r="B24" s="250"/>
       <c r="C24" s="250"/>
       <c r="D24" s="303"/>
-      <c r="E24" s="324" t="str">
+      <c r="E24" s="323" t="str">
         <f>구매리스트!B7</f>
         <v>0</v>
       </c>
@@ -10510,7 +10514,7 @@
       </c>
       <c r="I24" s="250"/>
       <c r="J24" s="303"/>
-      <c r="K24" s="325" t="inlineStr">
+      <c r="K24" s="324" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">증명용</t>
@@ -10530,12 +10534,12 @@
           </r>
         </is>
       </c>
-      <c r="B25" s="326"/>
-      <c r="C25" s="326"/>
-      <c r="D25" s="327"/>
-      <c r="E25" s="328"/>
-      <c r="F25" s="326"/>
-      <c r="G25" s="327"/>
+      <c r="B25" s="325"/>
+      <c r="C25" s="325"/>
+      <c r="D25" s="326"/>
+      <c r="E25" s="327"/>
+      <c r="F25" s="325"/>
+      <c r="G25" s="326"/>
       <c r="H25" s="215" t="inlineStr">
         <is>
           <r>
@@ -10543,13 +10547,13 @@
           </r>
         </is>
       </c>
-      <c r="I25" s="326"/>
-      <c r="J25" s="327"/>
-      <c r="K25" s="328"/>
-      <c r="L25" s="326"/>
-      <c r="M25" s="326"/>
-      <c r="N25" s="326"/>
-      <c r="O25" s="327"/>
+      <c r="I25" s="325"/>
+      <c r="J25" s="326"/>
+      <c r="K25" s="327"/>
+      <c r="L25" s="325"/>
+      <c r="M25" s="325"/>
+      <c r="N25" s="325"/>
+      <c r="O25" s="326"/>
     </row>
     <row r="26" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A26" s="213" t="inlineStr">
@@ -10612,10 +10616,10 @@
       </c>
       <c r="B27" s="252"/>
       <c r="C27" s="252"/>
-      <c r="D27" s="321"/>
-      <c r="E27" s="322"/>
+      <c r="D27" s="320"/>
+      <c r="E27" s="321"/>
       <c r="F27" s="252"/>
-      <c r="G27" s="321"/>
+      <c r="G27" s="320"/>
       <c r="H27" s="182" t="inlineStr">
         <is>
           <r>
@@ -10624,7 +10628,7 @@
         </is>
       </c>
       <c r="I27" s="252"/>
-      <c r="J27" s="321"/>
+      <c r="J27" s="320"/>
       <c r="K27" s="98" t="inlineStr">
         <is>
           <r>
@@ -10751,8 +10755,8 @@
       <c r="D34" s="77"/>
       <c r="E34" s="77"/>
       <c r="F34" s="77"/>
-      <c r="G34" s="398" t="s">
-        <v>104</v>
+      <c r="G34" s="397" t="s">
+        <v>105</v>
       </c>
       <c r="H34" s="77"/>
       <c r="I34" s="77"/>
@@ -10804,20 +10808,20 @@
           </r>
         </is>
       </c>
-      <c r="B38" s="329"/>
-      <c r="C38" s="329"/>
-      <c r="D38" s="329"/>
-      <c r="E38" s="329"/>
-      <c r="F38" s="329"/>
-      <c r="G38" s="329"/>
-      <c r="H38" s="329"/>
-      <c r="I38" s="329"/>
-      <c r="J38" s="329"/>
-      <c r="K38" s="329"/>
-      <c r="L38" s="329"/>
-      <c r="M38" s="329"/>
-      <c r="N38" s="329"/>
-      <c r="O38" s="329"/>
+      <c r="B38" s="328"/>
+      <c r="C38" s="328"/>
+      <c r="D38" s="328"/>
+      <c r="E38" s="328"/>
+      <c r="F38" s="328"/>
+      <c r="G38" s="328"/>
+      <c r="H38" s="328"/>
+      <c r="I38" s="328"/>
+      <c r="J38" s="328"/>
+      <c r="K38" s="328"/>
+      <c r="L38" s="328"/>
+      <c r="M38" s="328"/>
+      <c r="N38" s="328"/>
+      <c r="O38" s="328"/>
     </row>
     <row r="39" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A39" s="220" t="inlineStr">
@@ -10827,20 +10831,20 @@
           </r>
         </is>
       </c>
-      <c r="B39" s="330"/>
-      <c r="C39" s="330"/>
-      <c r="D39" s="330"/>
-      <c r="E39" s="330"/>
-      <c r="F39" s="330"/>
-      <c r="G39" s="330"/>
-      <c r="H39" s="330"/>
-      <c r="I39" s="330"/>
-      <c r="J39" s="330"/>
-      <c r="K39" s="330"/>
-      <c r="L39" s="330"/>
-      <c r="M39" s="330"/>
-      <c r="N39" s="330"/>
-      <c r="O39" s="330"/>
+      <c r="B39" s="329"/>
+      <c r="C39" s="329"/>
+      <c r="D39" s="329"/>
+      <c r="E39" s="329"/>
+      <c r="F39" s="329"/>
+      <c r="G39" s="329"/>
+      <c r="H39" s="329"/>
+      <c r="I39" s="329"/>
+      <c r="J39" s="329"/>
+      <c r="K39" s="329"/>
+      <c r="L39" s="329"/>
+      <c r="M39" s="329"/>
+      <c r="N39" s="329"/>
+      <c r="O39" s="329"/>
     </row>
     <row r="40" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="191" t="inlineStr">
@@ -10877,15 +10881,15 @@
           </r>
         </is>
       </c>
-      <c r="B43" s="331"/>
-      <c r="C43" s="331"/>
-      <c r="D43" s="331"/>
-      <c r="E43" s="331"/>
-      <c r="F43" s="331"/>
-      <c r="G43" s="331"/>
-      <c r="H43" s="331"/>
-      <c r="I43" s="331"/>
-      <c r="J43" s="332"/>
+      <c r="B43" s="330"/>
+      <c r="C43" s="330"/>
+      <c r="D43" s="330"/>
+      <c r="E43" s="330"/>
+      <c r="F43" s="330"/>
+      <c r="G43" s="330"/>
+      <c r="H43" s="330"/>
+      <c r="I43" s="330"/>
+      <c r="J43" s="331"/>
       <c r="K43" s="222" t="inlineStr">
         <is>
           <r>
@@ -10893,10 +10897,10 @@
           </r>
         </is>
       </c>
-      <c r="L43" s="331"/>
-      <c r="M43" s="331"/>
-      <c r="N43" s="331"/>
-      <c r="O43" s="332"/>
+      <c r="L43" s="330"/>
+      <c r="M43" s="330"/>
+      <c r="N43" s="330"/>
+      <c r="O43" s="331"/>
     </row>
     <row r="44" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="76" t="inlineStr">
@@ -10925,7 +10929,7 @@
       <c r="L44" s="308"/>
       <c r="M44" s="308"/>
       <c r="N44" s="308"/>
-      <c r="O44" s="333"/>
+      <c r="O44" s="332"/>
     </row>
     <row r="45" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="76" t="inlineStr">
@@ -10944,8 +10948,8 @@
       <c r="H45" s="76"/>
       <c r="I45" s="76"/>
       <c r="J45" s="76"/>
-      <c r="K45" s="334"/>
-      <c r="O45" s="335"/>
+      <c r="K45" s="333"/>
+      <c r="O45" s="334"/>
     </row>
     <row r="46" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A46" s="223" t="inlineStr">
@@ -10955,8 +10959,8 @@
           </r>
         </is>
       </c>
-      <c r="K46" s="334"/>
-      <c r="O46" s="335"/>
+      <c r="K46" s="333"/>
+      <c r="O46" s="334"/>
     </row>
     <row r="47" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A47" s="191" t="inlineStr">
@@ -10966,8 +10970,8 @@
           </r>
         </is>
       </c>
-      <c r="K47" s="334"/>
-      <c r="O47" s="335"/>
+      <c r="K47" s="333"/>
+      <c r="O47" s="334"/>
     </row>
     <row r="48" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A48" s="191" t="inlineStr">
@@ -10977,8 +10981,8 @@
           </r>
         </is>
       </c>
-      <c r="K48" s="334"/>
-      <c r="O48" s="335"/>
+      <c r="K48" s="333"/>
+      <c r="O48" s="334"/>
     </row>
     <row r="49" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A49" s="191" t="inlineStr">
@@ -10989,8 +10993,8 @@
         </is>
       </c>
       <c r="B49" s="245"/>
-      <c r="K49" s="334"/>
-      <c r="O49" s="335"/>
+      <c r="K49" s="333"/>
+      <c r="O49" s="334"/>
     </row>
     <row r="50" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A50" s="195" t="inlineStr">
@@ -11009,7 +11013,7 @@
       <c r="H50" s="308"/>
       <c r="I50" s="308"/>
       <c r="J50" s="308"/>
-      <c r="K50" s="336" t="inlineStr">
+      <c r="K50" s="335" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 6개월 이내</t>
@@ -11019,7 +11023,7 @@
       <c r="L50" s="308"/>
       <c r="M50" s="308"/>
       <c r="N50" s="308"/>
-      <c r="O50" s="333"/>
+      <c r="O50" s="332"/>
     </row>
     <row r="51" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A51" s="192" t="inlineStr">
@@ -11038,11 +11042,11 @@
       <c r="H51" s="312"/>
       <c r="I51" s="312"/>
       <c r="J51" s="312"/>
-      <c r="K51" s="337"/>
+      <c r="K51" s="336"/>
       <c r="L51" s="312"/>
       <c r="M51" s="312"/>
       <c r="N51" s="312"/>
-      <c r="O51" s="338"/>
+      <c r="O51" s="337"/>
     </row>
     <row r="52" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A52" s="193" t="inlineStr">
@@ -11052,15 +11056,15 @@
           </r>
         </is>
       </c>
-      <c r="B52" s="339"/>
-      <c r="C52" s="339"/>
-      <c r="D52" s="339"/>
-      <c r="E52" s="339"/>
-      <c r="F52" s="339"/>
-      <c r="G52" s="339"/>
-      <c r="H52" s="339"/>
-      <c r="I52" s="339"/>
-      <c r="J52" s="339"/>
+      <c r="B52" s="338"/>
+      <c r="C52" s="338"/>
+      <c r="D52" s="338"/>
+      <c r="E52" s="338"/>
+      <c r="F52" s="338"/>
+      <c r="G52" s="338"/>
+      <c r="H52" s="338"/>
+      <c r="I52" s="338"/>
+      <c r="J52" s="338"/>
       <c r="K52" s="194" t="inlineStr">
         <is>
           <r>
@@ -11068,10 +11072,10 @@
           </r>
         </is>
       </c>
-      <c r="L52" s="339"/>
-      <c r="M52" s="339"/>
-      <c r="N52" s="339"/>
-      <c r="O52" s="340"/>
+      <c r="L52" s="338"/>
+      <c r="M52" s="338"/>
+      <c r="N52" s="338"/>
+      <c r="O52" s="339"/>
     </row>
     <row r="53" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A53" s="189" t="inlineStr">
@@ -11089,7 +11093,7 @@
       <c r="G53" s="252"/>
       <c r="H53" s="252"/>
       <c r="I53" s="252"/>
-      <c r="J53" s="341"/>
+      <c r="J53" s="340"/>
       <c r="K53" s="188" t="inlineStr">
         <is>
           <r>
@@ -11269,7 +11273,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="47.25" s="245" customFormat="1">
-      <c r="A1" s="342" t="inlineStr">
+      <c r="A1" s="341" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL INVOICE</t>
@@ -11286,7 +11290,7 @@
       <c r="I1" s="255"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A2" s="343" t="inlineStr">
+      <c r="A2" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
@@ -11308,7 +11312,7 @@
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
-      <c r="H2" s="344" t="inlineStr">
+      <c r="H2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
@@ -11318,7 +11322,7 @@
       <c r="I2" s="251"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A3" s="345" t="inlineStr">
+      <c r="A3" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR LTD.,
@@ -11347,7 +11351,7 @@
     <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A4" s="271"/>
       <c r="D4" s="262"/>
-      <c r="E4" s="346" t="inlineStr">
+      <c r="E4" s="345" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
@@ -11365,7 +11369,7 @@
     <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A6" s="271"/>
       <c r="D6" s="262"/>
-      <c r="E6" s="347" t="inlineStr">
+      <c r="E6" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
@@ -11379,7 +11383,7 @@
       <c r="B7" s="252"/>
       <c r="C7" s="252"/>
       <c r="D7" s="253"/>
-      <c r="E7" s="347" t="inlineStr">
+      <c r="E7" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
@@ -11389,7 +11393,7 @@
       <c r="I7" s="262"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A8" s="343" t="inlineStr">
+      <c r="A8" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
@@ -11399,7 +11403,7 @@
       <c r="B8" s="250"/>
       <c r="C8" s="250"/>
       <c r="D8" s="251"/>
-      <c r="E8" s="348" t="inlineStr">
+      <c r="E8" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
@@ -11412,7 +11416,7 @@
       <c r="I8" s="253"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
-      <c r="A9" s="349" t="str">
+      <c r="A9" s="348" t="str">
         <f>구매리스트!B14</f>
         <v>0</v>
       </c>
@@ -11466,7 +11470,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A12" s="343" t="inlineStr">
+      <c r="A12" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
@@ -11476,7 +11480,7 @@
       <c r="B12" s="250"/>
       <c r="C12" s="250"/>
       <c r="D12" s="251"/>
-      <c r="E12" s="343" t="inlineStr">
+      <c r="E12" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
@@ -11489,7 +11493,7 @@
       <c r="I12" s="251"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A13" s="350" t="inlineStr">
+      <c r="A13" s="349" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
@@ -11518,7 +11522,7 @@
       <c r="I14" s="253"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
-      <c r="A15" s="343" t="inlineStr">
+      <c r="A15" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
@@ -11552,12 +11556,12 @@
         <v>0</v>
       </c>
       <c r="B16" s="252"/>
-      <c r="C16" s="351" t="str">
+      <c r="C16" s="350" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
       <c r="D16" s="253"/>
-      <c r="E16" s="352" t="inlineStr">
+      <c r="E16" s="351" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11567,7 +11571,7 @@
       <c r="I16" s="262"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
-      <c r="A17" s="343" t="inlineStr">
+      <c r="A17" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
@@ -11583,7 +11587,7 @@
         </is>
       </c>
       <c r="D17" s="251"/>
-      <c r="E17" s="353" t="str">
+      <c r="E17" s="352" t="str">
         <f>구매리스트!D12</f>
         <v>0</v>
       </c>
@@ -11593,12 +11597,12 @@
       <c r="I17" s="251"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
-      <c r="A18" s="351" t="str">
+      <c r="A18" s="350" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
       <c r="B18" s="253"/>
-      <c r="C18" s="354" t="str">
+      <c r="C18" s="353" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
@@ -11626,7 +11630,7 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="355" t="inlineStr">
+      <c r="E19" s="354" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
@@ -11696,7 +11700,7 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="356" t="inlineStr">
+      <c r="E21" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
@@ -11704,21 +11708,21 @@
         </is>
       </c>
       <c r="F21" s="255"/>
-      <c r="G21" s="357" t="inlineStr">
+      <c r="G21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="358" t="inlineStr">
+      <c r="H21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
           </r>
         </is>
       </c>
-      <c r="I21" s="359" t="inlineStr">
+      <c r="I21" s="358" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Shipping</t>
@@ -11728,7 +11732,7 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A22" s="360">
+      <c r="A22" s="359">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -11743,7 +11747,7 @@
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="E22" s="361">
+      <c r="E22" s="399">
         <v>1</v>
       </c>
       <c r="F22" s="255"/>
@@ -11765,8 +11769,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A23" s="363"/>
-      <c r="B23" s="364"/>
+      <c r="A23" s="362"/>
+      <c r="B23" s="363"/>
       <c r="C23" s="254"/>
       <c r="D23" s="254"/>
       <c r="E23" s="254"/>
@@ -11774,13 +11778,13 @@
       <c r="G23" s="254"/>
       <c r="H23" s="254"/>
       <c r="I23" s="255"/>
-      <c r="J23" s="362"/>
+      <c r="J23" s="361"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A24" s="363">
+      <c r="A24" s="362">
         <v>2</v>
       </c>
-      <c r="B24" s="365" t="inlineStr">
+      <c r="B24" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11801,9 +11805,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="366"/>
+      <c r="E24" s="365"/>
       <c r="F24" s="255"/>
-      <c r="G24" s="367" t="inlineStr">
+      <c r="G24" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11817,20 +11821,20 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="362">
+      <c r="I24" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="361">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A25" s="363"/>
-      <c r="B25" s="364" t="inlineStr">
+      <c r="A25" s="362"/>
+      <c r="B25" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11844,13 +11848,13 @@
       <c r="G25" s="254"/>
       <c r="H25" s="254"/>
       <c r="I25" s="255"/>
-      <c r="J25" s="362"/>
+      <c r="J25" s="361"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A26" s="363">
+      <c r="A26" s="362">
         <v>3</v>
       </c>
-      <c r="B26" s="365" t="inlineStr">
+      <c r="B26" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11871,9 +11875,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="366"/>
+      <c r="E26" s="365"/>
       <c r="F26" s="255"/>
-      <c r="G26" s="367" t="inlineStr">
+      <c r="G26" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11887,20 +11891,20 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="362">
+      <c r="I26" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="361">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A27" s="363"/>
-      <c r="B27" s="364" t="inlineStr">
+      <c r="A27" s="362"/>
+      <c r="B27" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11914,13 +11918,13 @@
       <c r="G27" s="254"/>
       <c r="H27" s="254"/>
       <c r="I27" s="255"/>
-      <c r="J27" s="362"/>
+      <c r="J27" s="361"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A28" s="363">
+      <c r="A28" s="362">
         <v>4</v>
       </c>
-      <c r="B28" s="369" t="inlineStr">
+      <c r="B28" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11941,9 +11945,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="366"/>
+      <c r="E28" s="365"/>
       <c r="F28" s="255"/>
-      <c r="G28" s="367" t="inlineStr">
+      <c r="G28" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11957,26 +11961,26 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="362">
+      <c r="I28" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="361">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A29" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="364" t="inlineStr">
+      <c r="A29" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11993,10 +11997,10 @@
       <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A30" s="363">
+      <c r="A30" s="362">
         <v>5</v>
       </c>
-      <c r="B30" s="369" t="inlineStr">
+      <c r="B30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12017,9 +12021,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="366"/>
+      <c r="E30" s="365"/>
       <c r="F30" s="255"/>
-      <c r="G30" s="367" t="inlineStr">
+      <c r="G30" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12033,7 +12037,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="368" t="inlineStr">
+      <c r="I30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12043,14 +12047,14 @@
       <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A31" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="364" t="inlineStr">
+      <c r="A31" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12075,7 +12079,7 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="370"/>
+      <c r="C32" s="369"/>
       <c r="D32" s="233" t="inlineStr">
         <is>
           <r>
@@ -12083,14 +12087,14 @@
           </r>
         </is>
       </c>
-      <c r="E32" s="370"/>
+      <c r="E32" s="369"/>
       <c r="F32" s="233"/>
       <c r="G32" s="233"/>
       <c r="H32" s="227" t="str">
         <f>SUM(H22:I22,H24:I24,H26:I26,H28:I28,H30:I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="371"/>
+      <c r="I32" s="370"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
@@ -12295,7 +12299,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="47.25" s="245" customFormat="1">
-      <c r="A1" s="342" t="inlineStr">
+      <c r="A1" s="341" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL PACKING LIST</t>
@@ -12312,7 +12316,7 @@
       <c r="I1" s="255"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A2" s="343" t="inlineStr">
+      <c r="A2" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
@@ -12334,7 +12338,7 @@
         <f>차량인보이스!G2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="344" t="inlineStr">
+      <c r="H2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
@@ -12344,7 +12348,7 @@
       <c r="I2" s="251"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A3" s="345" t="inlineStr">
+      <c r="A3" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR LTD.,
@@ -12373,7 +12377,7 @@
     <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A4" s="271"/>
       <c r="D4" s="262"/>
-      <c r="E4" s="346" t="inlineStr">
+      <c r="E4" s="345" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
@@ -12391,7 +12395,7 @@
     <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A6" s="271"/>
       <c r="D6" s="262"/>
-      <c r="E6" s="347" t="inlineStr">
+      <c r="E6" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
@@ -12405,7 +12409,7 @@
       <c r="B7" s="252"/>
       <c r="C7" s="252"/>
       <c r="D7" s="253"/>
-      <c r="E7" s="347" t="inlineStr">
+      <c r="E7" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
@@ -12415,7 +12419,7 @@
       <c r="I7" s="262"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A8" s="343" t="inlineStr">
+      <c r="A8" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
@@ -12425,7 +12429,7 @@
       <c r="B8" s="250"/>
       <c r="C8" s="250"/>
       <c r="D8" s="251"/>
-      <c r="E8" s="348" t="inlineStr">
+      <c r="E8" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
@@ -12438,7 +12442,7 @@
       <c r="I8" s="253"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
-      <c r="A9" s="372" t="str">
+      <c r="A9" s="371" t="str">
         <f>차량인보이스!A9</f>
         <v>0</v>
       </c>
@@ -12492,7 +12496,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A12" s="343" t="inlineStr">
+      <c r="A12" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
@@ -12502,7 +12506,7 @@
       <c r="B12" s="250"/>
       <c r="C12" s="250"/>
       <c r="D12" s="251"/>
-      <c r="E12" s="343" t="inlineStr">
+      <c r="E12" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
@@ -12515,7 +12519,7 @@
       <c r="I12" s="251"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A13" s="350" t="inlineStr">
+      <c r="A13" s="349" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
@@ -12544,7 +12548,7 @@
       <c r="I14" s="253"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
-      <c r="A15" s="343" t="inlineStr">
+      <c r="A15" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
@@ -12578,12 +12582,12 @@
         <v>0</v>
       </c>
       <c r="B16" s="252"/>
-      <c r="C16" s="351" t="str">
+      <c r="C16" s="350" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
       <c r="D16" s="253"/>
-      <c r="E16" s="352" t="inlineStr">
+      <c r="E16" s="351" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12593,7 +12597,7 @@
       <c r="I16" s="262"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
-      <c r="A17" s="343" t="inlineStr">
+      <c r="A17" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
@@ -12609,7 +12613,7 @@
         </is>
       </c>
       <c r="D17" s="251"/>
-      <c r="E17" s="353" t="str">
+      <c r="E17" s="352" t="str">
         <f>차량인보이스!E17</f>
         <v>0</v>
       </c>
@@ -12619,12 +12623,12 @@
       <c r="I17" s="251"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
-      <c r="A18" s="351" t="str">
+      <c r="A18" s="350" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
       <c r="B18" s="253"/>
-      <c r="C18" s="354" t="str">
+      <c r="C18" s="353" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
@@ -12652,7 +12656,7 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="355" t="inlineStr">
+      <c r="E19" s="354" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
@@ -12722,7 +12726,7 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="356" t="inlineStr">
+      <c r="E21" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
@@ -12730,14 +12734,14 @@
         </is>
       </c>
       <c r="F21" s="255"/>
-      <c r="G21" s="357" t="inlineStr">
+      <c r="G21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="358" t="inlineStr">
+      <c r="H21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
@@ -12755,7 +12759,7 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A22" s="360">
+      <c r="A22" s="359">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -12770,19 +12774,19 @@
         <f>차량인보이스!D22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="361" t="str">
+      <c r="E22" s="360" t="str">
         <f>차량인보이스!E22</f>
         <v>0</v>
       </c>
       <c r="F22" s="255"/>
-      <c r="G22" s="373" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="H22" s="373" t="inlineStr">
+      <c r="G22" s="372" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H22" s="372" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12793,7 +12797,7 @@
         <f>구매리스트!I8</f>
         <v>0</v>
       </c>
-      <c r="J22" s="362" t="inlineStr">
+      <c r="J22" s="361" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12802,8 +12806,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A23" s="363"/>
-      <c r="B23" s="364"/>
+      <c r="A23" s="362"/>
+      <c r="B23" s="363"/>
       <c r="C23" s="254"/>
       <c r="D23" s="254"/>
       <c r="E23" s="254"/>
@@ -12811,13 +12815,13 @@
       <c r="G23" s="254"/>
       <c r="H23" s="254"/>
       <c r="I23" s="255"/>
-      <c r="J23" s="362"/>
+      <c r="J23" s="361"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A24" s="363">
+      <c r="A24" s="362">
         <v>2</v>
       </c>
-      <c r="B24" s="365" t="inlineStr">
+      <c r="B24" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12838,9 +12842,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="366"/>
+      <c r="E24" s="365"/>
       <c r="F24" s="255"/>
-      <c r="G24" s="367" t="inlineStr">
+      <c r="G24" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12854,14 +12858,14 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="362" t="inlineStr">
+      <c r="I24" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="361" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12870,8 +12874,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A25" s="363"/>
-      <c r="B25" s="364" t="inlineStr">
+      <c r="A25" s="362"/>
+      <c r="B25" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12885,13 +12889,13 @@
       <c r="G25" s="254"/>
       <c r="H25" s="254"/>
       <c r="I25" s="255"/>
-      <c r="J25" s="362"/>
+      <c r="J25" s="361"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A26" s="363">
+      <c r="A26" s="362">
         <v>3</v>
       </c>
-      <c r="B26" s="365" t="inlineStr">
+      <c r="B26" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12912,9 +12916,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="366"/>
+      <c r="E26" s="365"/>
       <c r="F26" s="255"/>
-      <c r="G26" s="367" t="inlineStr">
+      <c r="G26" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12928,14 +12932,14 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="362" t="inlineStr">
+      <c r="I26" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="361" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12944,8 +12948,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A27" s="363"/>
-      <c r="B27" s="364" t="inlineStr">
+      <c r="A27" s="362"/>
+      <c r="B27" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12959,13 +12963,13 @@
       <c r="G27" s="254"/>
       <c r="H27" s="254"/>
       <c r="I27" s="255"/>
-      <c r="J27" s="362"/>
+      <c r="J27" s="361"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A28" s="363">
+      <c r="A28" s="362">
         <v>4</v>
       </c>
-      <c r="B28" s="369" t="inlineStr">
+      <c r="B28" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12986,9 +12990,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="366"/>
+      <c r="E28" s="365"/>
       <c r="F28" s="255"/>
-      <c r="G28" s="367" t="inlineStr">
+      <c r="G28" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13002,14 +13006,14 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="362" t="inlineStr">
+      <c r="I28" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="361" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13018,14 +13022,14 @@
       </c>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A29" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="364" t="inlineStr">
+      <c r="A29" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13042,10 +13046,10 @@
       <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A30" s="363">
+      <c r="A30" s="362">
         <v>5</v>
       </c>
-      <c r="B30" s="369" t="inlineStr">
+      <c r="B30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13066,9 +13070,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="366"/>
+      <c r="E30" s="365"/>
       <c r="F30" s="255"/>
-      <c r="G30" s="367" t="inlineStr">
+      <c r="G30" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13082,7 +13086,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="368" t="inlineStr">
+      <c r="I30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13092,14 +13096,14 @@
       <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A31" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="364" t="inlineStr">
+      <c r="A31" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13124,7 +13128,7 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="370"/>
+      <c r="C32" s="369"/>
       <c r="D32" s="235" t="inlineStr">
         <is>
           <r>
@@ -13132,14 +13136,14 @@
           </r>
         </is>
       </c>
-      <c r="E32" s="370"/>
+      <c r="E32" s="369"/>
       <c r="F32" s="235"/>
       <c r="G32" s="235"/>
       <c r="H32" s="236" t="str">
         <f>SUM(I22,I24,I26,I28,I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="371"/>
+      <c r="I32" s="370"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
@@ -13371,11 +13375,11 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="374" t="str">
+      <c r="F3" s="373" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="G3" s="375"/>
+      <c r="G3" s="374"/>
     </row>
     <row r="4" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A4" s="47"/>
@@ -13389,11 +13393,11 @@
           </r>
         </is>
       </c>
-      <c r="F4" s="376" t="str">
+      <c r="F4" s="375" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
-      <c r="G4" s="377"/>
+      <c r="G4" s="376"/>
     </row>
     <row r="5" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A5" s="238"/>
@@ -13405,11 +13409,11 @@
           </r>
         </is>
       </c>
-      <c r="F5" s="378" t="str">
+      <c r="F5" s="377" t="str">
         <f>구매리스트!D14</f>
         <v>0</v>
       </c>
-      <c r="G5" s="377"/>
+      <c r="G5" s="376"/>
     </row>
     <row r="6" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A6" s="238"/>
@@ -13421,8 +13425,8 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="379"/>
-      <c r="G6" s="377"/>
+      <c r="F6" s="378"/>
+      <c r="G6" s="376"/>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A7" s="238"/>
@@ -13433,8 +13437,8 @@
           </r>
         </is>
       </c>
-      <c r="F7" s="380"/>
-      <c r="G7" s="377"/>
+      <c r="F7" s="379"/>
+      <c r="G7" s="376"/>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A8" s="238"/>
@@ -13445,8 +13449,8 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="381"/>
-      <c r="G8" s="377"/>
+      <c r="F8" s="380"/>
+      <c r="G8" s="376"/>
     </row>
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A9" s="238"/>
@@ -13458,8 +13462,8 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="379"/>
-      <c r="G9" s="377"/>
+      <c r="F9" s="378"/>
+      <c r="G9" s="376"/>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A10" s="238"/>
@@ -13477,11 +13481,11 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="382" t="str">
+      <c r="F11" s="381" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G11" s="377"/>
+      <c r="G11" s="376"/>
     </row>
     <row r="12" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A12" s="237"/>
@@ -13492,11 +13496,11 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="382" t="str">
+      <c r="F12" s="381" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G12" s="377"/>
+      <c r="G12" s="376"/>
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A13" s="244"/>
@@ -13509,32 +13513,32 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="383" t="str">
+      <c r="F13" s="382" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="377"/>
+      <c r="G13" s="376"/>
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="17.25" s="245" customFormat="1">
       <c r="A14" s="244"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
-      <c r="E14" s="384"/>
+      <c r="E14" s="383"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
-      <c r="A15" s="385" t="inlineStr">
+      <c r="A15" s="384" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">BANK ACCOUNT INFORMATION</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="386"/>
-      <c r="C15" s="386"/>
-      <c r="D15" s="386"/>
-      <c r="E15" s="386"/>
-      <c r="F15" s="386"/>
-      <c r="G15" s="387"/>
+      <c r="B15" s="385"/>
+      <c r="C15" s="385"/>
+      <c r="D15" s="385"/>
+      <c r="E15" s="385"/>
+      <c r="F15" s="385"/>
+      <c r="G15" s="386"/>
     </row>
     <row r="16" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A16" s="239" t="inlineStr">
@@ -13544,15 +13548,15 @@
           </r>
         </is>
       </c>
-      <c r="B16" s="387"/>
-      <c r="C16" s="388" t="inlineStr">
+      <c r="B16" s="386"/>
+      <c r="C16" s="387" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR CO LTD</t>
           </r>
         </is>
       </c>
-      <c r="D16" s="387"/>
+      <c r="D16" s="386"/>
       <c r="E16" s="239" t="inlineStr">
         <is>
           <r>
@@ -13560,14 +13564,14 @@
           </r>
         </is>
       </c>
-      <c r="F16" s="389" t="inlineStr">
+      <c r="F16" s="388" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHINHAN BANK</t>
           </r>
         </is>
       </c>
-      <c r="G16" s="387"/>
+      <c r="G16" s="386"/>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A17" s="239" t="inlineStr">
@@ -13577,15 +13581,15 @@
           </r>
         </is>
       </c>
-      <c r="B17" s="387"/>
-      <c r="C17" s="388" t="inlineStr">
+      <c r="B17" s="386"/>
+      <c r="C17" s="387" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHBKKRSE</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="387"/>
+      <c r="D17" s="386"/>
       <c r="E17" s="239" t="inlineStr">
         <is>
           <r>
@@ -13600,7 +13604,7 @@
           </r>
         </is>
       </c>
-      <c r="G17" s="387"/>
+      <c r="G17" s="386"/>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A18" s="239" t="inlineStr">
@@ -13610,15 +13614,15 @@
           </r>
         </is>
       </c>
-      <c r="B18" s="387"/>
-      <c r="C18" s="388" t="inlineStr">
+      <c r="B18" s="386"/>
+      <c r="C18" s="387" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">180-008-400167</t>
           </r>
         </is>
       </c>
-      <c r="D18" s="387"/>
+      <c r="D18" s="386"/>
       <c r="E18" s="239" t="inlineStr">
         <is>
           <r>
@@ -13626,19 +13630,19 @@
           </r>
         </is>
       </c>
-      <c r="F18" s="390" t="inlineStr">
+      <c r="F18" s="389" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do,   SOUTH KOREA</t>
           </r>
         </is>
       </c>
-      <c r="G18" s="387"/>
+      <c r="G18" s="386"/>
     </row>
     <row r="19" spans="1:7">
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="384"/>
+      <c r="E19" s="383"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A20" s="42" t="inlineStr">
@@ -13683,7 +13687,7 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="387"/>
+      <c r="G20" s="386"/>
     </row>
     <row r="21" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A21" s="133" t="str">
@@ -13703,11 +13707,11 @@
         <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="391" t="str">
+      <c r="F21" s="390" t="str">
         <f>차량인보이스!H22</f>
         <v>0</v>
       </c>
-      <c r="G21" s="387"/>
+      <c r="G21" s="386"/>
     </row>
     <row r="22" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A22" s="41"/>
@@ -13715,8 +13719,8 @@
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="392"/>
-      <c r="G22" s="387"/>
+      <c r="F22" s="391"/>
+      <c r="G22" s="386"/>
     </row>
     <row r="23" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A23" s="41"/>
@@ -13724,8 +13728,8 @@
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="392"/>
-      <c r="G23" s="387"/>
+      <c r="F23" s="391"/>
+      <c r="G23" s="386"/>
     </row>
     <row r="24" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A24" s="41"/>
@@ -13733,8 +13737,8 @@
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="392"/>
-      <c r="G24" s="387"/>
+      <c r="F24" s="391"/>
+      <c r="G24" s="386"/>
     </row>
     <row r="25" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A25" s="41"/>
@@ -13742,8 +13746,8 @@
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="392"/>
-      <c r="G25" s="387"/>
+      <c r="F25" s="391"/>
+      <c r="G25" s="386"/>
     </row>
     <row r="26" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A26" s="41"/>
@@ -13751,8 +13755,8 @@
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="392"/>
-      <c r="G26" s="387"/>
+      <c r="F26" s="391"/>
+      <c r="G26" s="386"/>
     </row>
     <row r="27" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A27" s="41"/>
@@ -13760,8 +13764,8 @@
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="392"/>
-      <c r="G27" s="387"/>
+      <c r="F27" s="391"/>
+      <c r="G27" s="386"/>
     </row>
     <row r="28" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A28" s="38"/>
@@ -13775,11 +13779,11 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="393" t="str">
+      <c r="F28" s="392" t="str">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="387"/>
+      <c r="G28" s="386"/>
     </row>
     <row r="29" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A29" s="38"/>
@@ -13793,11 +13797,11 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="393" t="str">
+      <c r="F29" s="392" t="str">
         <f>차량인보이스!I22</f>
         <v>0</v>
       </c>
-      <c r="G29" s="387"/>
+      <c r="G29" s="386"/>
     </row>
     <row r="30" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A30" s="38"/>
@@ -13805,8 +13809,8 @@
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
       <c r="E30" s="50"/>
-      <c r="F30" s="394"/>
-      <c r="G30" s="395"/>
+      <c r="F30" s="393"/>
+      <c r="G30" s="394"/>
     </row>
     <row r="31" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A31" s="38"/>
@@ -13820,11 +13824,11 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="393" t="str">
+      <c r="F31" s="392" t="str">
         <f>SUM(F28:G29)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="387"/>
+      <c r="G31" s="386"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="38"/>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -3527,7 +3527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="401">
+  <cellXfs count="400">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4727,9 +4727,6 @@
     </xf>
     <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9060,7 +9057,7 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="400" t="str">
+      <c r="I23" s="11" t="str">
         <f>구매리스트!I9</f>
         <v>0</v>
       </c>
@@ -11465,7 +11462,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="53" t="str">
-        <f>구매리스트!D11</f>
+        <f>TODAY()</f>
         <v>0</v>
       </c>
     </row>
@@ -12491,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="53" t="str">
-        <f>구매리스트!D11</f>
+        <f>TODAY()</f>
         <v>0</v>
       </c>
     </row>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="6" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -1972,7 +1972,7 @@
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="74">
+  <fonts count="71">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -2592,33 +2592,6 @@
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
     </font>
     <font>
       <b val="0"/>
@@ -4662,15 +4635,6 @@
     <xf xfId="0" fontId="20" numFmtId="168" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="67" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="68" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="69" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="20" numFmtId="167" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4680,7 +4644,7 @@
     <xf xfId="0" fontId="18" numFmtId="179" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="70" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="67" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="63" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4713,13 +4677,13 @@
     <xf xfId="0" fontId="20" numFmtId="167" fillId="6" borderId="64" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="71" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="68" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="72" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="69" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="73" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="70" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="29" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4727,6 +4691,15 @@
     </xf>
     <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="20" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="24" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="19" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7046,7 +7019,7 @@
     </row>
     <row r="15" spans="1:20" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="395" t="s">
+      <c r="J15" s="392" t="s">
         <v>105</v>
       </c>
       <c r="Q15" s="262"/>
@@ -8691,7 +8664,7 @@
     </row>
     <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="396" t="s">
+      <c r="J15" s="393" t="s">
         <v>191</v>
       </c>
       <c r="Q15" s="262"/>
@@ -10402,7 +10375,7 @@
         </is>
       </c>
       <c r="D21" s="303"/>
-      <c r="E21" s="398" t="inlineStr">
+      <c r="E21" s="395" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">주식회사싼카</t>
@@ -10752,7 +10725,7 @@
       <c r="D34" s="77"/>
       <c r="E34" s="77"/>
       <c r="F34" s="77"/>
-      <c r="G34" s="397" t="s">
+      <c r="G34" s="394" t="s">
         <v>105</v>
       </c>
       <c r="H34" s="77"/>
@@ -11744,7 +11717,7 @@
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="E22" s="399">
+      <c r="E22" s="396">
         <v>1</v>
       </c>
       <c r="F22" s="255"/>
@@ -13422,7 +13395,7 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="378"/>
+      <c r="F6" s="397"/>
       <c r="G6" s="376"/>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
@@ -13434,7 +13407,7 @@
           </r>
         </is>
       </c>
-      <c r="F7" s="379"/>
+      <c r="F7" s="398"/>
       <c r="G7" s="376"/>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
@@ -13446,7 +13419,7 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="380"/>
+      <c r="F8" s="399"/>
       <c r="G8" s="376"/>
     </row>
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
@@ -13459,7 +13432,7 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="378"/>
+      <c r="F9" s="397"/>
       <c r="G9" s="376"/>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="245" customFormat="1">
@@ -13478,7 +13451,7 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="381" t="str">
+      <c r="F11" s="378" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
@@ -13493,7 +13466,7 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="381" t="str">
+      <c r="F12" s="378" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
@@ -13510,7 +13483,7 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="382" t="str">
+      <c r="F13" s="379" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
@@ -13520,22 +13493,22 @@
       <c r="A14" s="244"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
-      <c r="E14" s="383"/>
+      <c r="E14" s="380"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
-      <c r="A15" s="384" t="inlineStr">
+      <c r="A15" s="381" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">BANK ACCOUNT INFORMATION</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="385"/>
-      <c r="C15" s="385"/>
-      <c r="D15" s="385"/>
-      <c r="E15" s="385"/>
-      <c r="F15" s="385"/>
-      <c r="G15" s="386"/>
+      <c r="B15" s="382"/>
+      <c r="C15" s="382"/>
+      <c r="D15" s="382"/>
+      <c r="E15" s="382"/>
+      <c r="F15" s="382"/>
+      <c r="G15" s="383"/>
     </row>
     <row r="16" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A16" s="239" t="inlineStr">
@@ -13545,15 +13518,15 @@
           </r>
         </is>
       </c>
-      <c r="B16" s="386"/>
-      <c r="C16" s="387" t="inlineStr">
+      <c r="B16" s="383"/>
+      <c r="C16" s="384" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR CO LTD</t>
           </r>
         </is>
       </c>
-      <c r="D16" s="386"/>
+      <c r="D16" s="383"/>
       <c r="E16" s="239" t="inlineStr">
         <is>
           <r>
@@ -13561,14 +13534,14 @@
           </r>
         </is>
       </c>
-      <c r="F16" s="388" t="inlineStr">
+      <c r="F16" s="385" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHINHAN BANK</t>
           </r>
         </is>
       </c>
-      <c r="G16" s="386"/>
+      <c r="G16" s="383"/>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A17" s="239" t="inlineStr">
@@ -13578,15 +13551,15 @@
           </r>
         </is>
       </c>
-      <c r="B17" s="386"/>
-      <c r="C17" s="387" t="inlineStr">
+      <c r="B17" s="383"/>
+      <c r="C17" s="384" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHBKKRSE</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="386"/>
+      <c r="D17" s="383"/>
       <c r="E17" s="239" t="inlineStr">
         <is>
           <r>
@@ -13601,7 +13574,7 @@
           </r>
         </is>
       </c>
-      <c r="G17" s="386"/>
+      <c r="G17" s="383"/>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A18" s="239" t="inlineStr">
@@ -13611,15 +13584,15 @@
           </r>
         </is>
       </c>
-      <c r="B18" s="386"/>
-      <c r="C18" s="387" t="inlineStr">
+      <c r="B18" s="383"/>
+      <c r="C18" s="384" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">180-008-400167</t>
           </r>
         </is>
       </c>
-      <c r="D18" s="386"/>
+      <c r="D18" s="383"/>
       <c r="E18" s="239" t="inlineStr">
         <is>
           <r>
@@ -13627,19 +13600,19 @@
           </r>
         </is>
       </c>
-      <c r="F18" s="389" t="inlineStr">
+      <c r="F18" s="386" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do,   SOUTH KOREA</t>
           </r>
         </is>
       </c>
-      <c r="G18" s="386"/>
+      <c r="G18" s="383"/>
     </row>
     <row r="19" spans="1:7">
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="383"/>
+      <c r="E19" s="380"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A20" s="42" t="inlineStr">
@@ -13684,7 +13657,7 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="386"/>
+      <c r="G20" s="383"/>
     </row>
     <row r="21" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A21" s="133" t="str">
@@ -13704,11 +13677,11 @@
         <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="390" t="str">
+      <c r="F21" s="387" t="str">
         <f>차량인보이스!H22</f>
         <v>0</v>
       </c>
-      <c r="G21" s="386"/>
+      <c r="G21" s="383"/>
     </row>
     <row r="22" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A22" s="41"/>
@@ -13716,8 +13689,8 @@
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="391"/>
-      <c r="G22" s="386"/>
+      <c r="F22" s="388"/>
+      <c r="G22" s="383"/>
     </row>
     <row r="23" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A23" s="41"/>
@@ -13725,8 +13698,8 @@
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="391"/>
-      <c r="G23" s="386"/>
+      <c r="F23" s="388"/>
+      <c r="G23" s="383"/>
     </row>
     <row r="24" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A24" s="41"/>
@@ -13734,8 +13707,8 @@
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="391"/>
-      <c r="G24" s="386"/>
+      <c r="F24" s="388"/>
+      <c r="G24" s="383"/>
     </row>
     <row r="25" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A25" s="41"/>
@@ -13743,8 +13716,8 @@
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="391"/>
-      <c r="G25" s="386"/>
+      <c r="F25" s="388"/>
+      <c r="G25" s="383"/>
     </row>
     <row r="26" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A26" s="41"/>
@@ -13752,8 +13725,8 @@
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="391"/>
-      <c r="G26" s="386"/>
+      <c r="F26" s="388"/>
+      <c r="G26" s="383"/>
     </row>
     <row r="27" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A27" s="41"/>
@@ -13761,8 +13734,8 @@
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="391"/>
-      <c r="G27" s="386"/>
+      <c r="F27" s="388"/>
+      <c r="G27" s="383"/>
     </row>
     <row r="28" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A28" s="38"/>
@@ -13776,11 +13749,11 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="392" t="str">
+      <c r="F28" s="389" t="str">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="386"/>
+      <c r="G28" s="383"/>
     </row>
     <row r="29" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A29" s="38"/>
@@ -13794,11 +13767,11 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="392" t="str">
+      <c r="F29" s="389" t="str">
         <f>차량인보이스!I22</f>
         <v>0</v>
       </c>
-      <c r="G29" s="386"/>
+      <c r="G29" s="383"/>
     </row>
     <row r="30" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A30" s="38"/>
@@ -13806,8 +13779,8 @@
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
       <c r="E30" s="50"/>
-      <c r="F30" s="393"/>
-      <c r="G30" s="394"/>
+      <c r="F30" s="390"/>
+      <c r="G30" s="391"/>
     </row>
     <row r="31" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A31" s="38"/>
@@ -13821,11 +13794,11 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="392" t="str">
+      <c r="F31" s="389" t="str">
         <f>SUM(F28:G29)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="386"/>
+      <c r="G31" s="383"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="38"/>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -4749,22 +4749,17 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="1057275" cy="1028700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 32" descr=""/>
+        <xdr:cNvPr id="2" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4776,16 +4771,14 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1057275" cy="1028700"/>
-        </a:xfrm>
+        <a:xfrm rot="0"/>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4830,43 +4823,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>457200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 4" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1057275" cy="1028700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
       <xdr:row>11</xdr:row>
@@ -4880,13 +4836,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 12" descr=""/>
+        <xdr:cNvPr id="2" name="그림 12" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4902,6 +4858,36 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4946,43 +4932,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>447675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 4" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1247775" cy="1228725"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>48</xdr:row>
@@ -4996,13 +4945,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 7" descr=""/>
+        <xdr:cNvPr id="2" name="그림 7" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5018,6 +4967,36 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>447675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1247775" cy="1228725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -1600,13 +1600,12 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">SSANCAR LTD.,
-163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Kore
-TEL:82-505-366-9977 
-FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
-    </r>
+    <t>SSANCAR LTD.,
+163 Sangidaehak-ro, Siheung-si,
+Gyeonggi-do, Republic of Korea
+TEL:82-505-355-9977  
+FAX:82-505-366-9977 
+EMAIL : ssancar9977@gmail.com</t>
   </si>
   <si>
     <r>
@@ -1796,13 +1795,11 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">PROFORM INVOICE</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ssancar LTD 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea   Phone: +82-505-366-9977</t>
-    </r>
+      <t xml:space="preserve">PROFORMA INVOICE</t>
+    </r>
+  </si>
+  <si>
+    <t>Ssancar LTD 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea   Phone: +82-505-355-9977</t>
   </si>
   <si>
     <r>
@@ -1821,7 +1818,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Adress</t>
+      <t xml:space="preserve">Address</t>
     </r>
   </si>
   <si>
@@ -1876,7 +1873,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Swift Cose</t>
+      <t xml:space="preserve">Swift Code</t>
     </r>
   </si>
   <si>
@@ -1886,7 +1883,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Bank Adress</t>
+      <t xml:space="preserve">Bank Address</t>
     </r>
   </si>
   <si>
@@ -1906,7 +1903,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Beneficiary Adress</t>
+      <t xml:space="preserve">Beneficiary Address</t>
     </r>
   </si>
   <si>
@@ -4712,6 +4709,36 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4727,13 +4754,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 30" descr=""/>
+        <xdr:cNvPr id="2" name="그림 30" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4749,23 +4776,28 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
+      <xdr:colOff>638175</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1057275" cy="1028700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="govt_seal" descr=""/>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4779,11 +4811,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4799,13 +4826,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 3" descr=""/>
+        <xdr:cNvPr id="2" name="그림 3" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4836,13 +4863,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 12" descr=""/>
+        <xdr:cNvPr id="3" name="그림 12" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4858,23 +4885,28 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>447675</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:ext cx="1247775" cy="1228725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4888,11 +4920,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4908,13 +4935,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 2" descr=""/>
+        <xdr:cNvPr id="2" name="그림 2" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4945,13 +4972,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 7" descr=""/>
+        <xdr:cNvPr id="3" name="그림 7" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4967,36 +4994,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>447675</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1247775" cy="1228725"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0"/>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5569,7 +5566,20 @@
     <col min="12" max="12" width="11.75" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="245" customFormat="1"/>
+    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A1" s="245"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
+      <c r="I1" s="245"/>
+      <c r="J1" s="245"/>
+      <c r="K1" s="245"/>
+      <c r="L1" s="245"/>
+    </row>
     <row r="2" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A2" s="105" t="inlineStr">
         <is>
@@ -5578,6 +5588,10 @@
           </r>
         </is>
       </c>
+      <c r="B2" s="245"/>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
       <c r="F2" s="105" t="inlineStr">
         <is>
           <r>
@@ -5585,6 +5599,12 @@
           </r>
         </is>
       </c>
+      <c r="G2" s="245"/>
+      <c r="H2" s="245"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A3" s="103" t="inlineStr">
@@ -5609,6 +5629,7 @@
         </is>
       </c>
       <c r="D3" s="113"/>
+      <c r="E3" s="245"/>
       <c r="F3" s="106" t="inlineStr">
         <is>
           <r>
@@ -5627,6 +5648,9 @@
       <c r="I3" s="115">
         <v>45875</v>
       </c>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
     </row>
     <row r="4" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A4" s="103" t="inlineStr">
@@ -5686,6 +5710,9 @@
           </r>
         </is>
       </c>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A5" s="103" t="inlineStr">
@@ -5745,6 +5772,9 @@
           </r>
         </is>
       </c>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A6" s="103" t="inlineStr">
@@ -5793,6 +5823,9 @@
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"승용 소형","Small Passenger"),"승용 중형","Medium Passenger"),"승용 대형","HEAVY Passenger"),"중형 승합","Medium Ven"),"대형 승합","Large Ven"),"중형 화물","Medium Cargo")</f>
         <v>0</v>
       </c>
+      <c r="J6" s="245"/>
+      <c r="K6" s="245"/>
+      <c r="L6" s="245"/>
     </row>
     <row r="7" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A7" s="103" t="inlineStr">
@@ -5836,6 +5869,9 @@
       <c r="I7" s="113">
         <v>1860</v>
       </c>
+      <c r="J7" s="245"/>
+      <c r="K7" s="245"/>
+      <c r="L7" s="245"/>
     </row>
     <row r="8" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A8" s="103" t="inlineStr">
@@ -5879,6 +5915,9 @@
       <c r="I8" s="113">
         <v>2095</v>
       </c>
+      <c r="J8" s="245"/>
+      <c r="K8" s="245"/>
+      <c r="L8" s="245"/>
     </row>
     <row r="9" spans="1:12" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A9" s="105" t="inlineStr">
@@ -5916,6 +5955,9 @@
           </r>
         </is>
       </c>
+      <c r="J9" s="245"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
     </row>
     <row r="10" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A10" s="103" t="inlineStr">
@@ -5971,6 +6013,9 @@
       <c r="I10" s="115">
         <v>45775</v>
       </c>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
     </row>
     <row r="11" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A11" s="103" t="inlineStr">
@@ -6026,6 +6071,9 @@
       <c r="I11" s="115">
         <v>46504</v>
       </c>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
     </row>
     <row r="12" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A12" s="103" t="inlineStr">
@@ -6081,6 +6129,9 @@
       <c r="I12" s="113">
         <v>163268</v>
       </c>
+      <c r="J12" s="245"/>
+      <c r="K12" s="245"/>
+      <c r="L12" s="245"/>
     </row>
     <row r="13" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A13" s="105" t="inlineStr">
@@ -6113,6 +6164,9 @@
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
         <v>0</v>
       </c>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="245"/>
     </row>
     <row r="14" spans="1:12" customHeight="1" ht="120.75" s="245" customFormat="1">
       <c r="A14" s="103" t="inlineStr">
@@ -6148,6 +6202,11 @@
       <c r="E14" s="100"/>
       <c r="F14" s="100"/>
       <c r="G14" s="100"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
     </row>
     <row r="15" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A15" s="103" t="inlineStr">
@@ -6179,11 +6238,15 @@
           </r>
         </is>
       </c>
+      <c r="H15" s="245"/>
       <c r="I15" s="245" t="str">
         <f t="array" ref="I15" aca="1" ca="1">_xlfn.TEXTJOIN(",",,
  _xlfn.UNIQUE(_xlfn.IFNA(INDEX({"GASOLIN","DIESEL","LPG"},
  MATCH(G15,{"휘발유","경유","LPG"},0)),""),1))</f>
       </c>
+      <c r="J15" s="245"/>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
     </row>
     <row r="16" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A16" s="100"/>
@@ -6202,6 +6265,7 @@
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
+      <c r="H16" s="245"/>
       <c r="I16" s="245" t="inlineStr">
         <is>
           <r>
@@ -6209,6 +6273,9 @@
           </r>
         </is>
       </c>
+      <c r="J16" s="245"/>
+      <c r="K16" s="245"/>
+      <c r="L16" s="245"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="100"/>
@@ -6218,6 +6285,11 @@
       <c r="E17" s="100"/>
       <c r="F17" s="100"/>
       <c r="G17" s="100"/>
+      <c r="H17" s="245"/>
+      <c r="I17" s="245"/>
+      <c r="J17" s="245"/>
+      <c r="K17" s="245"/>
+      <c r="L17" s="245"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="100"/>
@@ -6233,6 +6305,11 @@
           </r>
         </is>
       </c>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="100"/>
@@ -6242,6 +6319,11 @@
       <c r="E19" s="100"/>
       <c r="F19" s="100"/>
       <c r="G19" s="100"/>
+      <c r="H19" s="245"/>
+      <c r="I19" s="245"/>
+      <c r="J19" s="245"/>
+      <c r="K19" s="245"/>
+      <c r="L19" s="245"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="100"/>
@@ -6251,6 +6333,11 @@
       <c r="E20" s="100"/>
       <c r="F20" s="100"/>
       <c r="G20" s="100"/>
+      <c r="H20" s="245"/>
+      <c r="I20" s="245"/>
+      <c r="J20" s="245"/>
+      <c r="K20" s="245"/>
+      <c r="L20" s="245"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="100"/>
@@ -6260,8 +6347,28 @@
       <c r="E21" s="100"/>
       <c r="F21" s="100"/>
       <c r="G21" s="100"/>
+      <c r="H21" s="245"/>
+      <c r="I21" s="245"/>
+      <c r="J21" s="245"/>
+      <c r="K21" s="245"/>
+      <c r="L21" s="245"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="245"/>
+      <c r="B22" s="245"/>
+      <c r="C22" s="245"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
+      <c r="F22" s="245"/>
+      <c r="G22" s="245"/>
+      <c r="H22" s="245"/>
+      <c r="I22" s="245"/>
+      <c r="J22" s="245"/>
+      <c r="K22" s="245"/>
+      <c r="L22" s="245"/>
     </row>
     <row r="23" spans="1:12">
+      <c r="A23" s="245"/>
       <c r="B23" s="108" t="inlineStr">
         <is>
           <r>
@@ -6269,6 +6376,7 @@
           </r>
         </is>
       </c>
+      <c r="C23" s="245"/>
       <c r="D23" s="108" t="inlineStr">
         <is>
           <r>
@@ -6276,8 +6384,17 @@
           </r>
         </is>
       </c>
+      <c r="E23" s="245"/>
+      <c r="F23" s="245"/>
+      <c r="G23" s="245"/>
+      <c r="H23" s="245"/>
+      <c r="I23" s="245"/>
+      <c r="J23" s="245"/>
+      <c r="K23" s="245"/>
+      <c r="L23" s="245"/>
     </row>
     <row r="24" spans="1:12">
+      <c r="A24" s="245"/>
       <c r="B24" s="108" t="inlineStr">
         <is>
           <r>
@@ -6285,6 +6402,7 @@
           </r>
         </is>
       </c>
+      <c r="C24" s="245"/>
       <c r="D24" s="108" t="inlineStr">
         <is>
           <r>
@@ -6292,9 +6410,17 @@
           </r>
         </is>
       </c>
+      <c r="E24" s="245"/>
       <c r="F24" s="108"/>
+      <c r="G24" s="245"/>
+      <c r="H24" s="245"/>
+      <c r="I24" s="245"/>
+      <c r="J24" s="245"/>
+      <c r="K24" s="245"/>
+      <c r="L24" s="245"/>
     </row>
     <row r="25" spans="1:12">
+      <c r="A25" s="245"/>
       <c r="B25" s="108" t="inlineStr">
         <is>
           <r>
@@ -6302,6 +6428,7 @@
           </r>
         </is>
       </c>
+      <c r="C25" s="245"/>
       <c r="D25" s="108" t="inlineStr">
         <is>
           <r>
@@ -6309,9 +6436,17 @@
           </r>
         </is>
       </c>
+      <c r="E25" s="245"/>
       <c r="F25" s="108"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
+      <c r="J25" s="245"/>
+      <c r="K25" s="245"/>
+      <c r="L25" s="245"/>
     </row>
     <row r="26" spans="1:12">
+      <c r="A26" s="245"/>
       <c r="B26" s="108" t="inlineStr">
         <is>
           <r>
@@ -6319,6 +6454,7 @@
           </r>
         </is>
       </c>
+      <c r="C26" s="245"/>
       <c r="D26" s="108" t="inlineStr">
         <is>
           <r>
@@ -6326,9 +6462,19 @@
           </r>
         </is>
       </c>
+      <c r="E26" s="245"/>
       <c r="F26" s="108"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
     </row>
     <row r="27" spans="1:12">
+      <c r="A27" s="245"/>
+      <c r="B27" s="245"/>
+      <c r="C27" s="245"/>
       <c r="D27" s="108" t="inlineStr">
         <is>
           <r>
@@ -6336,9 +6482,19 @@
           </r>
         </is>
       </c>
+      <c r="E27" s="245"/>
       <c r="F27" s="108"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
     </row>
     <row r="28" spans="1:12">
+      <c r="A28" s="245"/>
+      <c r="B28" s="245"/>
+      <c r="C28" s="245"/>
       <c r="D28" s="108" t="inlineStr">
         <is>
           <r>
@@ -6346,9 +6502,19 @@
           </r>
         </is>
       </c>
+      <c r="E28" s="245"/>
       <c r="F28" s="108"/>
+      <c r="G28" s="245"/>
+      <c r="H28" s="245"/>
+      <c r="I28" s="245"/>
+      <c r="J28" s="245"/>
+      <c r="K28" s="245"/>
+      <c r="L28" s="245"/>
     </row>
     <row r="29" spans="1:12">
+      <c r="A29" s="245"/>
+      <c r="B29" s="245"/>
+      <c r="C29" s="245"/>
       <c r="D29" s="109" t="inlineStr">
         <is>
           <r>
@@ -6356,9 +6522,19 @@
           </r>
         </is>
       </c>
+      <c r="E29" s="245"/>
       <c r="F29" s="108"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
+      <c r="K29" s="245"/>
+      <c r="L29" s="245"/>
     </row>
     <row r="30" spans="1:12">
+      <c r="A30" s="245"/>
+      <c r="B30" s="245"/>
+      <c r="C30" s="245"/>
       <c r="D30" s="108" t="inlineStr">
         <is>
           <r>
@@ -6366,8 +6542,19 @@
           </r>
         </is>
       </c>
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+      <c r="G30" s="245"/>
+      <c r="H30" s="245"/>
+      <c r="I30" s="245"/>
+      <c r="J30" s="245"/>
+      <c r="K30" s="245"/>
+      <c r="L30" s="245"/>
     </row>
     <row r="31" spans="1:12">
+      <c r="A31" s="245"/>
+      <c r="B31" s="245"/>
+      <c r="C31" s="245"/>
       <c r="D31" s="108" t="inlineStr">
         <is>
           <r>
@@ -6375,8 +6562,19 @@
           </r>
         </is>
       </c>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
+      <c r="K31" s="245"/>
+      <c r="L31" s="245"/>
     </row>
     <row r="32" spans="1:12">
+      <c r="A32" s="245"/>
+      <c r="B32" s="245"/>
+      <c r="C32" s="245"/>
       <c r="D32" s="108" t="inlineStr">
         <is>
           <r>
@@ -6384,8 +6582,19 @@
           </r>
         </is>
       </c>
+      <c r="E32" s="245"/>
+      <c r="F32" s="245"/>
+      <c r="G32" s="245"/>
+      <c r="H32" s="245"/>
+      <c r="I32" s="245"/>
+      <c r="J32" s="245"/>
+      <c r="K32" s="245"/>
+      <c r="L32" s="245"/>
     </row>
     <row r="33" spans="1:12">
+      <c r="A33" s="245"/>
+      <c r="B33" s="245"/>
+      <c r="C33" s="245"/>
       <c r="D33" s="108" t="inlineStr">
         <is>
           <r>
@@ -6393,8 +6602,19 @@
           </r>
         </is>
       </c>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+      <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
+      <c r="K33" s="245"/>
+      <c r="L33" s="245"/>
     </row>
     <row r="34" spans="1:12">
+      <c r="A34" s="245"/>
+      <c r="B34" s="245"/>
+      <c r="C34" s="245"/>
       <c r="D34" s="108" t="inlineStr">
         <is>
           <r>
@@ -6402,8 +6622,19 @@
           </r>
         </is>
       </c>
+      <c r="E34" s="245"/>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
+      <c r="I34" s="245"/>
+      <c r="J34" s="245"/>
+      <c r="K34" s="245"/>
+      <c r="L34" s="245"/>
     </row>
     <row r="35" spans="1:12">
+      <c r="A35" s="245"/>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
       <c r="D35" s="108" t="inlineStr">
         <is>
           <r>
@@ -6411,8 +6642,19 @@
           </r>
         </is>
       </c>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
+      <c r="J35" s="245"/>
+      <c r="K35" s="245"/>
+      <c r="L35" s="245"/>
     </row>
     <row r="36" spans="1:12">
+      <c r="A36" s="245"/>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
       <c r="D36" s="108" t="inlineStr">
         <is>
           <r>
@@ -6420,8 +6662,19 @@
           </r>
         </is>
       </c>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
+      <c r="J36" s="245"/>
+      <c r="K36" s="245"/>
+      <c r="L36" s="245"/>
     </row>
     <row r="37" spans="1:12">
+      <c r="A37" s="245"/>
+      <c r="B37" s="245"/>
+      <c r="C37" s="245"/>
       <c r="D37" s="108" t="inlineStr">
         <is>
           <r>
@@ -6429,8 +6682,19 @@
           </r>
         </is>
       </c>
+      <c r="E37" s="245"/>
+      <c r="F37" s="245"/>
+      <c r="G37" s="245"/>
+      <c r="H37" s="245"/>
+      <c r="I37" s="245"/>
+      <c r="J37" s="245"/>
+      <c r="K37" s="245"/>
+      <c r="L37" s="245"/>
     </row>
     <row r="38" spans="1:12">
+      <c r="A38" s="245"/>
+      <c r="B38" s="245"/>
+      <c r="C38" s="245"/>
       <c r="D38" s="108" t="inlineStr">
         <is>
           <r>
@@ -6438,8 +6702,19 @@
           </r>
         </is>
       </c>
+      <c r="E38" s="245"/>
+      <c r="F38" s="245"/>
+      <c r="G38" s="245"/>
+      <c r="H38" s="245"/>
+      <c r="I38" s="245"/>
+      <c r="J38" s="245"/>
+      <c r="K38" s="245"/>
+      <c r="L38" s="245"/>
     </row>
     <row r="39" spans="1:12">
+      <c r="A39" s="245"/>
+      <c r="B39" s="245"/>
+      <c r="C39" s="245"/>
       <c r="D39" s="108" t="inlineStr">
         <is>
           <r>
@@ -6447,86 +6722,380 @@
           </r>
         </is>
       </c>
+      <c r="E39" s="245"/>
+      <c r="F39" s="245"/>
+      <c r="G39" s="245"/>
+      <c r="H39" s="245"/>
+      <c r="I39" s="245"/>
+      <c r="J39" s="245"/>
+      <c r="K39" s="245"/>
+      <c r="L39" s="245"/>
     </row>
     <row r="40" spans="1:12">
+      <c r="A40" s="245"/>
+      <c r="B40" s="245"/>
+      <c r="C40" s="245"/>
       <c r="D40" s="108">
         <v>123456</v>
       </c>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
     </row>
     <row r="41" spans="1:12">
+      <c r="A41" s="245"/>
+      <c r="B41" s="245"/>
+      <c r="C41" s="245"/>
       <c r="D41" s="108"/>
+      <c r="E41" s="245"/>
+      <c r="F41" s="245"/>
+      <c r="G41" s="245"/>
+      <c r="H41" s="245"/>
+      <c r="I41" s="245"/>
+      <c r="J41" s="245"/>
+      <c r="K41" s="245"/>
+      <c r="L41" s="245"/>
     </row>
     <row r="42" spans="1:12">
+      <c r="A42" s="245"/>
+      <c r="B42" s="245"/>
+      <c r="C42" s="245"/>
       <c r="D42" s="108"/>
+      <c r="E42" s="245"/>
+      <c r="F42" s="245"/>
+      <c r="G42" s="245"/>
+      <c r="H42" s="245"/>
+      <c r="I42" s="245"/>
+      <c r="J42" s="245"/>
+      <c r="K42" s="245"/>
+      <c r="L42" s="245"/>
     </row>
     <row r="43" spans="1:12">
+      <c r="A43" s="245"/>
+      <c r="B43" s="245"/>
+      <c r="C43" s="245"/>
       <c r="D43" s="108"/>
+      <c r="E43" s="245"/>
+      <c r="F43" s="245"/>
+      <c r="G43" s="245"/>
+      <c r="H43" s="245"/>
+      <c r="I43" s="245"/>
+      <c r="J43" s="245"/>
+      <c r="K43" s="245"/>
+      <c r="L43" s="245"/>
     </row>
     <row r="44" spans="1:12">
+      <c r="A44" s="245"/>
+      <c r="B44" s="245"/>
+      <c r="C44" s="245"/>
       <c r="D44" s="108"/>
+      <c r="E44" s="245"/>
+      <c r="F44" s="245"/>
+      <c r="G44" s="245"/>
+      <c r="H44" s="245"/>
+      <c r="I44" s="245"/>
+      <c r="J44" s="245"/>
+      <c r="K44" s="245"/>
+      <c r="L44" s="245"/>
     </row>
     <row r="45" spans="1:12">
+      <c r="A45" s="245"/>
+      <c r="B45" s="245"/>
+      <c r="C45" s="245"/>
       <c r="D45" s="108"/>
+      <c r="E45" s="245"/>
+      <c r="F45" s="245"/>
+      <c r="G45" s="245"/>
+      <c r="H45" s="245"/>
+      <c r="I45" s="245"/>
+      <c r="J45" s="245"/>
+      <c r="K45" s="245"/>
+      <c r="L45" s="245"/>
     </row>
     <row r="46" spans="1:12">
+      <c r="A46" s="245"/>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
       <c r="D46" s="108"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
+      <c r="I46" s="245"/>
+      <c r="J46" s="245"/>
+      <c r="K46" s="245"/>
+      <c r="L46" s="245"/>
     </row>
     <row r="47" spans="1:12">
+      <c r="A47" s="245"/>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
       <c r="D47" s="108"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
+      <c r="G47" s="245"/>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
+      <c r="K47" s="245"/>
+      <c r="L47" s="245"/>
     </row>
     <row r="48" spans="1:12">
+      <c r="A48" s="245"/>
+      <c r="B48" s="245"/>
+      <c r="C48" s="245"/>
       <c r="D48" s="108"/>
+      <c r="E48" s="245"/>
+      <c r="F48" s="245"/>
+      <c r="G48" s="245"/>
+      <c r="H48" s="245"/>
+      <c r="I48" s="245"/>
+      <c r="J48" s="245"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="245"/>
     </row>
     <row r="49" spans="1:12">
+      <c r="A49" s="245"/>
+      <c r="B49" s="245"/>
+      <c r="C49" s="245"/>
       <c r="D49" s="108"/>
+      <c r="E49" s="245"/>
+      <c r="F49" s="245"/>
+      <c r="G49" s="245"/>
+      <c r="H49" s="245"/>
+      <c r="I49" s="245"/>
+      <c r="J49" s="245"/>
+      <c r="K49" s="245"/>
+      <c r="L49" s="245"/>
     </row>
     <row r="50" spans="1:12">
+      <c r="A50" s="245"/>
+      <c r="B50" s="245"/>
+      <c r="C50" s="245"/>
       <c r="D50" s="108"/>
+      <c r="E50" s="245"/>
+      <c r="F50" s="245"/>
+      <c r="G50" s="245"/>
+      <c r="H50" s="245"/>
+      <c r="I50" s="245"/>
+      <c r="J50" s="245"/>
+      <c r="K50" s="245"/>
+      <c r="L50" s="245"/>
     </row>
     <row r="51" spans="1:12">
+      <c r="A51" s="245"/>
+      <c r="B51" s="245"/>
+      <c r="C51" s="245"/>
       <c r="D51" s="108"/>
+      <c r="E51" s="245"/>
+      <c r="F51" s="245"/>
+      <c r="G51" s="245"/>
+      <c r="H51" s="245"/>
+      <c r="I51" s="245"/>
+      <c r="J51" s="245"/>
+      <c r="K51" s="245"/>
+      <c r="L51" s="245"/>
     </row>
     <row r="52" spans="1:12">
+      <c r="A52" s="245"/>
+      <c r="B52" s="245"/>
+      <c r="C52" s="245"/>
       <c r="D52" s="108"/>
+      <c r="E52" s="245"/>
+      <c r="F52" s="245"/>
+      <c r="G52" s="245"/>
+      <c r="H52" s="245"/>
+      <c r="I52" s="245"/>
+      <c r="J52" s="245"/>
+      <c r="K52" s="245"/>
+      <c r="L52" s="245"/>
     </row>
     <row r="53" spans="1:12">
+      <c r="A53" s="245"/>
+      <c r="B53" s="245"/>
+      <c r="C53" s="245"/>
       <c r="D53" s="108"/>
+      <c r="E53" s="245"/>
+      <c r="F53" s="245"/>
+      <c r="G53" s="245"/>
+      <c r="H53" s="245"/>
+      <c r="I53" s="245"/>
+      <c r="J53" s="245"/>
+      <c r="K53" s="245"/>
+      <c r="L53" s="245"/>
     </row>
     <row r="54" spans="1:12">
+      <c r="A54" s="245"/>
+      <c r="B54" s="245"/>
+      <c r="C54" s="245"/>
       <c r="D54" s="108"/>
+      <c r="E54" s="245"/>
+      <c r="F54" s="245"/>
+      <c r="G54" s="245"/>
+      <c r="H54" s="245"/>
+      <c r="I54" s="245"/>
+      <c r="J54" s="245"/>
+      <c r="K54" s="245"/>
+      <c r="L54" s="245"/>
     </row>
     <row r="55" spans="1:12">
+      <c r="A55" s="245"/>
+      <c r="B55" s="245"/>
+      <c r="C55" s="245"/>
       <c r="D55" s="108"/>
+      <c r="E55" s="245"/>
+      <c r="F55" s="245"/>
+      <c r="G55" s="245"/>
+      <c r="H55" s="245"/>
+      <c r="I55" s="245"/>
+      <c r="J55" s="245"/>
+      <c r="K55" s="245"/>
+      <c r="L55" s="245"/>
     </row>
     <row r="56" spans="1:12">
+      <c r="A56" s="245"/>
+      <c r="B56" s="245"/>
+      <c r="C56" s="245"/>
       <c r="D56" s="108"/>
+      <c r="E56" s="245"/>
+      <c r="F56" s="245"/>
+      <c r="G56" s="245"/>
+      <c r="H56" s="245"/>
+      <c r="I56" s="245"/>
+      <c r="J56" s="245"/>
+      <c r="K56" s="245"/>
+      <c r="L56" s="245"/>
     </row>
     <row r="57" spans="1:12">
+      <c r="A57" s="245"/>
+      <c r="B57" s="245"/>
+      <c r="C57" s="245"/>
       <c r="D57" s="108"/>
+      <c r="E57" s="245"/>
+      <c r="F57" s="245"/>
+      <c r="G57" s="245"/>
+      <c r="H57" s="245"/>
+      <c r="I57" s="245"/>
+      <c r="J57" s="245"/>
+      <c r="K57" s="245"/>
+      <c r="L57" s="245"/>
     </row>
     <row r="58" spans="1:12">
+      <c r="A58" s="245"/>
+      <c r="B58" s="245"/>
+      <c r="C58" s="245"/>
       <c r="D58" s="108"/>
+      <c r="E58" s="245"/>
+      <c r="F58" s="245"/>
+      <c r="G58" s="245"/>
+      <c r="H58" s="245"/>
+      <c r="I58" s="245"/>
+      <c r="J58" s="245"/>
+      <c r="K58" s="245"/>
+      <c r="L58" s="245"/>
     </row>
     <row r="59" spans="1:12">
+      <c r="A59" s="245"/>
+      <c r="B59" s="245"/>
+      <c r="C59" s="245"/>
       <c r="D59" s="108"/>
+      <c r="E59" s="245"/>
+      <c r="F59" s="245"/>
+      <c r="G59" s="245"/>
+      <c r="H59" s="245"/>
+      <c r="I59" s="245"/>
+      <c r="J59" s="245"/>
+      <c r="K59" s="245"/>
+      <c r="L59" s="245"/>
     </row>
     <row r="60" spans="1:12">
+      <c r="A60" s="245"/>
+      <c r="B60" s="245"/>
+      <c r="C60" s="245"/>
       <c r="D60" s="108"/>
+      <c r="E60" s="245"/>
+      <c r="F60" s="245"/>
+      <c r="G60" s="245"/>
+      <c r="H60" s="245"/>
+      <c r="I60" s="245"/>
+      <c r="J60" s="245"/>
+      <c r="K60" s="245"/>
+      <c r="L60" s="245"/>
     </row>
     <row r="61" spans="1:12">
+      <c r="A61" s="245"/>
+      <c r="B61" s="245"/>
+      <c r="C61" s="245"/>
       <c r="D61" s="108"/>
+      <c r="E61" s="245"/>
+      <c r="F61" s="245"/>
+      <c r="G61" s="245"/>
+      <c r="H61" s="245"/>
+      <c r="I61" s="245"/>
+      <c r="J61" s="245"/>
+      <c r="K61" s="245"/>
+      <c r="L61" s="245"/>
     </row>
     <row r="62" spans="1:12">
+      <c r="A62" s="245"/>
+      <c r="B62" s="245"/>
+      <c r="C62" s="245"/>
       <c r="D62" s="108"/>
+      <c r="E62" s="245"/>
+      <c r="F62" s="245"/>
+      <c r="G62" s="245"/>
+      <c r="H62" s="245"/>
+      <c r="I62" s="245"/>
+      <c r="J62" s="245"/>
+      <c r="K62" s="245"/>
+      <c r="L62" s="245"/>
     </row>
     <row r="63" spans="1:12">
+      <c r="A63" s="245"/>
+      <c r="B63" s="245"/>
+      <c r="C63" s="245"/>
       <c r="D63" s="108"/>
+      <c r="E63" s="245"/>
+      <c r="F63" s="245"/>
+      <c r="G63" s="245"/>
+      <c r="H63" s="245"/>
+      <c r="I63" s="245"/>
+      <c r="J63" s="245"/>
+      <c r="K63" s="245"/>
+      <c r="L63" s="245"/>
     </row>
     <row r="64" spans="1:12">
+      <c r="A64" s="245"/>
+      <c r="B64" s="245"/>
+      <c r="C64" s="245"/>
       <c r="D64" s="108"/>
+      <c r="E64" s="245"/>
+      <c r="F64" s="245"/>
+      <c r="G64" s="245"/>
+      <c r="H64" s="245"/>
+      <c r="I64" s="245"/>
+      <c r="J64" s="245"/>
+      <c r="K64" s="245"/>
+      <c r="L64" s="245"/>
     </row>
     <row r="65" spans="1:12">
+      <c r="A65" s="245"/>
+      <c r="B65" s="245"/>
+      <c r="C65" s="245"/>
       <c r="D65" s="108"/>
+      <c r="E65" s="245"/>
+      <c r="F65" s="245"/>
+      <c r="G65" s="245"/>
+      <c r="H65" s="245"/>
+      <c r="I65" s="245"/>
+      <c r="J65" s="245"/>
+      <c r="K65" s="245"/>
+      <c r="L65" s="245"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -6618,6 +7187,9 @@
           </r>
         </is>
       </c>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
     </row>
     <row r="2" spans="1:20" customHeight="1" ht="60" s="245" customFormat="1">
       <c r="A2" s="249" t="inlineStr">
@@ -6643,6 +7215,9 @@
       <c r="O2" s="250"/>
       <c r="P2" s="250"/>
       <c r="Q2" s="251"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
     </row>
     <row r="3" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A3" s="1"/>
@@ -6685,12 +7260,16 @@
           </r>
         </is>
       </c>
+      <c r="N3" s="245"/>
       <c r="O3" s="150" t="str">
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
       <c r="P3" s="252"/>
       <c r="Q3" s="253"/>
+      <c r="R3" s="245"/>
+      <c r="S3" s="245"/>
+      <c r="T3" s="245"/>
     </row>
     <row r="4" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A4" s="135" t="inlineStr">
@@ -6740,6 +7319,9 @@
         </is>
       </c>
       <c r="Q4" s="255"/>
+      <c r="R4" s="245"/>
+      <c r="S4" s="245"/>
+      <c r="T4" s="245"/>
     </row>
     <row r="5" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A5" s="136" t="inlineStr">
@@ -6780,6 +7362,9 @@
         <v>0</v>
       </c>
       <c r="Q5" s="255"/>
+      <c r="R5" s="245"/>
+      <c r="S5" s="245"/>
+      <c r="T5" s="245"/>
     </row>
     <row r="6" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A6" s="136" t="inlineStr">
@@ -6817,6 +7402,9 @@
       <c r="O6" s="254"/>
       <c r="P6" s="254"/>
       <c r="Q6" s="255"/>
+      <c r="R6" s="245"/>
+      <c r="S6" s="245"/>
+      <c r="T6" s="245"/>
     </row>
     <row r="7" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A7" s="136" t="inlineStr">
@@ -6848,6 +7436,9 @@
       <c r="O7" s="254"/>
       <c r="P7" s="254"/>
       <c r="Q7" s="255"/>
+      <c r="R7" s="245"/>
+      <c r="S7" s="245"/>
+      <c r="T7" s="245"/>
     </row>
     <row r="8" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A8" s="258" t="inlineStr">
@@ -6898,6 +7489,8 @@
       <c r="O8" s="254"/>
       <c r="P8" s="254"/>
       <c r="Q8" s="255"/>
+      <c r="R8" s="245"/>
+      <c r="S8" s="245"/>
       <c r="T8" s="245" t="inlineStr">
         <is>
           <r>
@@ -6924,6 +7517,9 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
     </row>
     <row r="10" spans="1:20" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A10" s="261" t="inlineStr">
@@ -6933,7 +7529,25 @@
           </r>
         </is>
       </c>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
+      <c r="M10" s="245"/>
+      <c r="N10" s="245"/>
+      <c r="O10" s="245"/>
+      <c r="P10" s="245"/>
       <c r="Q10" s="262"/>
+      <c r="R10" s="245"/>
+      <c r="S10" s="245"/>
+      <c r="T10" s="245"/>
     </row>
     <row r="11" spans="1:20" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A11" s="1"/>
@@ -6944,7 +7558,24 @@
           </r>
         </is>
       </c>
+      <c r="C11" s="245"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
+      <c r="M11" s="245"/>
+      <c r="N11" s="245"/>
+      <c r="O11" s="245"/>
+      <c r="P11" s="245"/>
       <c r="Q11" s="262"/>
+      <c r="R11" s="245"/>
+      <c r="S11" s="245"/>
+      <c r="T11" s="245"/>
     </row>
     <row r="12" spans="1:20" customHeight="1" ht="20.25" s="245" customFormat="1">
       <c r="A12" s="1"/>
@@ -6964,6 +7595,9 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
+      <c r="R12" s="245"/>
+      <c r="S12" s="245"/>
+      <c r="T12" s="245"/>
     </row>
     <row r="13" spans="1:20" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
@@ -6980,28 +7614,73 @@
           </r>
         </is>
       </c>
+      <c r="C13" s="245"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
       <c r="L13" s="155" t="str">
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
+      <c r="M13" s="245"/>
+      <c r="N13" s="245"/>
       <c r="O13" s="245"/>
       <c r="P13" s="263"/>
       <c r="Q13" s="5"/>
+      <c r="R13" s="245"/>
+      <c r="S13" s="245"/>
+      <c r="T13" s="245"/>
     </row>
     <row r="14" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A14" s="4"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
+      <c r="R14" s="245"/>
+      <c r="S14" s="245"/>
+      <c r="T14" s="245"/>
     </row>
     <row r="15" spans="1:20" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="245"/>
+      <c r="H15" s="245"/>
+      <c r="I15" s="245"/>
       <c r="J15" s="392" t="s">
         <v>105</v>
       </c>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
+      <c r="M15" s="245"/>
+      <c r="N15" s="245"/>
+      <c r="O15" s="245"/>
+      <c r="P15" s="245"/>
       <c r="Q15" s="262"/>
+      <c r="R15" s="245"/>
+      <c r="S15" s="245"/>
+      <c r="T15" s="245"/>
     </row>
     <row r="16" spans="1:20" customHeight="1" ht="9" s="245" customFormat="1">
       <c r="A16" s="7"/>
@@ -7021,6 +7700,9 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
+      <c r="R16" s="245"/>
+      <c r="S16" s="245"/>
+      <c r="T16" s="245"/>
     </row>
     <row r="17" spans="1:20" customHeight="1" ht="8.25" s="245" customFormat="1">
       <c r="A17" s="4"/>
@@ -7031,13 +7713,24 @@
           </r>
         </is>
       </c>
+      <c r="C17" s="245"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
       <c r="I17" s="264"/>
       <c r="J17" s="264"/>
       <c r="K17" s="264"/>
       <c r="L17" s="264"/>
       <c r="M17" s="264"/>
       <c r="N17" s="264"/>
+      <c r="O17" s="245"/>
+      <c r="P17" s="245"/>
       <c r="Q17" s="5"/>
+      <c r="R17" s="245"/>
+      <c r="S17" s="245"/>
+      <c r="T17" s="245"/>
     </row>
     <row r="18" spans="1:20" customHeight="1" ht="21.75" s="245" customFormat="1">
       <c r="A18" s="265" t="inlineStr">
@@ -7056,6 +7749,7 @@
       <c r="H18" s="254"/>
       <c r="I18" s="254"/>
       <c r="J18" s="255"/>
+      <c r="K18" s="245"/>
       <c r="L18" s="266" t="inlineStr">
         <is>
           <r>
@@ -7068,6 +7762,9 @@
       <c r="O18" s="254"/>
       <c r="P18" s="254"/>
       <c r="Q18" s="255"/>
+      <c r="R18" s="245"/>
+      <c r="S18" s="245"/>
+      <c r="T18" s="245"/>
     </row>
     <row r="19" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
@@ -7095,6 +7792,7 @@
       <c r="H19" s="250"/>
       <c r="I19" s="250"/>
       <c r="J19" s="251"/>
+      <c r="K19" s="245"/>
       <c r="L19" s="165" t="inlineStr">
         <is>
           <r>
@@ -7137,6 +7835,9 @@
           </r>
         </is>
       </c>
+      <c r="R19" s="245"/>
+      <c r="S19" s="245"/>
+      <c r="T19" s="245"/>
     </row>
     <row r="20" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
@@ -7161,6 +7862,7 @@
       <c r="H20" s="252"/>
       <c r="I20" s="252"/>
       <c r="J20" s="253"/>
+      <c r="K20" s="245"/>
       <c r="L20" s="166" t="inlineStr">
         <is>
           <r>
@@ -7203,6 +7905,9 @@
           </r>
         </is>
       </c>
+      <c r="R20" s="245"/>
+      <c r="S20" s="245"/>
+      <c r="T20" s="245"/>
     </row>
     <row r="21" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
@@ -7257,6 +7962,7 @@
           </r>
         </is>
       </c>
+      <c r="K21" s="245"/>
       <c r="L21" s="121" t="str">
         <f>구매리스트!I10</f>
         <v>0</v>
@@ -7272,6 +7978,9 @@
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
+      <c r="R21" s="245"/>
+      <c r="S21" s="245"/>
+      <c r="T21" s="245"/>
     </row>
     <row r="22" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
@@ -7326,12 +8035,16 @@
           </r>
         </is>
       </c>
+      <c r="K22" s="245"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
+      <c r="R22" s="245"/>
+      <c r="S22" s="245"/>
+      <c r="T22" s="245"/>
     </row>
     <row r="23" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
@@ -7386,12 +8099,16 @@
           </r>
         </is>
       </c>
+      <c r="K23" s="245"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
+      <c r="R23" s="245"/>
+      <c r="S23" s="245"/>
+      <c r="T23" s="245"/>
     </row>
     <row r="24" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A24" s="268" t="inlineStr">
@@ -7425,12 +8142,16 @@
         </is>
       </c>
       <c r="J24" s="251"/>
+      <c r="K24" s="245"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
+      <c r="R24" s="245"/>
+      <c r="S24" s="245"/>
+      <c r="T24" s="245"/>
     </row>
     <row r="25" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A25" s="271"/>
@@ -7443,13 +8164,22 @@
       </c>
       <c r="C25" s="262"/>
       <c r="D25" s="271"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
       <c r="J25" s="262"/>
+      <c r="K25" s="245"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
+      <c r="R25" s="245"/>
+      <c r="S25" s="245"/>
+      <c r="T25" s="245"/>
     </row>
     <row r="26" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A26" s="272"/>
@@ -7462,12 +8192,16 @@
       <c r="H26" s="252"/>
       <c r="I26" s="252"/>
       <c r="J26" s="253"/>
+      <c r="K26" s="245"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
+      <c r="R26" s="245"/>
+      <c r="S26" s="245"/>
+      <c r="T26" s="245"/>
     </row>
     <row r="27" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
@@ -7501,12 +8235,16 @@
       </c>
       <c r="I27" s="254"/>
       <c r="J27" s="255"/>
+      <c r="K27" s="245"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
+      <c r="R27" s="245"/>
+      <c r="S27" s="245"/>
+      <c r="T27" s="245"/>
     </row>
     <row r="28" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
@@ -7540,12 +8278,16 @@
         </is>
       </c>
       <c r="J28" s="251"/>
+      <c r="K28" s="245"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
+      <c r="R28" s="245"/>
+      <c r="S28" s="245"/>
+      <c r="T28" s="245"/>
     </row>
     <row r="29" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A29" s="274" t="inlineStr">
@@ -7555,15 +8297,25 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="245"/>
       <c r="C29" s="262"/>
       <c r="D29" s="271"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
       <c r="J29" s="262"/>
+      <c r="K29" s="245"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
+      <c r="R29" s="245"/>
+      <c r="S29" s="245"/>
+      <c r="T29" s="245"/>
     </row>
     <row r="30" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A30" s="275" t="inlineStr">
@@ -7582,12 +8334,16 @@
       <c r="H30" s="252"/>
       <c r="I30" s="252"/>
       <c r="J30" s="253"/>
+      <c r="K30" s="245"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
+      <c r="R30" s="245"/>
+      <c r="S30" s="245"/>
+      <c r="T30" s="245"/>
     </row>
     <row r="31" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
@@ -7624,12 +8380,16 @@
       </c>
       <c r="I31" s="254"/>
       <c r="J31" s="255"/>
+      <c r="K31" s="245"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
+      <c r="R31" s="245"/>
+      <c r="S31" s="245"/>
+      <c r="T31" s="245"/>
     </row>
     <row r="32" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
@@ -7678,12 +8438,16 @@
         </is>
       </c>
       <c r="J32" s="255"/>
+      <c r="K32" s="245"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
+      <c r="R32" s="245"/>
+      <c r="S32" s="245"/>
+      <c r="T32" s="245"/>
     </row>
     <row r="33" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
@@ -7726,12 +8490,16 @@
         </is>
       </c>
       <c r="J33" s="255"/>
+      <c r="K33" s="245"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
+      <c r="R33" s="245"/>
+      <c r="S33" s="245"/>
+      <c r="T33" s="245"/>
     </row>
     <row r="34" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A34" s="277" t="inlineStr">
@@ -7750,32 +8518,60 @@
       <c r="H34" s="250"/>
       <c r="I34" s="250"/>
       <c r="J34" s="251"/>
+      <c r="K34" s="245"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
       <c r="O34" s="14"/>
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
+      <c r="R34" s="245"/>
+      <c r="S34" s="245"/>
+      <c r="T34" s="245"/>
     </row>
     <row r="35" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A35" s="271"/>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="245"/>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
       <c r="J35" s="262"/>
+      <c r="K35" s="245"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
+      <c r="R35" s="245"/>
+      <c r="S35" s="245"/>
+      <c r="T35" s="245"/>
     </row>
     <row r="36" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A36" s="271"/>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
       <c r="J36" s="262"/>
+      <c r="K36" s="245"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
+      <c r="R36" s="245"/>
+      <c r="S36" s="245"/>
+      <c r="T36" s="245"/>
     </row>
     <row r="37" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A37" s="272"/>
@@ -7788,12 +8584,16 @@
       <c r="H37" s="252"/>
       <c r="I37" s="252"/>
       <c r="J37" s="253"/>
+      <c r="K37" s="245"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
+      <c r="R37" s="245"/>
+      <c r="S37" s="245"/>
+      <c r="T37" s="245"/>
     </row>
     <row r="38" spans="1:20" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A38" s="172" t="inlineStr">
@@ -7812,6 +8612,7 @@
       <c r="H38" s="254"/>
       <c r="I38" s="254"/>
       <c r="J38" s="255"/>
+      <c r="K38" s="245"/>
       <c r="L38" s="278" t="inlineStr">
         <is>
           <r>
@@ -7824,6 +8625,9 @@
       <c r="O38" s="250"/>
       <c r="P38" s="250"/>
       <c r="Q38" s="251"/>
+      <c r="R38" s="245"/>
+      <c r="S38" s="245"/>
+      <c r="T38" s="245"/>
     </row>
     <row r="39" spans="1:20" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A39" s="279" t="inlineStr">
@@ -7854,6 +8658,7 @@
       </c>
       <c r="I39" s="254"/>
       <c r="J39" s="255"/>
+      <c r="K39" s="245"/>
       <c r="L39" s="280" t="inlineStr">
         <is>
           <r>
@@ -7866,6 +8671,9 @@
       <c r="O39" s="250"/>
       <c r="P39" s="250"/>
       <c r="Q39" s="251"/>
+      <c r="R39" s="245"/>
+      <c r="S39" s="245"/>
+      <c r="T39" s="245"/>
     </row>
     <row r="40" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
@@ -7902,8 +8710,16 @@
       </c>
       <c r="I40" s="254"/>
       <c r="J40" s="255"/>
+      <c r="K40" s="245"/>
       <c r="L40" s="4"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="245"/>
+      <c r="P40" s="245"/>
       <c r="Q40" s="5"/>
+      <c r="R40" s="245"/>
+      <c r="S40" s="245"/>
+      <c r="T40" s="245"/>
     </row>
     <row r="41" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
@@ -7940,7 +8756,10 @@
       </c>
       <c r="I41" s="254"/>
       <c r="J41" s="255"/>
+      <c r="K41" s="245"/>
       <c r="L41" s="4"/>
+      <c r="M41" s="245"/>
+      <c r="N41" s="245"/>
       <c r="O41" s="245" t="inlineStr">
         <is>
           <r>
@@ -7948,7 +8767,11 @@
           </r>
         </is>
       </c>
+      <c r="P41" s="245"/>
       <c r="Q41" s="5"/>
+      <c r="R41" s="245"/>
+      <c r="S41" s="245"/>
+      <c r="T41" s="245"/>
     </row>
     <row r="42" spans="1:20" customHeight="1" ht="33" s="245" customFormat="1">
       <c r="A42" s="266" t="inlineStr">
@@ -7968,8 +8791,16 @@
       <c r="H42" s="254"/>
       <c r="I42" s="254"/>
       <c r="J42" s="255"/>
+      <c r="K42" s="245"/>
       <c r="L42" s="4"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
+      <c r="P42" s="245"/>
       <c r="Q42" s="5"/>
+      <c r="R42" s="245"/>
+      <c r="S42" s="245"/>
+      <c r="T42" s="245"/>
     </row>
     <row r="43" spans="1:20" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A43" s="281" t="inlineStr">
@@ -7994,8 +8825,16 @@
       </c>
       <c r="I43" s="254"/>
       <c r="J43" s="255"/>
+      <c r="K43" s="245"/>
       <c r="L43" s="4"/>
+      <c r="M43" s="245"/>
+      <c r="N43" s="245"/>
+      <c r="O43" s="245"/>
+      <c r="P43" s="245"/>
       <c r="Q43" s="5"/>
+      <c r="R43" s="245"/>
+      <c r="S43" s="245"/>
+      <c r="T43" s="245"/>
     </row>
     <row r="44" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
@@ -8020,8 +8859,16 @@
       </c>
       <c r="I44" s="254"/>
       <c r="J44" s="255"/>
+      <c r="K44" s="245"/>
       <c r="L44" s="4"/>
+      <c r="M44" s="245"/>
+      <c r="N44" s="245"/>
+      <c r="O44" s="245"/>
+      <c r="P44" s="245"/>
       <c r="Q44" s="5"/>
+      <c r="R44" s="245"/>
+      <c r="S44" s="245"/>
+      <c r="T44" s="245"/>
     </row>
     <row r="45" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
@@ -8053,9 +8900,39 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
-    </row>
-    <row r="46" spans="1:20" customHeight="1" ht="6" s="245" customFormat="1"/>
+      <c r="R45" s="245"/>
+      <c r="S45" s="245"/>
+      <c r="T45" s="245"/>
+    </row>
+    <row r="46" spans="1:20" customHeight="1" ht="6" s="245" customFormat="1">
+      <c r="A46" s="245"/>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
+      <c r="D46" s="245"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
+      <c r="I46" s="245"/>
+      <c r="J46" s="245"/>
+      <c r="K46" s="245"/>
+      <c r="L46" s="245"/>
+      <c r="M46" s="245"/>
+      <c r="N46" s="245"/>
+      <c r="O46" s="245"/>
+      <c r="P46" s="245"/>
+      <c r="Q46" s="245"/>
+      <c r="R46" s="245"/>
+      <c r="S46" s="245"/>
+      <c r="T46" s="245"/>
+    </row>
     <row r="47" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A47" s="245"/>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
+      <c r="D47" s="245"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
       <c r="G47" s="162" t="inlineStr">
         <is>
           <r>
@@ -8063,6 +8940,12 @@
           </r>
         </is>
       </c>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
+      <c r="K47" s="245"/>
+      <c r="L47" s="245"/>
+      <c r="M47" s="245"/>
       <c r="N47" s="163" t="inlineStr">
         <is>
           <r>
@@ -8070,6 +8953,12 @@
           </r>
         </is>
       </c>
+      <c r="O47" s="245"/>
+      <c r="P47" s="245"/>
+      <c r="Q47" s="245"/>
+      <c r="R47" s="245"/>
+      <c r="S47" s="245"/>
+      <c r="T47" s="245"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -8235,6 +9124,12 @@
           </r>
         </is>
       </c>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
     </row>
     <row r="2" spans="1:23" customHeight="1" ht="60" s="245" customFormat="1">
       <c r="A2" s="282" t="inlineStr">
@@ -8260,6 +9155,12 @@
       <c r="O2" s="250"/>
       <c r="P2" s="250"/>
       <c r="Q2" s="251"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
     </row>
     <row r="3" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A3" s="1"/>
@@ -8309,6 +9210,12 @@
       </c>
       <c r="P3" s="252"/>
       <c r="Q3" s="253"/>
+      <c r="R3" s="245"/>
+      <c r="S3" s="245"/>
+      <c r="T3" s="245"/>
+      <c r="U3" s="245"/>
+      <c r="V3" s="245"/>
+      <c r="W3" s="245"/>
     </row>
     <row r="4" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A4" s="172" t="inlineStr">
@@ -8358,6 +9265,12 @@
         </is>
       </c>
       <c r="Q4" s="255"/>
+      <c r="R4" s="245"/>
+      <c r="S4" s="245"/>
+      <c r="T4" s="245"/>
+      <c r="U4" s="245"/>
+      <c r="V4" s="245"/>
+      <c r="W4" s="245"/>
     </row>
     <row r="5" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A5" s="172" t="inlineStr">
@@ -8398,6 +9311,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="255"/>
+      <c r="R5" s="245"/>
       <c r="S5" s="245" t="inlineStr">
         <is>
           <r>
@@ -8405,6 +9319,10 @@
           </r>
         </is>
       </c>
+      <c r="T5" s="245"/>
+      <c r="U5" s="245"/>
+      <c r="V5" s="245"/>
+      <c r="W5" s="245"/>
     </row>
     <row r="6" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A6" s="172" t="inlineStr">
@@ -8442,6 +9360,7 @@
       <c r="O6" s="254"/>
       <c r="P6" s="254"/>
       <c r="Q6" s="255"/>
+      <c r="R6" s="245"/>
       <c r="S6" s="283" t="inlineStr">
         <is>
           <r>
@@ -8449,6 +9368,10 @@
           </r>
         </is>
       </c>
+      <c r="T6" s="245"/>
+      <c r="U6" s="245"/>
+      <c r="V6" s="245"/>
+      <c r="W6" s="245"/>
     </row>
     <row r="7" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A7" s="172" t="inlineStr">
@@ -8480,6 +9403,12 @@
       <c r="O7" s="254"/>
       <c r="P7" s="254"/>
       <c r="Q7" s="255"/>
+      <c r="R7" s="245"/>
+      <c r="S7" s="245"/>
+      <c r="T7" s="245"/>
+      <c r="U7" s="245"/>
+      <c r="V7" s="245"/>
+      <c r="W7" s="245"/>
     </row>
     <row r="8" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A8" s="258" t="inlineStr">
@@ -8536,6 +9465,11 @@
           </r>
         </is>
       </c>
+      <c r="S8" s="245"/>
+      <c r="T8" s="245"/>
+      <c r="U8" s="245"/>
+      <c r="V8" s="245"/>
+      <c r="W8" s="245"/>
     </row>
     <row r="9" spans="1:23" customHeight="1" ht="6.75" s="245" customFormat="1">
       <c r="A9" s="1"/>
@@ -8555,6 +9489,12 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
+      <c r="U9" s="245"/>
+      <c r="V9" s="245"/>
+      <c r="W9" s="245"/>
     </row>
     <row r="10" spans="1:23" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A10" s="284" t="inlineStr">
@@ -8564,7 +9504,28 @@
           </r>
         </is>
       </c>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
+      <c r="M10" s="245"/>
+      <c r="N10" s="245"/>
+      <c r="O10" s="245"/>
+      <c r="P10" s="245"/>
       <c r="Q10" s="262"/>
+      <c r="R10" s="245"/>
+      <c r="S10" s="245"/>
+      <c r="T10" s="245"/>
+      <c r="U10" s="245"/>
+      <c r="V10" s="245"/>
+      <c r="W10" s="245"/>
     </row>
     <row r="11" spans="1:23" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A11" s="1"/>
@@ -8575,7 +9536,27 @@
           </r>
         </is>
       </c>
+      <c r="C11" s="245"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
+      <c r="M11" s="245"/>
+      <c r="N11" s="245"/>
+      <c r="O11" s="245"/>
+      <c r="P11" s="245"/>
       <c r="Q11" s="262"/>
+      <c r="R11" s="245"/>
+      <c r="S11" s="245"/>
+      <c r="T11" s="245"/>
+      <c r="U11" s="245"/>
+      <c r="V11" s="245"/>
+      <c r="W11" s="245"/>
     </row>
     <row r="12" spans="1:23" customHeight="1" ht="20.25" s="245" customFormat="1">
       <c r="A12" s="1"/>
@@ -8601,6 +9582,12 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
+      <c r="R12" s="245"/>
+      <c r="S12" s="245"/>
+      <c r="T12" s="245"/>
+      <c r="U12" s="245"/>
+      <c r="V12" s="245"/>
+      <c r="W12" s="245"/>
     </row>
     <row r="13" spans="1:23" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
@@ -8617,6 +9604,13 @@
           </r>
         </is>
       </c>
+      <c r="C13" s="245"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
       <c r="J13" s="245" t="inlineStr">
         <is>
           <r>
@@ -8624,29 +9618,73 @@
           </r>
         </is>
       </c>
+      <c r="K13" s="245"/>
       <c r="L13" s="168" t="str">
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
+      <c r="M13" s="245"/>
+      <c r="N13" s="245"/>
       <c r="O13" s="245"/>
       <c r="P13" s="263"/>
       <c r="Q13" s="5"/>
+      <c r="R13" s="245"/>
       <c r="S13" s="72"/>
+      <c r="T13" s="245"/>
+      <c r="U13" s="245"/>
+      <c r="V13" s="245"/>
+      <c r="W13" s="245"/>
     </row>
     <row r="14" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A14" s="4"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
+      <c r="R14" s="245"/>
+      <c r="S14" s="245"/>
+      <c r="T14" s="245"/>
+      <c r="U14" s="245"/>
+      <c r="V14" s="245"/>
+      <c r="W14" s="245"/>
     </row>
     <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="245"/>
+      <c r="H15" s="245"/>
+      <c r="I15" s="245"/>
       <c r="J15" s="393" t="s">
         <v>191</v>
       </c>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
+      <c r="M15" s="245"/>
+      <c r="N15" s="245"/>
+      <c r="O15" s="245"/>
+      <c r="P15" s="245"/>
       <c r="Q15" s="262"/>
+      <c r="R15" s="245"/>
+      <c r="S15" s="245"/>
+      <c r="T15" s="245"/>
+      <c r="U15" s="245"/>
+      <c r="V15" s="245"/>
       <c r="W15" s="245" t="inlineStr">
         <is>
           <r>
@@ -8673,6 +9711,12 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
+      <c r="R16" s="245"/>
+      <c r="S16" s="245"/>
+      <c r="T16" s="245"/>
+      <c r="U16" s="245"/>
+      <c r="V16" s="245"/>
+      <c r="W16" s="245"/>
     </row>
     <row r="17" spans="1:23" customHeight="1" ht="8.25" s="245" customFormat="1">
       <c r="A17" s="4"/>
@@ -8683,13 +9727,27 @@
           </r>
         </is>
       </c>
+      <c r="C17" s="245"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
       <c r="I17" s="264"/>
       <c r="J17" s="264"/>
       <c r="K17" s="264"/>
       <c r="L17" s="264"/>
       <c r="M17" s="264"/>
       <c r="N17" s="264"/>
+      <c r="O17" s="245"/>
+      <c r="P17" s="245"/>
       <c r="Q17" s="5"/>
+      <c r="R17" s="245"/>
+      <c r="S17" s="245"/>
+      <c r="T17" s="245"/>
+      <c r="U17" s="245"/>
+      <c r="V17" s="245"/>
+      <c r="W17" s="245"/>
     </row>
     <row r="18" spans="1:23" customHeight="1" ht="21.75" s="245" customFormat="1">
       <c r="A18" s="265" t="inlineStr">
@@ -8708,6 +9766,7 @@
       <c r="H18" s="254"/>
       <c r="I18" s="254"/>
       <c r="J18" s="255"/>
+      <c r="K18" s="245"/>
       <c r="L18" s="266" t="inlineStr">
         <is>
           <r>
@@ -8720,6 +9779,12 @@
       <c r="O18" s="254"/>
       <c r="P18" s="254"/>
       <c r="Q18" s="255"/>
+      <c r="R18" s="245"/>
+      <c r="S18" s="245"/>
+      <c r="T18" s="245"/>
+      <c r="U18" s="245"/>
+      <c r="V18" s="245"/>
+      <c r="W18" s="245"/>
     </row>
     <row r="19" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
@@ -8747,6 +9812,7 @@
       <c r="H19" s="250"/>
       <c r="I19" s="250"/>
       <c r="J19" s="251"/>
+      <c r="K19" s="245"/>
       <c r="L19" s="285" t="inlineStr">
         <is>
           <r>
@@ -8793,6 +9859,12 @@
           </r>
         </is>
       </c>
+      <c r="R19" s="245"/>
+      <c r="S19" s="245"/>
+      <c r="T19" s="245"/>
+      <c r="U19" s="245"/>
+      <c r="V19" s="245"/>
+      <c r="W19" s="245"/>
     </row>
     <row r="20" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
@@ -8817,12 +9889,19 @@
       <c r="H20" s="252"/>
       <c r="I20" s="252"/>
       <c r="J20" s="253"/>
+      <c r="K20" s="245"/>
       <c r="L20" s="290"/>
       <c r="M20" s="290"/>
       <c r="N20" s="290"/>
       <c r="O20" s="290"/>
       <c r="P20" s="290"/>
       <c r="Q20" s="290"/>
+      <c r="R20" s="245"/>
+      <c r="S20" s="245"/>
+      <c r="T20" s="245"/>
+      <c r="U20" s="245"/>
+      <c r="V20" s="245"/>
+      <c r="W20" s="245"/>
     </row>
     <row r="21" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
@@ -8877,6 +9956,7 @@
           </r>
         </is>
       </c>
+      <c r="K21" s="245"/>
       <c r="L21" s="121" t="str">
         <f>구매리스트!I10</f>
         <v>0</v>
@@ -8899,6 +9979,11 @@
           </r>
         </is>
       </c>
+      <c r="S21" s="245"/>
+      <c r="T21" s="245"/>
+      <c r="U21" s="245"/>
+      <c r="V21" s="245"/>
+      <c r="W21" s="245"/>
     </row>
     <row r="22" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
@@ -8953,12 +10038,14 @@
           </r>
         </is>
       </c>
+      <c r="K22" s="245"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
+      <c r="R22" s="245"/>
       <c r="S22" s="245" t="inlineStr">
         <is>
           <r>
@@ -8966,6 +10053,10 @@
           </r>
         </is>
       </c>
+      <c r="T22" s="245"/>
+      <c r="U22" s="245"/>
+      <c r="V22" s="245"/>
+      <c r="W22" s="245"/>
     </row>
     <row r="23" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
@@ -9020,12 +10111,19 @@
           </r>
         </is>
       </c>
+      <c r="K23" s="245"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
+      <c r="R23" s="245"/>
+      <c r="S23" s="245"/>
+      <c r="T23" s="245"/>
+      <c r="U23" s="245"/>
+      <c r="V23" s="245"/>
+      <c r="W23" s="245"/>
     </row>
     <row r="24" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A24" s="268" t="inlineStr">
@@ -9059,12 +10157,14 @@
         </is>
       </c>
       <c r="J24" s="251"/>
+      <c r="K24" s="245"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
+      <c r="R24" s="245"/>
       <c r="S24" s="245" t="inlineStr">
         <is>
           <r>
@@ -9072,6 +10172,10 @@
           </r>
         </is>
       </c>
+      <c r="T24" s="245"/>
+      <c r="U24" s="245"/>
+      <c r="V24" s="245"/>
+      <c r="W24" s="245"/>
     </row>
     <row r="25" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A25" s="271"/>
@@ -9085,13 +10189,25 @@
       </c>
       <c r="C25" s="262"/>
       <c r="D25" s="271"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
       <c r="J25" s="262"/>
+      <c r="K25" s="245"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
+      <c r="R25" s="245"/>
+      <c r="S25" s="245"/>
+      <c r="T25" s="245"/>
+      <c r="U25" s="245"/>
+      <c r="V25" s="245"/>
+      <c r="W25" s="245"/>
     </row>
     <row r="26" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A26" s="272"/>
@@ -9104,12 +10220,14 @@
       <c r="H26" s="252"/>
       <c r="I26" s="252"/>
       <c r="J26" s="253"/>
+      <c r="K26" s="245"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
+      <c r="R26" s="245"/>
       <c r="S26" s="245" t="inlineStr">
         <is>
           <r>
@@ -9117,6 +10235,10 @@
           </r>
         </is>
       </c>
+      <c r="T26" s="245"/>
+      <c r="U26" s="245"/>
+      <c r="V26" s="245"/>
+      <c r="W26" s="245"/>
     </row>
     <row r="27" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
@@ -9150,12 +10272,19 @@
       </c>
       <c r="I27" s="254"/>
       <c r="J27" s="255"/>
+      <c r="K27" s="245"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
+      <c r="R27" s="245"/>
+      <c r="S27" s="245"/>
+      <c r="T27" s="245"/>
+      <c r="U27" s="245"/>
+      <c r="V27" s="245"/>
+      <c r="W27" s="245"/>
     </row>
     <row r="28" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
@@ -9190,12 +10319,19 @@
         </is>
       </c>
       <c r="J28" s="251"/>
+      <c r="K28" s="245"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
+      <c r="R28" s="245"/>
+      <c r="S28" s="245"/>
+      <c r="T28" s="245"/>
+      <c r="U28" s="245"/>
+      <c r="V28" s="245"/>
+      <c r="W28" s="245"/>
     </row>
     <row r="29" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A29" s="292" t="inlineStr">
@@ -9205,15 +10341,28 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="245"/>
       <c r="C29" s="262"/>
       <c r="D29" s="271"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
       <c r="J29" s="262"/>
+      <c r="K29" s="245"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
+      <c r="R29" s="245"/>
+      <c r="S29" s="245"/>
+      <c r="T29" s="245"/>
+      <c r="U29" s="245"/>
+      <c r="V29" s="245"/>
+      <c r="W29" s="245"/>
     </row>
     <row r="30" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A30" s="293" t="inlineStr">
@@ -9232,12 +10381,19 @@
       <c r="H30" s="252"/>
       <c r="I30" s="252"/>
       <c r="J30" s="253"/>
+      <c r="K30" s="245"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
+      <c r="R30" s="245"/>
+      <c r="S30" s="245"/>
+      <c r="T30" s="245"/>
+      <c r="U30" s="245"/>
+      <c r="V30" s="245"/>
+      <c r="W30" s="245"/>
     </row>
     <row r="31" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
@@ -9275,12 +10431,19 @@
       </c>
       <c r="I31" s="254"/>
       <c r="J31" s="255"/>
+      <c r="K31" s="245"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
+      <c r="R31" s="245"/>
+      <c r="S31" s="245"/>
+      <c r="T31" s="245"/>
+      <c r="U31" s="245"/>
+      <c r="V31" s="245"/>
+      <c r="W31" s="245"/>
     </row>
     <row r="32" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
@@ -9330,12 +10493,19 @@
         </is>
       </c>
       <c r="J32" s="255"/>
+      <c r="K32" s="245"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
+      <c r="R32" s="245"/>
+      <c r="S32" s="245"/>
+      <c r="T32" s="245"/>
+      <c r="U32" s="245"/>
+      <c r="V32" s="245"/>
+      <c r="W32" s="245"/>
     </row>
     <row r="33" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
@@ -9379,12 +10549,19 @@
         </is>
       </c>
       <c r="J33" s="255"/>
+      <c r="K33" s="245"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
+      <c r="R33" s="245"/>
+      <c r="S33" s="245"/>
+      <c r="T33" s="245"/>
+      <c r="U33" s="245"/>
+      <c r="V33" s="245"/>
+      <c r="W33" s="245"/>
     </row>
     <row r="34" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A34" s="277" t="inlineStr">
@@ -9403,32 +10580,69 @@
       <c r="H34" s="250"/>
       <c r="I34" s="250"/>
       <c r="J34" s="251"/>
+      <c r="K34" s="245"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
       <c r="O34" s="14"/>
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
+      <c r="R34" s="245"/>
+      <c r="S34" s="245"/>
+      <c r="T34" s="245"/>
+      <c r="U34" s="245"/>
+      <c r="V34" s="245"/>
+      <c r="W34" s="245"/>
     </row>
     <row r="35" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A35" s="271"/>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="245"/>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
       <c r="J35" s="262"/>
+      <c r="K35" s="245"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
+      <c r="R35" s="245"/>
+      <c r="S35" s="245"/>
+      <c r="T35" s="245"/>
+      <c r="U35" s="245"/>
+      <c r="V35" s="245"/>
+      <c r="W35" s="245"/>
     </row>
     <row r="36" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A36" s="271"/>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
       <c r="J36" s="262"/>
+      <c r="K36" s="245"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
+      <c r="R36" s="245"/>
+      <c r="S36" s="245"/>
+      <c r="T36" s="245"/>
+      <c r="U36" s="245"/>
+      <c r="V36" s="245"/>
+      <c r="W36" s="245"/>
     </row>
     <row r="37" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A37" s="272"/>
@@ -9441,12 +10655,19 @@
       <c r="H37" s="252"/>
       <c r="I37" s="252"/>
       <c r="J37" s="253"/>
+      <c r="K37" s="245"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
+      <c r="R37" s="245"/>
+      <c r="S37" s="245"/>
+      <c r="T37" s="245"/>
+      <c r="U37" s="245"/>
+      <c r="V37" s="245"/>
+      <c r="W37" s="245"/>
     </row>
     <row r="38" spans="1:23" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A38" s="172" t="inlineStr">
@@ -9465,6 +10686,7 @@
       <c r="H38" s="254"/>
       <c r="I38" s="254"/>
       <c r="J38" s="255"/>
+      <c r="K38" s="245"/>
       <c r="L38" s="296" t="inlineStr">
         <is>
           <r>
@@ -9477,6 +10699,12 @@
       <c r="O38" s="250"/>
       <c r="P38" s="250"/>
       <c r="Q38" s="251"/>
+      <c r="R38" s="245"/>
+      <c r="S38" s="245"/>
+      <c r="T38" s="245"/>
+      <c r="U38" s="245"/>
+      <c r="V38" s="245"/>
+      <c r="W38" s="245"/>
     </row>
     <row r="39" spans="1:23" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A39" s="279" t="inlineStr">
@@ -9508,6 +10736,7 @@
       </c>
       <c r="I39" s="254"/>
       <c r="J39" s="255"/>
+      <c r="K39" s="245"/>
       <c r="L39" s="299" t="inlineStr">
         <is>
           <r>
@@ -9520,6 +10749,12 @@
       <c r="O39" s="250"/>
       <c r="P39" s="250"/>
       <c r="Q39" s="251"/>
+      <c r="R39" s="245"/>
+      <c r="S39" s="245"/>
+      <c r="T39" s="245"/>
+      <c r="U39" s="245"/>
+      <c r="V39" s="245"/>
+      <c r="W39" s="245"/>
     </row>
     <row r="40" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
@@ -9556,8 +10791,19 @@
       </c>
       <c r="I40" s="254"/>
       <c r="J40" s="255"/>
+      <c r="K40" s="245"/>
       <c r="L40" s="4"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="245"/>
+      <c r="P40" s="245"/>
       <c r="Q40" s="5"/>
+      <c r="R40" s="245"/>
+      <c r="S40" s="245"/>
+      <c r="T40" s="245"/>
+      <c r="U40" s="245"/>
+      <c r="V40" s="245"/>
+      <c r="W40" s="245"/>
     </row>
     <row r="41" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
@@ -9594,7 +10840,10 @@
       </c>
       <c r="I41" s="254"/>
       <c r="J41" s="255"/>
+      <c r="K41" s="245"/>
       <c r="L41" s="4"/>
+      <c r="M41" s="245"/>
+      <c r="N41" s="245"/>
       <c r="O41" s="245" t="inlineStr">
         <is>
           <r>
@@ -9602,7 +10851,14 @@
           </r>
         </is>
       </c>
+      <c r="P41" s="245"/>
       <c r="Q41" s="5"/>
+      <c r="R41" s="245"/>
+      <c r="S41" s="245"/>
+      <c r="T41" s="245"/>
+      <c r="U41" s="245"/>
+      <c r="V41" s="245"/>
+      <c r="W41" s="245"/>
     </row>
     <row r="42" spans="1:23" customHeight="1" ht="33" s="245" customFormat="1">
       <c r="A42" s="297" t="inlineStr">
@@ -9621,8 +10877,19 @@
       <c r="H42" s="254"/>
       <c r="I42" s="254"/>
       <c r="J42" s="255"/>
+      <c r="K42" s="245"/>
       <c r="L42" s="4"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
+      <c r="P42" s="245"/>
       <c r="Q42" s="5"/>
+      <c r="R42" s="245"/>
+      <c r="S42" s="245"/>
+      <c r="T42" s="245"/>
+      <c r="U42" s="245"/>
+      <c r="V42" s="245"/>
+      <c r="W42" s="245"/>
     </row>
     <row r="43" spans="1:23" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A43" s="300" t="inlineStr">
@@ -9647,8 +10914,19 @@
       </c>
       <c r="I43" s="254"/>
       <c r="J43" s="255"/>
+      <c r="K43" s="245"/>
       <c r="L43" s="4"/>
+      <c r="M43" s="245"/>
+      <c r="N43" s="245"/>
+      <c r="O43" s="245"/>
+      <c r="P43" s="245"/>
       <c r="Q43" s="5"/>
+      <c r="R43" s="245"/>
+      <c r="S43" s="245"/>
+      <c r="T43" s="245"/>
+      <c r="U43" s="245"/>
+      <c r="V43" s="245"/>
+      <c r="W43" s="245"/>
     </row>
     <row r="44" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
@@ -9673,8 +10951,19 @@
       </c>
       <c r="I44" s="254"/>
       <c r="J44" s="255"/>
+      <c r="K44" s="245"/>
       <c r="L44" s="4"/>
+      <c r="M44" s="245"/>
+      <c r="N44" s="245"/>
+      <c r="O44" s="245"/>
+      <c r="P44" s="245"/>
       <c r="Q44" s="5"/>
+      <c r="R44" s="245"/>
+      <c r="S44" s="245"/>
+      <c r="T44" s="245"/>
+      <c r="U44" s="245"/>
+      <c r="V44" s="245"/>
+      <c r="W44" s="245"/>
     </row>
     <row r="45" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
@@ -9706,9 +10995,45 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
-    </row>
-    <row r="46" spans="1:23" customHeight="1" ht="6" s="245" customFormat="1"/>
+      <c r="R45" s="245"/>
+      <c r="S45" s="245"/>
+      <c r="T45" s="245"/>
+      <c r="U45" s="245"/>
+      <c r="V45" s="245"/>
+      <c r="W45" s="245"/>
+    </row>
+    <row r="46" spans="1:23" customHeight="1" ht="6" s="245" customFormat="1">
+      <c r="A46" s="245"/>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
+      <c r="D46" s="245"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
+      <c r="I46" s="245"/>
+      <c r="J46" s="245"/>
+      <c r="K46" s="245"/>
+      <c r="L46" s="245"/>
+      <c r="M46" s="245"/>
+      <c r="N46" s="245"/>
+      <c r="O46" s="245"/>
+      <c r="P46" s="245"/>
+      <c r="Q46" s="245"/>
+      <c r="R46" s="245"/>
+      <c r="S46" s="245"/>
+      <c r="T46" s="245"/>
+      <c r="U46" s="245"/>
+      <c r="V46" s="245"/>
+      <c r="W46" s="245"/>
+    </row>
     <row r="47" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A47" s="245"/>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
+      <c r="D47" s="245"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
       <c r="G47" s="162" t="inlineStr">
         <is>
           <r>
@@ -9716,6 +11041,12 @@
           </r>
         </is>
       </c>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
+      <c r="K47" s="245"/>
+      <c r="L47" s="245"/>
+      <c r="M47" s="245"/>
       <c r="N47" s="163" t="inlineStr">
         <is>
           <r>
@@ -9723,6 +11054,15 @@
           </r>
         </is>
       </c>
+      <c r="O47" s="245"/>
+      <c r="P47" s="245"/>
+      <c r="Q47" s="245"/>
+      <c r="R47" s="245"/>
+      <c r="S47" s="245"/>
+      <c r="T47" s="245"/>
+      <c r="U47" s="245"/>
+      <c r="V47" s="245"/>
+      <c r="W47" s="245"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -9871,6 +11211,20 @@
           </r>
         </is>
       </c>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
+      <c r="I1" s="245"/>
+      <c r="J1" s="245"/>
+      <c r="K1" s="245"/>
+      <c r="L1" s="245"/>
+      <c r="M1" s="245"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="245"/>
     </row>
     <row r="2" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
       <c r="A2" s="200" t="inlineStr">
@@ -9880,6 +11234,20 @@
           </r>
         </is>
       </c>
+      <c r="B2" s="245"/>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="245"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="M2" s="245"/>
+      <c r="N2" s="245"/>
+      <c r="O2" s="245"/>
     </row>
     <row r="3" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
       <c r="A3" s="200" t="inlineStr">
@@ -9889,6 +11257,20 @@
           </r>
         </is>
       </c>
+      <c r="B3" s="245"/>
+      <c r="C3" s="245"/>
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="245"/>
+      <c r="H3" s="245"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="M3" s="245"/>
+      <c r="N3" s="245"/>
+      <c r="O3" s="245"/>
     </row>
     <row r="4" spans="1:15" customHeight="1" ht="38.25" s="245" customFormat="1">
       <c r="A4" s="196" t="inlineStr">
@@ -9898,6 +11280,20 @@
           </r>
         </is>
       </c>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="M4" s="245"/>
+      <c r="N4" s="245"/>
+      <c r="O4" s="245"/>
     </row>
     <row r="5" spans="1:15" customHeight="1" ht="27.75" s="245" customFormat="1">
       <c r="A5" s="203" t="inlineStr">
@@ -9907,6 +11303,20 @@
           </r>
         </is>
       </c>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="M5" s="245"/>
+      <c r="N5" s="245"/>
+      <c r="O5" s="245"/>
     </row>
     <row r="6" spans="1:15" customHeight="1" ht="24.95" s="245" customFormat="1">
       <c r="A6" s="92" t="inlineStr">
@@ -10023,6 +11433,7 @@
       <c r="O8" s="81"/>
     </row>
     <row r="9" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A9" s="245"/>
       <c r="B9" s="304"/>
       <c r="C9" s="180" t="inlineStr">
         <is>
@@ -10045,15 +11456,19 @@
           </r>
         </is>
       </c>
+      <c r="I9" s="245"/>
       <c r="J9" s="304"/>
       <c r="K9" s="202" t="str">
         <f>구매리스트!D7</f>
         <v>0</v>
       </c>
+      <c r="L9" s="245"/>
+      <c r="M9" s="245"/>
       <c r="N9" s="82"/>
       <c r="O9" s="83"/>
     </row>
     <row r="10" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A10" s="245"/>
       <c r="B10" s="304"/>
       <c r="C10" s="201" t="inlineStr">
         <is>
@@ -10088,6 +11503,7 @@
       <c r="O10" s="308"/>
     </row>
     <row r="11" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A11" s="245"/>
       <c r="B11" s="304"/>
       <c r="C11" s="199" t="inlineStr">
         <is>
@@ -10116,6 +11532,7 @@
       <c r="O11" s="312"/>
     </row>
     <row r="12" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A12" s="245"/>
       <c r="B12" s="304"/>
       <c r="C12" s="180" t="inlineStr">
         <is>
@@ -10129,6 +11546,7 @@
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
+      <c r="F12" s="245"/>
       <c r="G12" s="304"/>
       <c r="H12" s="180" t="inlineStr">
         <is>
@@ -10137,13 +11555,19 @@
           </r>
         </is>
       </c>
+      <c r="I12" s="245"/>
       <c r="J12" s="304"/>
       <c r="K12" s="183" t="str">
         <f>구매리스트!D6</f>
         <v>0</v>
       </c>
+      <c r="L12" s="245"/>
+      <c r="M12" s="245"/>
+      <c r="N12" s="245"/>
+      <c r="O12" s="245"/>
     </row>
     <row r="13" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A13" s="245"/>
       <c r="B13" s="304"/>
       <c r="C13" s="180" t="inlineStr">
         <is>
@@ -10154,6 +11578,7 @@
       </c>
       <c r="D13" s="304"/>
       <c r="E13" s="305"/>
+      <c r="F13" s="245"/>
       <c r="G13" s="304"/>
       <c r="H13" s="180" t="inlineStr">
         <is>
@@ -10162,10 +11587,16 @@
           </r>
         </is>
       </c>
+      <c r="I13" s="245"/>
       <c r="J13" s="304"/>
       <c r="K13" s="305"/>
+      <c r="L13" s="245"/>
+      <c r="M13" s="245"/>
+      <c r="N13" s="245"/>
+      <c r="O13" s="245"/>
     </row>
     <row r="14" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A14" s="245"/>
       <c r="B14" s="304"/>
       <c r="C14" s="178" t="inlineStr">
         <is>
@@ -10201,6 +11632,7 @@
       <c r="O14" s="315"/>
     </row>
     <row r="15" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A15" s="245"/>
       <c r="B15" s="304"/>
       <c r="C15" s="180" t="inlineStr">
         <is>
@@ -10211,12 +11643,19 @@
       </c>
       <c r="D15" s="304"/>
       <c r="E15" s="305"/>
+      <c r="F15" s="245"/>
       <c r="G15" s="304"/>
       <c r="H15" s="305"/>
+      <c r="I15" s="245"/>
       <c r="J15" s="304"/>
       <c r="K15" s="305"/>
+      <c r="L15" s="245"/>
+      <c r="M15" s="245"/>
+      <c r="N15" s="245"/>
+      <c r="O15" s="245"/>
     </row>
     <row r="16" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A16" s="245"/>
       <c r="B16" s="304"/>
       <c r="C16" s="179" t="inlineStr">
         <is>
@@ -10239,6 +11678,7 @@
       <c r="O16" s="319"/>
     </row>
     <row r="17" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A17" s="245"/>
       <c r="B17" s="304"/>
       <c r="C17" s="180" t="inlineStr">
         <is>
@@ -10252,6 +11692,7 @@
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
+      <c r="F17" s="245"/>
       <c r="G17" s="304"/>
       <c r="H17" s="180" t="inlineStr">
         <is>
@@ -10260,6 +11701,7 @@
           </r>
         </is>
       </c>
+      <c r="I17" s="245"/>
       <c r="J17" s="304"/>
       <c r="K17" s="209" t="inlineStr">
         <is>
@@ -10268,8 +11710,13 @@
           </r>
         </is>
       </c>
+      <c r="L17" s="245"/>
+      <c r="M17" s="245"/>
+      <c r="N17" s="245"/>
+      <c r="O17" s="245"/>
     </row>
     <row r="18" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A18" s="245"/>
       <c r="B18" s="304"/>
       <c r="C18" s="180" t="inlineStr">
         <is>
@@ -10280,6 +11727,7 @@
       </c>
       <c r="D18" s="304"/>
       <c r="E18" s="305"/>
+      <c r="F18" s="245"/>
       <c r="G18" s="304"/>
       <c r="H18" s="180" t="inlineStr">
         <is>
@@ -10288,8 +11736,13 @@
           </r>
         </is>
       </c>
+      <c r="I18" s="245"/>
       <c r="J18" s="304"/>
       <c r="K18" s="305"/>
+      <c r="L18" s="245"/>
+      <c r="M18" s="245"/>
+      <c r="N18" s="245"/>
+      <c r="O18" s="245"/>
     </row>
     <row r="19" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A19" s="252"/>
@@ -10512,6 +11965,8 @@
           </r>
         </is>
       </c>
+      <c r="B26" s="245"/>
+      <c r="C26" s="245"/>
       <c r="D26" s="304"/>
       <c r="E26" s="216" t="inlineStr">
         <is>
@@ -10520,6 +11975,7 @@
           </r>
         </is>
       </c>
+      <c r="F26" s="245"/>
       <c r="G26" s="304"/>
       <c r="H26" s="180" t="inlineStr">
         <is>
@@ -10528,6 +11984,7 @@
           </r>
         </is>
       </c>
+      <c r="I26" s="245"/>
       <c r="J26" s="304"/>
       <c r="K26" s="94" t="inlineStr">
         <is>
@@ -10629,6 +12086,20 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="245"/>
+      <c r="C29" s="245"/>
+      <c r="D29" s="245"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
+      <c r="K29" s="245"/>
+      <c r="L29" s="245"/>
+      <c r="M29" s="245"/>
+      <c r="N29" s="245"/>
+      <c r="O29" s="245"/>
     </row>
     <row r="30" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
       <c r="A30" s="217" t="inlineStr">
@@ -10638,6 +12109,20 @@
           </r>
         </is>
       </c>
+      <c r="B30" s="245"/>
+      <c r="C30" s="245"/>
+      <c r="D30" s="245"/>
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+      <c r="G30" s="245"/>
+      <c r="H30" s="245"/>
+      <c r="I30" s="245"/>
+      <c r="J30" s="245"/>
+      <c r="K30" s="245"/>
+      <c r="L30" s="245"/>
+      <c r="M30" s="245"/>
+      <c r="N30" s="245"/>
+      <c r="O30" s="245"/>
     </row>
     <row r="31" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
       <c r="A31" s="217" t="inlineStr">
@@ -10647,6 +12132,20 @@
           </r>
         </is>
       </c>
+      <c r="B31" s="245"/>
+      <c r="C31" s="245"/>
+      <c r="D31" s="245"/>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
+      <c r="K31" s="245"/>
+      <c r="L31" s="245"/>
+      <c r="M31" s="245"/>
+      <c r="N31" s="245"/>
+      <c r="O31" s="245"/>
     </row>
     <row r="32" spans="1:15" customHeight="1" ht="9.75" s="245" customFormat="1">
       <c r="A32" s="77"/>
@@ -10691,10 +12190,16 @@
           </r>
         </is>
       </c>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
       <c r="K33" s="218" t="str">
         <f>E24</f>
         <v>0</v>
       </c>
+      <c r="L33" s="245"/>
+      <c r="M33" s="245"/>
+      <c r="N33" s="245"/>
       <c r="O33" s="77"/>
     </row>
     <row r="34" spans="1:15" customHeight="1" ht="85.5" s="245" customFormat="1">
@@ -10724,6 +12229,18 @@
           </r>
         </is>
       </c>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="245"/>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
+      <c r="J35" s="245"/>
+      <c r="K35" s="245"/>
+      <c r="L35" s="245"/>
+      <c r="M35" s="245"/>
       <c r="N35" s="77"/>
       <c r="O35" s="77"/>
     </row>
@@ -10735,6 +12252,18 @@
           </r>
         </is>
       </c>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
+      <c r="J36" s="245"/>
+      <c r="K36" s="245"/>
+      <c r="L36" s="245"/>
+      <c r="M36" s="245"/>
       <c r="N36" s="78"/>
       <c r="O36" s="77"/>
     </row>
@@ -10746,6 +12275,18 @@
           </r>
         </is>
       </c>
+      <c r="B37" s="245"/>
+      <c r="C37" s="245"/>
+      <c r="D37" s="245"/>
+      <c r="E37" s="245"/>
+      <c r="F37" s="245"/>
+      <c r="G37" s="245"/>
+      <c r="H37" s="245"/>
+      <c r="I37" s="245"/>
+      <c r="J37" s="245"/>
+      <c r="K37" s="245"/>
+      <c r="L37" s="245"/>
+      <c r="M37" s="245"/>
       <c r="N37" s="86"/>
       <c r="O37" s="87"/>
     </row>
@@ -10803,6 +12344,20 @@
           </r>
         </is>
       </c>
+      <c r="B40" s="245"/>
+      <c r="C40" s="245"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="245"/>
     </row>
     <row r="41" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="191" t="inlineStr">
@@ -10812,6 +12367,20 @@
           </r>
         </is>
       </c>
+      <c r="B41" s="245"/>
+      <c r="C41" s="245"/>
+      <c r="D41" s="245"/>
+      <c r="E41" s="245"/>
+      <c r="F41" s="245"/>
+      <c r="G41" s="245"/>
+      <c r="H41" s="245"/>
+      <c r="I41" s="245"/>
+      <c r="J41" s="245"/>
+      <c r="K41" s="245"/>
+      <c r="L41" s="245"/>
+      <c r="M41" s="245"/>
+      <c r="N41" s="245"/>
+      <c r="O41" s="245"/>
     </row>
     <row r="42" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A42" s="191" t="inlineStr">
@@ -10821,6 +12390,20 @@
           </r>
         </is>
       </c>
+      <c r="B42" s="245"/>
+      <c r="C42" s="245"/>
+      <c r="D42" s="245"/>
+      <c r="E42" s="245"/>
+      <c r="F42" s="245"/>
+      <c r="G42" s="245"/>
+      <c r="H42" s="245"/>
+      <c r="I42" s="245"/>
+      <c r="J42" s="245"/>
+      <c r="K42" s="245"/>
+      <c r="L42" s="245"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
     </row>
     <row r="43" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A43" s="221" t="inlineStr">
@@ -10898,6 +12481,9 @@
       <c r="I45" s="76"/>
       <c r="J45" s="76"/>
       <c r="K45" s="333"/>
+      <c r="L45" s="245"/>
+      <c r="M45" s="245"/>
+      <c r="N45" s="245"/>
       <c r="O45" s="334"/>
     </row>
     <row r="46" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -10908,7 +12494,19 @@
           </r>
         </is>
       </c>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
+      <c r="D46" s="245"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
+      <c r="I46" s="245"/>
+      <c r="J46" s="245"/>
       <c r="K46" s="333"/>
+      <c r="L46" s="245"/>
+      <c r="M46" s="245"/>
+      <c r="N46" s="245"/>
       <c r="O46" s="334"/>
     </row>
     <row r="47" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -10919,7 +12517,19 @@
           </r>
         </is>
       </c>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
+      <c r="D47" s="245"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
+      <c r="G47" s="245"/>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
       <c r="K47" s="333"/>
+      <c r="L47" s="245"/>
+      <c r="M47" s="245"/>
+      <c r="N47" s="245"/>
       <c r="O47" s="334"/>
     </row>
     <row r="48" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -10930,7 +12540,19 @@
           </r>
         </is>
       </c>
+      <c r="B48" s="245"/>
+      <c r="C48" s="245"/>
+      <c r="D48" s="245"/>
+      <c r="E48" s="245"/>
+      <c r="F48" s="245"/>
+      <c r="G48" s="245"/>
+      <c r="H48" s="245"/>
+      <c r="I48" s="245"/>
+      <c r="J48" s="245"/>
       <c r="K48" s="333"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="245"/>
       <c r="O48" s="334"/>
     </row>
     <row r="49" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -10942,7 +12564,18 @@
         </is>
       </c>
       <c r="B49" s="245"/>
+      <c r="C49" s="245"/>
+      <c r="D49" s="245"/>
+      <c r="E49" s="245"/>
+      <c r="F49" s="245"/>
+      <c r="G49" s="245"/>
+      <c r="H49" s="245"/>
+      <c r="I49" s="245"/>
+      <c r="J49" s="245"/>
       <c r="K49" s="333"/>
+      <c r="L49" s="245"/>
+      <c r="M49" s="245"/>
+      <c r="N49" s="245"/>
       <c r="O49" s="334"/>
     </row>
     <row r="50" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -11086,9 +12719,37 @@
           </r>
         </is>
       </c>
+      <c r="B55" s="89"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
+      <c r="H55" s="89"/>
+      <c r="I55" s="89"/>
+      <c r="J55" s="89"/>
+      <c r="K55" s="89"/>
+      <c r="L55" s="89"/>
+      <c r="M55" s="89"/>
+      <c r="N55" s="89"/>
+      <c r="O55" s="89"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="245"/>
+      <c r="B56" s="245"/>
+      <c r="C56" s="245"/>
+      <c r="D56" s="245"/>
+      <c r="E56" s="245"/>
+      <c r="F56" s="245"/>
+      <c r="G56" s="245"/>
+      <c r="H56" s="245"/>
+      <c r="I56" s="245"/>
+      <c r="J56" s="245"/>
+      <c r="K56" s="245"/>
+      <c r="L56" s="245"/>
+      <c r="M56" s="245"/>
+      <c r="N56" s="245"/>
+      <c r="O56" s="245"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -11237,6 +12898,7 @@
       <c r="G1" s="254"/>
       <c r="H1" s="254"/>
       <c r="I1" s="255"/>
+      <c r="J1" s="245"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A2" s="342" t="inlineStr">
@@ -11269,19 +12931,14 @@
         </is>
       </c>
       <c r="I2" s="251"/>
+      <c r="J2" s="245"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A3" s="344" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">SSANCAR LTD.,
-163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Kore
-TEL:82-505-366-9977 
-FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
-          </r>
-        </is>
-      </c>
+      <c r="A3" s="344" t="s">
+        <v>311</v>
+      </c>
+      <c r="B3" s="245"/>
+      <c r="C3" s="245"/>
       <c r="D3" s="262"/>
       <c r="E3" s="228" t="inlineStr">
         <is>
@@ -11290,15 +12947,19 @@
           </r>
         </is>
       </c>
+      <c r="F3" s="245"/>
       <c r="G3" s="129" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
       <c r="H3" s="272"/>
       <c r="I3" s="253"/>
+      <c r="J3" s="245"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A4" s="271"/>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
       <c r="D4" s="262"/>
       <c r="E4" s="345" t="inlineStr">
         <is>
@@ -11307,16 +12968,28 @@
           </r>
         </is>
       </c>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="262"/>
+      <c r="J4" s="245"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A5" s="271"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
       <c r="D5" s="262"/>
       <c r="E5" s="271"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
       <c r="I5" s="262"/>
+      <c r="J5" s="245"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A6" s="271"/>
+      <c r="B6" s="245"/>
+      <c r="C6" s="245"/>
       <c r="D6" s="262"/>
       <c r="E6" s="346" t="inlineStr">
         <is>
@@ -11325,7 +12998,11 @@
           </r>
         </is>
       </c>
+      <c r="F6" s="245"/>
+      <c r="G6" s="245"/>
+      <c r="H6" s="245"/>
       <c r="I6" s="262"/>
+      <c r="J6" s="245"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A7" s="272"/>
@@ -11339,7 +13016,11 @@
           </r>
         </is>
       </c>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
       <c r="I7" s="262"/>
+      <c r="J7" s="245"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A8" s="342" t="inlineStr">
@@ -11363,12 +13044,15 @@
       <c r="G8" s="252"/>
       <c r="H8" s="252"/>
       <c r="I8" s="253"/>
+      <c r="J8" s="245"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
       <c r="A9" s="348" t="str">
         <f>구매리스트!B14</f>
         <v>0</v>
       </c>
+      <c r="B9" s="245"/>
+      <c r="C9" s="245"/>
       <c r="D9" s="262"/>
       <c r="E9" s="234" t="inlineStr">
         <is>
@@ -11391,6 +13075,8 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A10" s="271"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="262"/>
       <c r="E10" s="225" t="inlineStr">
         <is>
@@ -11403,6 +13089,7 @@
       <c r="G10" s="250"/>
       <c r="H10" s="250"/>
       <c r="I10" s="251"/>
+      <c r="J10" s="245"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="35.25" s="245" customFormat="1">
       <c r="A11" s="272"/>
@@ -11413,10 +13100,14 @@
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
       <c r="I11" s="53" t="str">
         <f>TODAY()</f>
         <v>0</v>
       </c>
+      <c r="J11" s="245"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A12" s="342" t="inlineStr">
@@ -11440,6 +13131,7 @@
       <c r="G12" s="250"/>
       <c r="H12" s="250"/>
       <c r="I12" s="251"/>
+      <c r="J12" s="245"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A13" s="349" t="inlineStr">
@@ -11449,6 +13141,8 @@
           </r>
         </is>
       </c>
+      <c r="B13" s="245"/>
+      <c r="C13" s="245"/>
       <c r="D13" s="262"/>
       <c r="E13" s="229" t="inlineStr">
         <is>
@@ -11457,7 +13151,11 @@
           </r>
         </is>
       </c>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
       <c r="I13" s="262"/>
+      <c r="J13" s="245"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="9.75" s="245" customFormat="1">
       <c r="A14" s="272"/>
@@ -11469,6 +13167,7 @@
       <c r="G14" s="252"/>
       <c r="H14" s="252"/>
       <c r="I14" s="253"/>
+      <c r="J14" s="245"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
       <c r="A15" s="342" t="inlineStr">
@@ -11498,6 +13197,7 @@
       <c r="G15" s="250"/>
       <c r="H15" s="250"/>
       <c r="I15" s="251"/>
+      <c r="J15" s="245"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A16" s="231" t="str">
@@ -11517,7 +13217,11 @@
           </r>
         </is>
       </c>
+      <c r="F16" s="245"/>
+      <c r="G16" s="245"/>
+      <c r="H16" s="245"/>
       <c r="I16" s="262"/>
+      <c r="J16" s="245"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
       <c r="A17" s="342" t="inlineStr">
@@ -11544,6 +13248,7 @@
       <c r="G17" s="250"/>
       <c r="H17" s="250"/>
       <c r="I17" s="251"/>
+      <c r="J17" s="245"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A18" s="350" t="str">
@@ -11561,6 +13266,7 @@
       <c r="G18" s="252"/>
       <c r="H18" s="252"/>
       <c r="I18" s="253"/>
+      <c r="J18" s="245"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
@@ -11608,6 +13314,7 @@
           </r>
         </is>
       </c>
+      <c r="J19" s="245"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="10.5" s="245" customFormat="1">
       <c r="A20" s="30"/>
@@ -11619,6 +13326,7 @@
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
+      <c r="J20" s="245"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
@@ -12064,7 +13772,9 @@
           </r>
         </is>
       </c>
+      <c r="F33" s="245"/>
       <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -12086,7 +13796,11 @@
           </r>
         </is>
       </c>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
       <c r="I34" s="32"/>
+      <c r="J34"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="30" t="inlineStr">
@@ -12104,6 +13818,7 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="32"/>
+      <c r="J35"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="30"/>
@@ -12115,6 +13830,7 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="32"/>
+      <c r="J36"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="30"/>
@@ -12126,6 +13842,7 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
       <c r="I37" s="32"/>
+      <c r="J37"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="30"/>
@@ -12137,6 +13854,7 @@
       <c r="G38" s="31"/>
       <c r="H38" s="31"/>
       <c r="I38" s="32"/>
+      <c r="J38"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="30"/>
@@ -12148,6 +13866,7 @@
       <c r="G39" s="31"/>
       <c r="H39" s="31"/>
       <c r="I39" s="32"/>
+      <c r="J39"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="33"/>
@@ -12159,6 +13878,7 @@
       <c r="G40" s="34"/>
       <c r="H40" s="34"/>
       <c r="I40" s="35"/>
+      <c r="J40"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -12263,6 +13983,7 @@
       <c r="G1" s="254"/>
       <c r="H1" s="254"/>
       <c r="I1" s="255"/>
+      <c r="J1" s="245"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A2" s="342" t="inlineStr">
@@ -12295,19 +14016,14 @@
         </is>
       </c>
       <c r="I2" s="251"/>
+      <c r="J2" s="245"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A3" s="344" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">SSANCAR LTD.,
-163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Kore
-TEL:82-505-366-9977 
-FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
-          </r>
-        </is>
-      </c>
+      <c r="A3" s="344" t="s">
+        <v>311</v>
+      </c>
+      <c r="B3" s="245"/>
+      <c r="C3" s="245"/>
       <c r="D3" s="262"/>
       <c r="E3" s="228" t="inlineStr">
         <is>
@@ -12316,15 +14032,19 @@
           </r>
         </is>
       </c>
+      <c r="F3" s="245"/>
       <c r="G3" s="129" t="str">
         <f>차량인보이스!G3</f>
         <v>0</v>
       </c>
       <c r="H3" s="272"/>
       <c r="I3" s="253"/>
+      <c r="J3" s="245"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A4" s="271"/>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
       <c r="D4" s="262"/>
       <c r="E4" s="345" t="inlineStr">
         <is>
@@ -12333,16 +14053,28 @@
           </r>
         </is>
       </c>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="262"/>
+      <c r="J4" s="245"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A5" s="271"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
       <c r="D5" s="262"/>
       <c r="E5" s="271"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
       <c r="I5" s="262"/>
+      <c r="J5" s="245"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A6" s="271"/>
+      <c r="B6" s="245"/>
+      <c r="C6" s="245"/>
       <c r="D6" s="262"/>
       <c r="E6" s="346" t="inlineStr">
         <is>
@@ -12351,7 +14083,11 @@
           </r>
         </is>
       </c>
+      <c r="F6" s="245"/>
+      <c r="G6" s="245"/>
+      <c r="H6" s="245"/>
       <c r="I6" s="262"/>
+      <c r="J6" s="245"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A7" s="272"/>
@@ -12365,7 +14101,11 @@
           </r>
         </is>
       </c>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
       <c r="I7" s="262"/>
+      <c r="J7" s="245"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A8" s="342" t="inlineStr">
@@ -12389,12 +14129,15 @@
       <c r="G8" s="252"/>
       <c r="H8" s="252"/>
       <c r="I8" s="253"/>
+      <c r="J8" s="245"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
       <c r="A9" s="371" t="str">
         <f>차량인보이스!A9</f>
         <v>0</v>
       </c>
+      <c r="B9" s="245"/>
+      <c r="C9" s="245"/>
       <c r="D9" s="262"/>
       <c r="E9" s="234" t="inlineStr">
         <is>
@@ -12417,6 +14160,8 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A10" s="271"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="262"/>
       <c r="E10" s="225" t="inlineStr">
         <is>
@@ -12429,6 +14174,7 @@
       <c r="G10" s="250"/>
       <c r="H10" s="250"/>
       <c r="I10" s="251"/>
+      <c r="J10" s="245"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="35.25" s="245" customFormat="1">
       <c r="A11" s="272"/>
@@ -12439,10 +14185,14 @@
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
       <c r="I11" s="53" t="str">
         <f>TODAY()</f>
         <v>0</v>
       </c>
+      <c r="J11" s="245"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A12" s="342" t="inlineStr">
@@ -12466,6 +14216,7 @@
       <c r="G12" s="250"/>
       <c r="H12" s="250"/>
       <c r="I12" s="251"/>
+      <c r="J12" s="245"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A13" s="349" t="inlineStr">
@@ -12475,6 +14226,8 @@
           </r>
         </is>
       </c>
+      <c r="B13" s="245"/>
+      <c r="C13" s="245"/>
       <c r="D13" s="262"/>
       <c r="E13" s="229" t="inlineStr">
         <is>
@@ -12483,7 +14236,11 @@
           </r>
         </is>
       </c>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
       <c r="I13" s="262"/>
+      <c r="J13" s="245"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="9.75" s="245" customFormat="1">
       <c r="A14" s="272"/>
@@ -12495,6 +14252,7 @@
       <c r="G14" s="252"/>
       <c r="H14" s="252"/>
       <c r="I14" s="253"/>
+      <c r="J14" s="245"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
       <c r="A15" s="342" t="inlineStr">
@@ -12524,6 +14282,7 @@
       <c r="G15" s="250"/>
       <c r="H15" s="250"/>
       <c r="I15" s="251"/>
+      <c r="J15" s="245"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A16" s="231" t="str">
@@ -12543,7 +14302,11 @@
           </r>
         </is>
       </c>
+      <c r="F16" s="245"/>
+      <c r="G16" s="245"/>
+      <c r="H16" s="245"/>
       <c r="I16" s="262"/>
+      <c r="J16" s="245"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
       <c r="A17" s="342" t="inlineStr">
@@ -12570,6 +14333,7 @@
       <c r="G17" s="250"/>
       <c r="H17" s="250"/>
       <c r="I17" s="251"/>
+      <c r="J17" s="245"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A18" s="350" t="str">
@@ -12587,6 +14351,7 @@
       <c r="G18" s="252"/>
       <c r="H18" s="252"/>
       <c r="I18" s="253"/>
+      <c r="J18" s="245"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
@@ -12634,6 +14399,7 @@
           </r>
         </is>
       </c>
+      <c r="J19" s="245"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="10.5" s="245" customFormat="1">
       <c r="A20" s="30"/>
@@ -12645,6 +14411,7 @@
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
+      <c r="J20" s="245"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
@@ -13113,7 +14880,9 @@
           </r>
         </is>
       </c>
+      <c r="F33" s="245"/>
       <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -13135,7 +14904,11 @@
           </r>
         </is>
       </c>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
       <c r="I34" s="32"/>
+      <c r="J34"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="30" t="inlineStr">
@@ -13153,6 +14926,7 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="32"/>
+      <c r="J35"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="30"/>
@@ -13164,6 +14938,7 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="32"/>
+      <c r="J36"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="30"/>
@@ -13175,6 +14950,7 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
       <c r="I37" s="32"/>
+      <c r="J37"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="30"/>
@@ -13186,6 +14962,7 @@
       <c r="G38" s="31"/>
       <c r="H38" s="31"/>
       <c r="I38" s="32"/>
+      <c r="J38"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="30"/>
@@ -13197,6 +14974,7 @@
       <c r="G39" s="31"/>
       <c r="H39" s="31"/>
       <c r="I39" s="32"/>
+      <c r="J39"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="33"/>
@@ -13208,6 +14986,7 @@
       <c r="G40" s="34"/>
       <c r="H40" s="34"/>
       <c r="I40" s="35"/>
+      <c r="J40"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -13295,27 +15074,34 @@
   <sheetData>
     <row r="1" spans="1:7" customHeight="1" ht="84" s="245" customFormat="1">
       <c r="A1" s="242"/>
+      <c r="B1" s="245"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
       <c r="E1" s="241" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">PROFORM INVOICE</t>
-          </r>
-        </is>
-      </c>
+            <t xml:space="preserve">PROFORMA INVOICE</t>
+          </r>
+        </is>
+      </c>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="245" customFormat="1">
-      <c r="A2" s="243" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Ssancar LTD 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea   Phone: +82-505-366-9977</t>
-          </r>
-        </is>
-      </c>
+      <c r="A2" s="243" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="245"/>
+      <c r="C2" s="245"/>
       <c r="D2" s="243"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="245"/>
     </row>
     <row r="3" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A3" s="245"/>
+      <c r="B3" s="245"/>
+      <c r="C3" s="245"/>
       <c r="D3" s="243"/>
       <c r="E3" s="44" t="inlineStr">
         <is>
@@ -13351,6 +15137,8 @@
     <row r="5" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A5" s="238"/>
       <c r="B5" s="238"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
       <c r="E5" s="44" t="inlineStr">
         <is>
           <r>
@@ -13367,6 +15155,8 @@
     <row r="6" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A6" s="238"/>
       <c r="B6" s="238"/>
+      <c r="C6" s="245"/>
+      <c r="D6" s="245"/>
       <c r="E6" s="44" t="inlineStr">
         <is>
           <r>
@@ -13379,10 +15169,13 @@
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A7" s="238"/>
+      <c r="B7" s="245"/>
+      <c r="C7" s="245"/>
+      <c r="D7" s="245"/>
       <c r="E7" s="44" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Adress</t>
+            <t xml:space="preserve">Address</t>
           </r>
         </is>
       </c>
@@ -13391,6 +15184,9 @@
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A8" s="238"/>
+      <c r="B8" s="245"/>
+      <c r="C8" s="245"/>
+      <c r="D8" s="245"/>
       <c r="E8" s="44" t="inlineStr">
         <is>
           <r>
@@ -13404,6 +15200,8 @@
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A9" s="238"/>
       <c r="B9" s="238"/>
+      <c r="C9" s="245"/>
+      <c r="D9" s="245"/>
       <c r="E9" s="44" t="inlineStr">
         <is>
           <r>
@@ -13416,6 +15214,9 @@
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A10" s="238"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
       <c r="E10" s="44"/>
       <c r="F10" s="46"/>
       <c r="G10" s="45"/>
@@ -13423,6 +15224,8 @@
     <row r="11" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A11" s="237"/>
       <c r="B11" s="237"/>
+      <c r="C11" s="245"/>
+      <c r="D11" s="245"/>
       <c r="E11" s="44" t="inlineStr">
         <is>
           <r>
@@ -13438,6 +15241,9 @@
     </row>
     <row r="12" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A12" s="237"/>
+      <c r="B12" s="245"/>
+      <c r="C12" s="245"/>
+      <c r="D12" s="245"/>
       <c r="E12" s="44" t="inlineStr">
         <is>
           <r>
@@ -13453,6 +15259,7 @@
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A13" s="244"/>
+      <c r="B13" s="245"/>
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44" t="inlineStr">
@@ -13470,9 +15277,12 @@
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="17.25" s="245" customFormat="1">
       <c r="A14" s="244"/>
+      <c r="B14" s="245"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
       <c r="E14" s="380"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A15" s="381" t="inlineStr">
@@ -13526,7 +15336,7 @@
       <c r="A17" s="239" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Swift Cose</t>
+            <t xml:space="preserve">Swift Code</t>
           </r>
         </is>
       </c>
@@ -13542,7 +15352,7 @@
       <c r="E17" s="239" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Bank Adress</t>
+            <t xml:space="preserve">Bank Address</t>
           </r>
         </is>
       </c>
@@ -13575,7 +15385,7 @@
       <c r="E18" s="239" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Beneficiary Adress</t>
+            <t xml:space="preserve">Beneficiary Address</t>
           </r>
         </is>
       </c>
@@ -13589,9 +15399,13 @@
       <c r="G18" s="383"/>
     </row>
     <row r="19" spans="1:7">
+      <c r="A19" s="245"/>
+      <c r="B19" s="245"/>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
       <c r="E19" s="380"/>
+      <c r="F19" s="245"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A20" s="42" t="inlineStr">

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="378">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -488,11 +488,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">자가용</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">④ 차               명</t>
     </r>
   </si>
@@ -919,11 +914,6 @@
   <si>
     <r>
       <t xml:space="preserve">③Usage</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Private car</t>
     </r>
   </si>
   <si>
@@ -7317,12 +7307,9 @@
           </r>
         </is>
       </c>
-      <c r="P4" s="152" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">자가용</t>
-          </r>
-        </is>
+      <c r="P4" s="152" t="str">
+        <f>구매리스트!B8</f>
+        <v>0</v>
       </c>
       <c r="Q4" s="254"/>
       <c r="R4" s="244"/>
@@ -7675,7 +7662,7 @@
       <c r="H15" s="244"/>
       <c r="I15" s="244"/>
       <c r="J15" s="391" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K15" s="244"/>
       <c r="L15" s="244"/>
@@ -9263,12 +9250,9 @@
           </r>
         </is>
       </c>
-      <c r="P4" s="177" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Private car</t>
-          </r>
-        </is>
+      <c r="P4" s="177" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(구매리스트!B8,"자가용","Private"),"영업용","Business"),"관용","Official")</f>
+        <v>0</v>
       </c>
       <c r="Q4" s="254"/>
       <c r="R4" s="244"/>
@@ -9677,7 +9661,7 @@
       <c r="H15" s="244"/>
       <c r="I15" s="244"/>
       <c r="J15" s="392" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K15" s="244"/>
       <c r="L15" s="244"/>
@@ -12216,7 +12200,7 @@
       <c r="E34" s="77"/>
       <c r="F34" s="77"/>
       <c r="G34" s="393" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H34" s="77"/>
       <c r="I34" s="77"/>
@@ -12941,7 +12925,7 @@
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="244" customFormat="1">
       <c r="A3" s="343" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B3" s="244"/>
       <c r="C3" s="244"/>
@@ -14026,7 +14010,7 @@
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="244" customFormat="1">
       <c r="A3" s="343" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B3" s="244"/>
       <c r="C3" s="244"/>
@@ -15095,7 +15079,7 @@
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="244" customFormat="1">
       <c r="A2" s="242" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B2" s="244"/>
       <c r="C2" s="244"/>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="4" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -3493,7 +3493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="400">
+  <cellXfs count="402">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4693,6 +4693,12 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="13" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="11" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="11" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12867,7 +12873,7 @@
     <col min="4" max="4" width="23.625" customWidth="true" style="244"/>
     <col min="5" max="5" width="7.75" customWidth="true" style="244"/>
     <col min="6" max="6" width="2.125" customWidth="true" style="244"/>
-    <col min="7" max="7" width="12.25" customWidth="true" style="244"/>
+    <col min="7" max="7" width="19.5" customWidth="true" style="244"/>
     <col min="8" max="8" width="13.75" customWidth="true" style="244"/>
     <col min="9" max="9" width="13.25" customWidth="true" style="244"/>
   </cols>
@@ -12909,7 +12915,7 @@
         </is>
       </c>
       <c r="F2" s="249"/>
-      <c r="G2" s="128" t="str">
+      <c r="G2" s="400" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
@@ -12938,7 +12944,7 @@
         </is>
       </c>
       <c r="F3" s="244"/>
-      <c r="G3" s="129" t="str">
+      <c r="G3" s="401" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -5811,10 +5811,7 @@
           </r>
         </is>
       </c>
-      <c r="I6" s="115" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"승용 소형","Small Passenger"),"승용 중형","Medium Passenger"),"승용 대형","HEAVY Passenger"),"중형 승합","Medium Ven"),"대형 승합","Large Ven"),"중형 화물","Medium Cargo")</f>
-        <v>0</v>
-      </c>
+      <c r="I6" s="115"/>
       <c r="J6" s="242"/>
       <c r="K6" s="242"/>
       <c r="L6" s="242"/>

--- a/resources/templates/system/clearance_set.xlsx
+++ b/resources/templates/system/clearance_set.xlsx
@@ -6149,10 +6149,7 @@
         </is>
       </c>
       <c r="H13" s="243"/>
-      <c r="I13" s="113" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
-        <v>0</v>
-      </c>
+      <c r="I13" s="113"/>
       <c r="J13" s="242"/>
       <c r="K13" s="242"/>
       <c r="L13" s="242"/>
